--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="100-Day Roadmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Feature · Mind Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="OW · Features" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="OW · Connectors" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="OW · Tools" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="OW · Providers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="OW · Configs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="OW · GUI Screens" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100-Day Roadmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature · Mind Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Features" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Next Tasks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Connectors" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Tools" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Providers" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Configs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · GUI Screens" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,8 +26,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="24">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -165,8 +168,61 @@
       <color rgb="003730A3"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -243,8 +299,43 @@
         <fgColor rgb="00F1EBFE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C3AED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -266,11 +357,55 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -616,6 +751,58 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1413,6 +1600,1318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="107" t="inlineStr">
+        <is>
+          <t>Configuration surface (coworker/config.py + docs/config.example.toml). Local, file-based, no cloud config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D2" s="29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E2" s="29" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F2" s="29" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32.75" customHeight="1">
+      <c r="A3" s="108" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B3" s="112" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C3" s="112" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="109" t="inlineStr">
+        <is>
+          <t>gpt-5.6-sol</t>
+        </is>
+      </c>
+      <c r="E3" s="109" t="inlineStr">
+        <is>
+          <t>Default model id used for new sessions; overridable per session in the UI/CLI. docs example uses 'gpt-5.5'.</t>
+        </is>
+      </c>
+      <c r="F3" s="109" t="inlineStr">
+        <is>
+          <t>coworker/config.py; docs/config.example.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24.75" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="B4" s="114" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C4" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="110" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="E4" s="110" t="inlineStr">
+        <is>
+          <t>Default permission mode: plan | interactive | auto | custom (also discuss).</t>
+        </is>
+      </c>
+      <c r="F4" s="110" t="inlineStr">
+        <is>
+          <t>coworker/config.py; docs/config.example.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="108" t="inlineStr">
+        <is>
+          <t>max_iterations</t>
+        </is>
+      </c>
+      <c r="B5" s="112" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C5" s="112" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D5" s="109" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E5" s="109" t="inlineStr">
+        <is>
+          <t>Max model&lt;-&gt;tool iterations per turn before stopping. docs example shows 12.</t>
+        </is>
+      </c>
+      <c r="F5" s="109" t="inlineStr">
+        <is>
+          <t>coworker/config.py; docs/config.example.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="49.75" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>allowed_commands</t>
+        </is>
+      </c>
+      <c r="B6" s="114" t="inlineStr">
+        <is>
+          <t>global-only (workspace only after trust)</t>
+        </is>
+      </c>
+      <c r="C6" s="114" t="inlineStr">
+        <is>
+          <t>list[string]</t>
+        </is>
+      </c>
+      <c r="D6" s="110" t="inlineStr">
+        <is>
+          <t>[] (empty)</t>
+        </is>
+      </c>
+      <c r="E6" s="110" t="inlineStr">
+        <is>
+          <t>Command prefixes that auto-run without an approval prompt (prefix match). Built-in default is empty; workspace-declared entries apply only after the workspace path is trusted.</t>
+        </is>
+      </c>
+      <c r="F6" s="110" t="inlineStr">
+        <is>
+          <t>coworker/config.py; docs/config.example.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="43.5" customHeight="1">
+      <c r="A7" s="108" t="inlineStr">
+        <is>
+          <t>auto_allow</t>
+        </is>
+      </c>
+      <c r="B7" s="112" t="inlineStr">
+        <is>
+          <t>global-only</t>
+        </is>
+      </c>
+      <c r="C7" s="112" t="inlineStr">
+        <is>
+          <t>list[string]</t>
+        </is>
+      </c>
+      <c r="D7" s="109" t="inlineStr">
+        <is>
+          <t>[] (empty)</t>
+        </is>
+      </c>
+      <c r="E7" s="109" t="inlineStr">
+        <is>
+          <t>In 'custom' permission mode, tools auto-approved while everything else still asks (e.g. write_file, replace_in_file, apply_patch, apply_unified_diff).</t>
+        </is>
+      </c>
+      <c r="F7" s="109" t="inlineStr">
+        <is>
+          <t>coworker/config.py; docs/config.example.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20.5" customHeight="1">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="B8" s="114" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C8" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D8" s="110" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="E8" s="110" t="inlineStr">
+        <is>
+          <t>Bind address for the openworker-server local agent server.</t>
+        </is>
+      </c>
+      <c r="F8" s="110" t="inlineStr">
+        <is>
+          <t>coworker/config.py; docs/config.example.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="108" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="B9" s="112" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C9" s="112" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D9" s="109" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="E9" s="109" t="inlineStr">
+        <is>
+          <t>Bind port for the openworker-server local agent server.</t>
+        </is>
+      </c>
+      <c r="F9" s="109" t="inlineStr">
+        <is>
+          <t>coworker/config.py; docs/config.example.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="29.5" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>web_search_provider</t>
+        </is>
+      </c>
+      <c r="B10" s="114" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C10" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" s="110" t="inlineStr">
+        <is>
+          <t>duckduckgo</t>
+        </is>
+      </c>
+      <c r="E10" s="110" t="inlineStr">
+        <is>
+          <t>Web search provider: 'duckduckgo' (keyless default) | 'tavily' | 'brave' (require an API key).</t>
+        </is>
+      </c>
+      <c r="F10" s="110" t="inlineStr">
+        <is>
+          <t>coworker/config.py; coworker/web/providers.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="35.5" customHeight="1">
+      <c r="A11" s="108" t="inlineStr">
+        <is>
+          <t>cloud_base_url</t>
+        </is>
+      </c>
+      <c r="B11" s="112" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C11" s="112" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D11" s="109" t="inlineStr">
+        <is>
+          <t>https://api.openworker.com</t>
+        </is>
+      </c>
+      <c r="E11" s="109" t="inlineStr">
+        <is>
+          <t>OpenWorker Cloud API base URL for sign-in and managed connectors; point at dev/staging/BYO-VPC instances via override.</t>
+        </is>
+      </c>
+      <c r="F11" s="109" t="inlineStr">
+        <is>
+          <t>coworker/config.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>cloud_auth_domain</t>
+        </is>
+      </c>
+      <c r="B12" s="114" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C12" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D12" s="110" t="inlineStr">
+        <is>
+          <t>opencoworker.us.auth0.com</t>
+        </is>
+      </c>
+      <c r="E12" s="110" t="inlineStr">
+        <is>
+          <t>Auth0 tenant domain used for the sign-in Authorization Code + PKCE flow.</t>
+        </is>
+      </c>
+      <c r="F12" s="110" t="inlineStr">
+        <is>
+          <t>coworker/config.py; coworker/cloud.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="108" t="inlineStr">
+        <is>
+          <t>cloud_client_id</t>
+        </is>
+      </c>
+      <c r="B13" s="112" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C13" s="112" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D13" s="109" t="inlineStr">
+        <is>
+          <t>g1l4Q1lhYWmyS03qPSf4KEJGrgq02Qam</t>
+        </is>
+      </c>
+      <c r="E13" s="109" t="inlineStr">
+        <is>
+          <t>Auth0 OAuth client id for the cloud sign-in flow.</t>
+        </is>
+      </c>
+      <c r="F13" s="109" t="inlineStr">
+        <is>
+          <t>coworker/config.py; coworker/cloud.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30.75" customHeight="1">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>cloud_audience</t>
+        </is>
+      </c>
+      <c r="B14" s="114" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C14" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D14" s="110" t="inlineStr">
+        <is>
+          <t>https://api.opencoworker.app</t>
+        </is>
+      </c>
+      <c r="E14" s="110" t="inlineStr">
+        <is>
+          <t>Auth0 API audience; must match the registered API identifier (kept at the legacy value on purpose).</t>
+        </is>
+      </c>
+      <c r="F14" s="110" t="inlineStr">
+        <is>
+          <t>coworker/config.py; coworker/cloud.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.25" customHeight="1">
+      <c r="A15" s="108" t="inlineStr">
+        <is>
+          <t>cloud_relay_ws_url</t>
+        </is>
+      </c>
+      <c r="B15" s="112" t="inlineStr">
+        <is>
+          <t>global/workspace</t>
+        </is>
+      </c>
+      <c r="C15" s="112" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D15" s="109" t="inlineStr">
+        <is>
+          <t>wss://l4z1paxb83.execute-api.us-east-1.amazonaws.com/ocw-connect</t>
+        </is>
+      </c>
+      <c r="E15" s="109" t="inlineStr">
+        <is>
+          <t>Managed relay WebSocket endpoint for Slack/GitHub inbound events. Empty override disables the relay (manual Socket Mode still works).</t>
+        </is>
+      </c>
+      <c r="F15" s="109" t="inlineStr">
+        <is>
+          <t>coworker/config.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.25" customHeight="1">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>(scheduler) tick_seconds</t>
+        </is>
+      </c>
+      <c r="B16" s="114" t="inlineStr">
+        <is>
+          <t>automation runtime</t>
+        </is>
+      </c>
+      <c r="C16" s="114" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D16" s="110" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="E16" s="110" t="inlineStr">
+        <is>
+          <t>How often the automation scheduler polls for due tasks and self-wake resumptions.</t>
+        </is>
+      </c>
+      <c r="F16" s="110" t="inlineStr">
+        <is>
+          <t>coworker/automation/scheduler.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="108" t="inlineStr">
+        <is>
+          <t>schedule.kind</t>
+        </is>
+      </c>
+      <c r="B17" s="112" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C17" s="112" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D17" s="109" t="inlineStr">
+        <is>
+          <t>cron</t>
+        </is>
+      </c>
+      <c r="E17" s="109" t="inlineStr">
+        <is>
+          <t>A task's schedule kind: 'cron' (recurring) or 'once' (one-time).</t>
+        </is>
+      </c>
+      <c r="F17" s="109" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py; tools.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28.5" customHeight="1">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>schedule.cron</t>
+        </is>
+      </c>
+      <c r="B18" s="114" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C18" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D18" s="110" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E18" s="110" t="inlineStr">
+        <is>
+          <t>5-field cron expression for recurring tasks (e.g. '10 19 * * *'), validated with croniter.</t>
+        </is>
+      </c>
+      <c r="F18" s="110" t="inlineStr">
+        <is>
+          <t>coworker/automation/tools.py; store.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="108" t="inlineStr">
+        <is>
+          <t>schedule.fire_at</t>
+        </is>
+      </c>
+      <c r="B19" s="112" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C19" s="112" t="inlineStr">
+        <is>
+          <t>string (ISO datetime)</t>
+        </is>
+      </c>
+      <c r="D19" s="109" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E19" s="109" t="inlineStr">
+        <is>
+          <t>ISO datetime for a one-time run (used when kind='once').</t>
+        </is>
+      </c>
+      <c r="F19" s="109" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28.75" customHeight="1">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>schedule.timezone</t>
+        </is>
+      </c>
+      <c r="B20" s="114" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C20" s="114" t="inlineStr">
+        <is>
+          <t>string (IANA tz or 'local')</t>
+        </is>
+      </c>
+      <c r="D20" s="110" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E20" s="110" t="inlineStr">
+        <is>
+          <t>Timezone for schedule computation; 'local' means the machine's clock (local-first default).</t>
+        </is>
+      </c>
+      <c r="F20" s="110" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py; store.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20.5" customHeight="1">
+      <c r="A21" s="108" t="inlineStr">
+        <is>
+          <t>task.notify_on_completion</t>
+        </is>
+      </c>
+      <c r="B21" s="112" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C21" s="112" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D21" s="109" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E21" s="109" t="inlineStr">
+        <is>
+          <t>Whether the automation notifies on completion of each run.</t>
+        </is>
+      </c>
+      <c r="F21" s="109" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26.75" customHeight="1">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>task.notify_target</t>
+        </is>
+      </c>
+      <c r="B22" s="114" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C22" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D22" s="110" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E22" s="110" t="inlineStr">
+        <is>
+          <t>Optional extra messaging target for completion notifications (e.g. 'telegram:123').</t>
+        </is>
+      </c>
+      <c r="F22" s="110" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25.25" customHeight="1">
+      <c r="A23" s="108" t="inlineStr">
+        <is>
+          <t>task.max_runs</t>
+        </is>
+      </c>
+      <c r="B23" s="112" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C23" s="112" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D23" s="109" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E23" s="109" t="inlineStr">
+        <is>
+          <t>Optional cap on total runs; after reaching it next_run is no longer computed.</t>
+        </is>
+      </c>
+      <c r="F23" s="109" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py; store.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39.25" customHeight="1">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>task.always_allowed_tools</t>
+        </is>
+      </c>
+      <c r="B24" s="114" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C24" s="114" t="inlineStr">
+        <is>
+          <t>list[string]</t>
+        </is>
+      </c>
+      <c r="D24" s="110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E24" s="110" t="inlineStr">
+        <is>
+          <t>Standing scoped approvals as 'tool target' entries granting an automation a specific write against an exact target without re-asking.</t>
+        </is>
+      </c>
+      <c r="F24" s="110" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25.5" customHeight="1">
+      <c r="A25" s="108" t="inlineStr">
+        <is>
+          <t>task.enabled</t>
+        </is>
+      </c>
+      <c r="B25" s="112" t="inlineStr">
+        <is>
+          <t>automation task schema</t>
+        </is>
+      </c>
+      <c r="C25" s="112" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D25" s="109" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E25" s="109" t="inlineStr">
+        <is>
+          <t>Whether the task is active; disabled tasks compute no next_run and never fire.</t>
+        </is>
+      </c>
+      <c r="F25" s="109" t="inlineStr">
+        <is>
+          <t>coworker/automation/models.py; store.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="41.75" customHeight="1">
+      <c r="A26" s="37" t="inlineStr">
+        <is>
+          <t>pdf.fallback_mode</t>
+        </is>
+      </c>
+      <c r="B26" s="114" t="inlineStr">
+        <is>
+          <t>settings (Token savings)</t>
+        </is>
+      </c>
+      <c r="C26" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D26" s="110" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E26" s="110" t="inlineStr">
+        <is>
+          <t>Local PDF handling for models lacking native PDF: 'text' (extract embedded text via pypdf) or 'images' (rasterize pages to PNGs via pypdfium2).</t>
+        </is>
+      </c>
+      <c r="F26" s="110" t="inlineStr">
+        <is>
+          <t>coworker/pdf_support.py; route /v1/settings/pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="108" t="inlineStr">
+        <is>
+          <t>MAX_ATTACHMENTS</t>
+        </is>
+      </c>
+      <c r="B27" s="112" t="inlineStr">
+        <is>
+          <t>attachments limits</t>
+        </is>
+      </c>
+      <c r="C27" s="112" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D27" s="109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E27" s="109" t="inlineStr">
+        <is>
+          <t>Maximum attachments appended to a single user turn.</t>
+        </is>
+      </c>
+      <c r="F27" s="109" t="inlineStr">
+        <is>
+          <t>coworker/attachments.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20.75" customHeight="1">
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>MAX_IMAGE_CHARS</t>
+        </is>
+      </c>
+      <c r="B28" s="114" t="inlineStr">
+        <is>
+          <t>attachments limits</t>
+        </is>
+      </c>
+      <c r="C28" s="114" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D28" s="110" t="inlineStr">
+        <is>
+          <t>12000000</t>
+        </is>
+      </c>
+      <c r="E28" s="110" t="inlineStr">
+        <is>
+          <t>Data-URL length cap for image attachments (~8-9MB decoded).</t>
+        </is>
+      </c>
+      <c r="F28" s="110" t="inlineStr">
+        <is>
+          <t>coworker/attachments.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27.25" customHeight="1">
+      <c r="A29" s="108" t="inlineStr">
+        <is>
+          <t>MAX_PDF_CHARS</t>
+        </is>
+      </c>
+      <c r="B29" s="112" t="inlineStr">
+        <is>
+          <t>attachments limits</t>
+        </is>
+      </c>
+      <c r="C29" s="112" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D29" s="109" t="inlineStr">
+        <is>
+          <t>15000000</t>
+        </is>
+      </c>
+      <c r="E29" s="109" t="inlineStr">
+        <is>
+          <t>Data-URL length cap for PDF attachments (~10MB decoded, matching the GUI pick limit).</t>
+        </is>
+      </c>
+      <c r="F29" s="109" t="inlineStr">
+        <is>
+          <t>coworker/attachments.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>MAX_TEXT_CHARS</t>
+        </is>
+      </c>
+      <c r="B30" s="114" t="inlineStr">
+        <is>
+          <t>attachments limits</t>
+        </is>
+      </c>
+      <c r="C30" s="114" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D30" s="110" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="E30" s="110" t="inlineStr">
+        <is>
+          <t>Per-text-file character cap when inlining a text attachment.</t>
+        </is>
+      </c>
+      <c r="F30" s="110" t="inlineStr">
+        <is>
+          <t>coworker/attachments.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="27.75" customHeight="1">
+      <c r="A31" s="108" t="inlineStr">
+        <is>
+          <t>inbox binding.channel</t>
+        </is>
+      </c>
+      <c r="B31" s="112" t="inlineStr">
+        <is>
+          <t>inbox routing</t>
+        </is>
+      </c>
+      <c r="C31" s="112" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D31" s="109" t="inlineStr">
+        <is>
+          <t>null (in-app only)</t>
+        </is>
+      </c>
+      <c r="E31" s="109" t="inlineStr">
+        <is>
+          <t>Delivery binding channel for a named inbox: null (in-app only), 'slack', or 'telegram'.</t>
+        </is>
+      </c>
+      <c r="F31" s="109" t="inlineStr">
+        <is>
+          <t>coworker/inbox_routing.py; route /v1/inbox/routing/binding</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="29.25" customHeight="1">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>persona.default_permission_mode</t>
+        </is>
+      </c>
+      <c r="B32" s="114" t="inlineStr">
+        <is>
+          <t>persona manifest frontmatter</t>
+        </is>
+      </c>
+      <c r="C32" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D32" s="110" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="E32" s="110" t="inlineStr">
+        <is>
+          <t>Recommended permission mode a persona declares: discuss | plan | interactive | custom | auto.</t>
+        </is>
+      </c>
+      <c r="F32" s="110" t="inlineStr">
+        <is>
+          <t>coworker/personas/manifest.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28.25" customHeight="1">
+      <c r="A33" s="108" t="inlineStr">
+        <is>
+          <t>persona.family</t>
+        </is>
+      </c>
+      <c r="B33" s="112" t="inlineStr">
+        <is>
+          <t>persona manifest frontmatter</t>
+        </is>
+      </c>
+      <c r="C33" s="112" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D33" s="109" t="inlineStr">
+        <is>
+          <t>knowledge</t>
+        </is>
+      </c>
+      <c r="E33" s="109" t="inlineStr">
+        <is>
+          <t>Persona family: 'code' (git workspace) or 'knowledge' (deliverable scratch + user roots).</t>
+        </is>
+      </c>
+      <c r="F33" s="109" t="inlineStr">
+        <is>
+          <t>coworker/personas/manifest.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="31.5" customHeight="1">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>persona.tools</t>
+        </is>
+      </c>
+      <c r="B34" s="114" t="inlineStr">
+        <is>
+          <t>persona manifest frontmatter</t>
+        </is>
+      </c>
+      <c r="C34" s="114" t="inlineStr">
+        <is>
+          <t>list[string]</t>
+        </is>
+      </c>
+      <c r="D34" s="110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E34" s="110" t="inlineStr">
+        <is>
+          <t>Capability ids from the vetted catalog (code_files, files, git, search, shell, todo) the persona uses.</t>
+        </is>
+      </c>
+      <c r="F34" s="110" t="inlineStr">
+        <is>
+          <t>coworker/personas/manifest.py; catalog.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="23.25" customHeight="1">
+      <c r="A35" s="108" t="inlineStr">
+        <is>
+          <t>persona.messaging</t>
+        </is>
+      </c>
+      <c r="B35" s="112" t="inlineStr">
+        <is>
+          <t>persona manifest frontmatter</t>
+        </is>
+      </c>
+      <c r="C35" s="112" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D35" s="109" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" s="109" t="inlineStr">
+        <is>
+          <t>Whether the persona is reachable/able to act over messaging channels.</t>
+        </is>
+      </c>
+      <c r="F35" s="109" t="inlineStr">
+        <is>
+          <t>coworker/personas/manifest.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>persona.connectors</t>
+        </is>
+      </c>
+      <c r="B36" s="114" t="inlineStr">
+        <is>
+          <t>persona manifest frontmatter</t>
+        </is>
+      </c>
+      <c r="C36" s="114" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D36" s="110" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" s="110" t="inlineStr">
+        <is>
+          <t>Whether the persona uses external connectors.</t>
+        </is>
+      </c>
+      <c r="F36" s="110" t="inlineStr">
+        <is>
+          <t>coworker/personas/manifest.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25.75" customHeight="1">
+      <c r="A37" s="108" t="inlineStr">
+        <is>
+          <t>persona.recommended_models</t>
+        </is>
+      </c>
+      <c r="B37" s="112" t="inlineStr">
+        <is>
+          <t>persona manifest frontmatter</t>
+        </is>
+      </c>
+      <c r="C37" s="112" t="inlineStr">
+        <is>
+          <t>list[string]</t>
+        </is>
+      </c>
+      <c r="D37" s="109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E37" s="109" t="inlineStr">
+        <is>
+          <t>Models the persona recommends (e.g. anthropic:claude-opus-4-8, openai:gpt-5.5).</t>
+        </is>
+      </c>
+      <c r="F37" s="109" t="inlineStr">
+        <is>
+          <t>coworker/personas/manifest.py; builtin/ops.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="37" t="inlineStr">
+        <is>
+          <t>subscription.filter</t>
+        </is>
+      </c>
+      <c r="B38" s="114" t="inlineStr">
+        <is>
+          <t>channel subscription schema</t>
+        </is>
+      </c>
+      <c r="C38" s="114" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D38" s="110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E38" s="110" t="inlineStr">
+        <is>
+          <t>Which channel messages a subscription delivers; v1 always delivers 'all' (reserved for 'mentions' etc.).</t>
+        </is>
+      </c>
+      <c r="F38" s="110" t="inlineStr">
+        <is>
+          <t>coworker/subscriptions.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="108" t="inlineStr">
+        <is>
+          <t>skill.allowed-tools</t>
+        </is>
+      </c>
+      <c r="B39" s="112" t="inlineStr">
+        <is>
+          <t>SKILL.md frontmatter</t>
+        </is>
+      </c>
+      <c r="C39" s="112" t="inlineStr">
+        <is>
+          <t>list[string]</t>
+        </is>
+      </c>
+      <c r="D39" s="109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E39" s="109" t="inlineStr">
+        <is>
+          <t>Optional tool allowlist a skill declares in its frontmatter.</t>
+        </is>
+      </c>
+      <c r="F39" s="109" t="inlineStr">
+        <is>
+          <t>coworker/skills/base.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="23.5" customHeight="1">
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t>COWORKER_EXIT_WITH_PARENT</t>
+        </is>
+      </c>
+      <c r="B40" s="114" t="inlineStr">
+        <is>
+          <t>server env (sidecar)</t>
+        </is>
+      </c>
+      <c r="C40" s="114" t="inlineStr">
+        <is>
+          <t>env flag ('1')</t>
+        </is>
+      </c>
+      <c r="D40" s="110" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="E40" s="110" t="inlineStr">
+        <is>
+          <t>When set, the server exits if its parent (desktop shell) process dies.</t>
+        </is>
+      </c>
+      <c r="F40" s="110" t="inlineStr">
+        <is>
+          <t>coworker/server/run.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="108" t="inlineStr">
+        <is>
+          <t>COWORKER_PARENT_PID / COWORKER_PORT</t>
+        </is>
+      </c>
+      <c r="B41" s="112" t="inlineStr">
+        <is>
+          <t>server env (sidecar)</t>
+        </is>
+      </c>
+      <c r="C41" s="112" t="inlineStr">
+        <is>
+          <t>env int</t>
+        </is>
+      </c>
+      <c r="D41" s="109" t="inlineStr">
+        <is>
+          <t>unset</t>
+        </is>
+      </c>
+      <c r="E41" s="109" t="inlineStr">
+        <is>
+          <t>Parent PID the sidecar watches for liveness, and the port used in OAuth state suffixing.</t>
+        </is>
+      </c>
+      <c r="F41" s="109" t="inlineStr">
+        <is>
+          <t>coworker/server/run.py; cloud.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10948,6 +12447,9 @@
           <t>React Flow (@xyflow/react v12) for canvas/pan/zoom/minimap/export; Zustand for an isolated feature store (app's first Zustand use).</t>
         </is>
       </c>
+      <c r="C3" s="120" t="n"/>
+      <c r="D3" s="120" t="n"/>
+      <c r="E3" s="121" t="n"/>
     </row>
     <row r="4" ht="42.23076923076923" customHeight="1">
       <c r="A4" s="116" t="inlineStr">
@@ -10960,6 +12462,9 @@
           <t>New: mindmap_models.py, mindmap_service.py, mindmap_routes.py (/api/v1/mindmaps), mindmap_ai.py (P2), mindmap_export.py (P3). Reuses schema.py Base, ollama_client, Session.state.</t>
         </is>
       </c>
+      <c r="C4" s="120" t="n"/>
+      <c r="D4" s="120" t="n"/>
+      <c r="E4" s="121" t="n"/>
     </row>
     <row r="5" ht="35.11538461538461" customHeight="1">
       <c r="A5" s="116" t="inlineStr">
@@ -10972,6 +12477,9 @@
           <t>Isolated module tauri-app/src/features/mindmap/ (MindMapWorkspace entry). Reuses ui.tsx primitives + useToast; add Select/Textarea to ui.tsx.</t>
         </is>
       </c>
+      <c r="C5" s="120" t="n"/>
+      <c r="D5" s="120" t="n"/>
+      <c r="E5" s="121" t="n"/>
     </row>
     <row r="6" ht="36.46153846153846" customHeight="1">
       <c r="A6" s="116" t="inlineStr">
@@ -10984,6 +12492,9 @@
           <t>Sidebar nav /mindmap + Backlog 'List | Mind Map' toggle + Dashboard mode card. Uses Dobby violet tokens; theme-aware canvas. (see UI_INTEGRATION.md)</t>
         </is>
       </c>
+      <c r="C6" s="120" t="n"/>
+      <c r="D6" s="120" t="n"/>
+      <c r="E6" s="121" t="n"/>
     </row>
     <row r="7" ht="36.26923076923077" customHeight="1">
       <c r="A7" s="116" t="inlineStr">
@@ -10996,6 +12507,9 @@
           <t>mind_maps, mind_map_nodes (tree via parent_id), mind_map_edges (cross-branch), mind_map_snapshots (undo). String UUID PKs, metadata↔extra_metadata.</t>
         </is>
       </c>
+      <c r="C7" s="120" t="n"/>
+      <c r="D7" s="120" t="n"/>
+      <c r="E7" s="121" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="116" t="inlineStr">
@@ -11008,6 +12522,9 @@
           <t>30 new files, 7 modified files, 47 tracked steps.</t>
         </is>
       </c>
+      <c r="C8" s="120" t="n"/>
+      <c r="D8" s="120" t="n"/>
+      <c r="E8" s="121" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="118" t="inlineStr">
@@ -11137,12 +12654,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -11153,954 +12673,1884 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="122" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="122" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" s="122" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
+      <c r="D2" s="123" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E2" s="123" t="inlineStr">
+        <is>
+          <t>Dobby surface</t>
+        </is>
+      </c>
+      <c r="F2" s="123" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="108" t="inlineStr">
+      <c r="A3" s="124" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B3" s="109" t="inlineStr">
+      <c r="B3" s="124" t="inlineStr">
         <is>
           <t>Scheduled automations (cron + one-time)</t>
         </is>
       </c>
-      <c r="C3" s="109" t="inlineStr">
+      <c r="C3" s="124" t="inlineStr">
         <is>
           <t>Recurring or one-time tasks re-run fixed instructions on a schedule; the agent converts natural language timing into a 5-field cron string or a one-time ISO fire_at datetime (coworker/automation/tools.py, models.py).</t>
         </is>
       </c>
+      <c r="D3" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E3" s="126" t="inlineStr">
+        <is>
+          <t>Automations · cron + one-off</t>
+        </is>
+      </c>
+      <c r="F3" s="127" t="inlineStr">
+        <is>
+          <t>Full 5-field cron parser (stdlib, no croniter) + one-shot trigger.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="56.75" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="128" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B4" s="110" t="inlineStr">
+      <c r="B4" s="128" t="inlineStr">
         <is>
           <t>Always-on scheduler loop</t>
         </is>
       </c>
-      <c r="C4" s="110" t="inlineStr">
+      <c r="C4" s="128" t="inlineStr">
         <is>
           <t>A background scheduler ticks every ~30s in the always-on server, finds due tasks via an indexed next_run query, and spawns each run without blocking the loop (coworker/automation/scheduler.py, store.py).</t>
         </is>
       </c>
+      <c r="D4" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E4" s="126" t="inlineStr">
+        <is>
+          <t>SchedulerLoop</t>
+        </is>
+      </c>
+      <c r="F4" s="127" t="inlineStr">
+        <is>
+          <t>Ticks every 30s inside the API process; started in the app lifespan.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55.75" customHeight="1">
-      <c r="A5" s="108" t="inlineStr">
+      <c r="A5" s="124" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B5" s="109" t="inlineStr">
+      <c r="B5" s="124" t="inlineStr">
         <is>
           <t>Run-once catch-up + skip-on-overlap</t>
         </is>
       </c>
-      <c r="C5" s="109" t="inlineStr">
+      <c r="C5" s="124" t="inlineStr">
         <is>
           <t>On startup the scheduler fires anything missed while the server was down exactly once, and it refuses to stack a new run while a task's previous run is still going (coworker/automation/scheduler.py).</t>
         </is>
       </c>
+      <c r="D5" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E5" s="126" t="inlineStr">
+        <is>
+          <t>catch_up_targets()</t>
+        </is>
+      </c>
+      <c r="F5" s="127" t="inlineStr">
+        <is>
+          <t>Catches up misses &lt;24h once (not once per interval); skip-on-overlap recorded as 'skipped'.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="128" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B6" s="110" t="inlineStr">
+      <c r="B6" s="128" t="inlineStr">
         <is>
           <t>Next-fire computation with timezone</t>
         </is>
       </c>
-      <c r="C6" s="110" t="inlineStr">
+      <c r="C6" s="128" t="inlineStr">
         <is>
           <t>next_run is computed with croniter honoring the task's IANA timezone, defaulting to the machine's local clock ('local') as a local-first default (coworker/automation/store.py).</t>
         </is>
       </c>
+      <c r="D6" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E6" s="126" t="inlineStr">
+        <is>
+          <t>cron.next_fire()</t>
+        </is>
+      </c>
+      <c r="F6" s="127" t="inlineStr">
+        <is>
+          <t>Timezone-aware: 9am means 9am where you are. Impossible schedules return 'never'.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="108" t="inlineStr">
+      <c r="A7" s="124" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B7" s="109" t="inlineStr">
+      <c r="B7" s="124" t="inlineStr">
         <is>
           <t>Per-task threads, working folders and run history</t>
         </is>
       </c>
-      <c r="C7" s="109" t="inlineStr">
+      <c r="C7" s="124" t="inlineStr">
         <is>
           <t>Each task owns its own conversation thread and workspace; every fire is a persisted, continuable TaskRun with status, result text, artifacts and trigger (schedule/manual/catchup) recorded in SQLite (coworker/automation/models.py, store.py).</t>
         </is>
       </c>
+      <c r="D7" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E7" s="126" t="inlineStr">
+        <is>
+          <t>AutomationRun history</t>
+        </is>
+      </c>
+      <c r="F7" s="127" t="inlineStr">
+        <is>
+          <t>Run history, duration, status and trigger source are stored. No per-task OS threads or working folders — Dobby runs tasks in-process.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52.5" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="128" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B8" s="110" t="inlineStr">
+      <c r="B8" s="128" t="inlineStr">
         <is>
           <t>Approve-at-creation consent card</t>
         </is>
       </c>
-      <c r="C8" s="110" t="inlineStr">
+      <c r="C8" s="128" t="inlineStr">
         <is>
           <t>create_scheduled_task is approval-gated so a consent card surfaces before a standing automation exists, disclosing every read/write the instructions imply (coworker/automation/tools.py).</t>
         </is>
       </c>
+      <c r="D8" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E8" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="127" t="inlineStr">
+        <is>
+          <t>Needs the approval/consent subsystem (rows 13-19). Nothing is gated today.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="70.25" customHeight="1">
-      <c r="A9" s="108" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B9" s="109" t="inlineStr">
+      <c r="B9" s="124" t="inlineStr">
         <is>
           <t>Standing scoped approvals (per-target grants)</t>
         </is>
       </c>
-      <c r="C9" s="109" t="inlineStr">
+      <c r="C9" s="124" t="inlineStr">
         <is>
           <t>Approving a write on the consent card creates a target-bound standing grant ('tool target') so an automation may call that exact tool against that exact target every run without re-asking; grants are revocable per-automation (coworker/automation/models.py).</t>
         </is>
       </c>
+      <c r="D9" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E9" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 8.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="49.5" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="128" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B10" s="110" t="inlineStr">
+      <c r="B10" s="128" t="inlineStr">
         <is>
           <t>Example automation patterns (morning brief, weekly report, channel watch)</t>
         </is>
       </c>
-      <c r="C10" s="110" t="inlineStr">
+      <c r="C10" s="128" t="inlineStr">
         <is>
           <t>Automations cover recurring work such as a morning brief, a weekly report, or a standing watch over a channel, with runs landing in the app with full transcripts (README.md).</t>
         </is>
       </c>
+      <c r="D10" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E10" s="126" t="inlineStr">
+        <is>
+          <t>/automations/meta presets</t>
+        </is>
+      </c>
+      <c r="F10" s="127" t="inlineStr">
+        <is>
+          <t>Ships 4 action kinds (research, generate, verify, digest) and 5 schedule presets incl. a morning brief.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55.25" customHeight="1">
-      <c r="A11" s="108" t="inlineStr">
+      <c r="A11" s="124" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B11" s="109" t="inlineStr">
+      <c r="B11" s="124" t="inlineStr">
         <is>
           <t>Manual run + max-runs cap + enable/disable</t>
         </is>
       </c>
-      <c r="C11" s="109" t="inlineStr">
+      <c r="C11" s="124" t="inlineStr">
         <is>
           <t>Tasks can be run on demand, disabled/enabled, edited, deleted, and capped with max_runs after which next_run stops computing (coworker/automation/tools.py, store.py, server routes /v1/automations).</t>
         </is>
       </c>
+      <c r="D11" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E11" s="126" t="inlineStr">
+        <is>
+          <t>Run now / max_runs / enable</t>
+        </is>
+      </c>
+      <c r="F11" s="127" t="inlineStr">
+        <is>
+          <t>Manual fire, run cap that auto-disables, and enable/disable that re-arms from now.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="47.25" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="128" t="inlineStr">
         <is>
           <t>Automation</t>
         </is>
       </c>
-      <c r="B12" s="110" t="inlineStr">
+      <c r="B12" s="128" t="inlineStr">
         <is>
           <t>Unread run tracking</t>
         </is>
       </c>
-      <c r="C12" s="110" t="inlineStr">
+      <c r="C12" s="128" t="inlineStr">
         <is>
           <t>A seen_runs_at mark tracks which task runs are new since the automation's detail was last opened, driving 'new' pills in the sidebar (coworker/automation/models.py).</t>
         </is>
       </c>
+      <c r="D12" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E12" s="126" t="inlineStr">
+        <is>
+          <t>unread_count + mark read</t>
+        </is>
+      </c>
+      <c r="F12" s="127" t="inlineStr">
+        <is>
+          <t>Badge per automation and a project total; cleared when runs are opened.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="59" customHeight="1">
-      <c r="A13" s="108" t="inlineStr">
+      <c r="A13" s="124" t="inlineStr">
         <is>
           <t>Inbox &amp; Approvals</t>
         </is>
       </c>
-      <c r="B13" s="109" t="inlineStr">
+      <c r="B13" s="124" t="inlineStr">
         <is>
           <t>Cross-session attention Inbox</t>
         </is>
       </c>
-      <c r="C13" s="109" t="inlineStr">
+      <c r="C13" s="124" t="inlineStr">
         <is>
           <t>A single canonical queue holds what agents need from the human — approvals, questions, notifications, directory-grant requests, and plan approvals — as the store of record across all sessions (coworker/inbox.py).</t>
         </is>
       </c>
+      <c r="D13" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E13" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="127" t="inlineStr">
+        <is>
+          <t>Needs an Inbox surface. Highest-value next cluster.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="66" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="128" t="inlineStr">
         <is>
           <t>Inbox &amp; Approvals</t>
         </is>
       </c>
-      <c r="B14" s="110" t="inlineStr">
+      <c r="B14" s="128" t="inlineStr">
         <is>
           <t>Approval-gated writes, sends and shell commands</t>
         </is>
       </c>
-      <c r="C14" s="110" t="inlineStr">
+      <c r="C14" s="128" t="inlineStr">
         <is>
           <t>Consequential actions (file writes, external sends, shell) are permission-classified and gated; inbox_approver turns a permission request into an item and suspends the agent until it is resolved (coworker/inbox.py, permissions.py, risk.py).</t>
         </is>
       </c>
+      <c r="D14" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E14" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="127" t="inlineStr">
+        <is>
+          <t>Dobby has no shell execution or outbound sends yet, so there is nothing to gate — becomes real with Terminal (P2).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="108" t="inlineStr">
+      <c r="A15" s="124" t="inlineStr">
         <is>
           <t>Inbox &amp; Approvals</t>
         </is>
       </c>
-      <c r="B15" s="109" t="inlineStr">
+      <c r="B15" s="124" t="inlineStr">
         <is>
           <t>Parked, resolve-from-anywhere asks</t>
         </is>
       </c>
-      <c r="C15" s="109" t="inlineStr">
+      <c r="C15" s="124" t="inlineStr">
         <is>
           <t>Each item is a durable pending-to-resolved record, idempotent by (session, tool_call_id) and first-responder-wins, so it can be answered from the app, Slack, or the composer and survives restarts (coworker/inbox.py).</t>
         </is>
       </c>
+      <c r="D15" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E15" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 13.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="128" t="inlineStr">
         <is>
           <t>Inbox &amp; Approvals</t>
         </is>
       </c>
-      <c r="B16" s="110" t="inlineStr">
+      <c r="B16" s="128" t="inlineStr">
         <is>
           <t>Inline vs Inbox visibility</t>
         </is>
       </c>
-      <c r="C16" s="110" t="inlineStr">
+      <c r="C16" s="128" t="inlineStr">
         <is>
           <t>Attended sessions answer prompts inline in the composer (parked server-side, redelivered on reconnect); unattended sessions route the same prompts to the cross-session Inbox queue (coworker/inbox.py).</t>
         </is>
       </c>
+      <c r="D16" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E16" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 13.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="47.75" customHeight="1">
-      <c r="A17" s="108" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>Inbox &amp; Approvals</t>
         </is>
       </c>
-      <c r="B17" s="109" t="inlineStr">
+      <c r="B17" s="124" t="inlineStr">
         <is>
           <t>Ask-user quick replies with free-text escape</t>
         </is>
       </c>
-      <c r="C17" s="109" t="inlineStr">
+      <c r="C17" s="124" t="inlineStr">
         <is>
           <t>Questions can carry quick-reply options plus an always-available typed answer and optional multi-select, mirroring a structured-but-answerable ask (coworker/inbox.py).</t>
         </is>
       </c>
+      <c r="D17" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E17" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 13.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="128" t="inlineStr">
         <is>
           <t>Inbox &amp; Approvals</t>
         </is>
       </c>
-      <c r="B18" s="110" t="inlineStr">
+      <c r="B18" s="128" t="inlineStr">
         <is>
           <t>Multi-inbox routing with Slack/Telegram mirroring</t>
         </is>
       </c>
-      <c r="C18" s="110" t="inlineStr">
+      <c r="C18" s="128" t="inlineStr">
         <is>
           <t>Named inboxes can mirror items to a bound Slack channel or Telegram chat with the item id embedded; an inbound reply is correlated by that id and resolves the item bidirectionally (coworker/inbox_routing.py).</t>
         </is>
       </c>
+      <c r="D18" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E18" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="127" t="inlineStr">
+        <is>
+          <t>Needs messaging connectors (rows 33-39).</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="108" t="inlineStr">
+      <c r="A19" s="124" t="inlineStr">
         <is>
           <t>Inbox &amp; Approvals</t>
         </is>
       </c>
-      <c r="B19" s="109" t="inlineStr">
+      <c r="B19" s="124" t="inlineStr">
         <is>
           <t>Resume reconciliation</t>
         </is>
       </c>
-      <c r="C19" s="109" t="inlineStr">
+      <c r="C19" s="124" t="inlineStr">
         <is>
           <t>When a user resumes attended control, still-pending items are surfaced inline in one place plus a recap of what was answered while away (coworker/inbox.py).</t>
         </is>
       </c>
+      <c r="D19" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E19" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 13.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="128" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="B20" s="110" t="inlineStr">
+      <c r="B20" s="128" t="inlineStr">
         <is>
           <t>Unattended mode</t>
         </is>
       </c>
-      <c r="C20" s="110" t="inlineStr">
+      <c r="C20" s="128" t="inlineStr">
         <is>
           <t>A per-session toggle that routes any inline approval/question to the Inbox and suspends the agent instead of prompting in the composer; turning it on is a one-tap confirm (coworker/unattended.py).</t>
         </is>
       </c>
+      <c r="D20" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E20" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="127" t="inlineStr">
+        <is>
+          <t>Needs an agent runtime with permission modes.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="57.25" customHeight="1">
-      <c r="A21" s="108" t="inlineStr">
+      <c r="A21" s="124" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="B21" s="109" t="inlineStr">
+      <c r="B21" s="124" t="inlineStr">
         <is>
           <t>Permission modes</t>
         </is>
       </c>
-      <c r="C21" s="109" t="inlineStr">
+      <c r="C21" s="124" t="inlineStr">
         <is>
           <t>Sessions run in Discuss (read-only), Plan (read-only + planning contract), Interactive (ask on writes/commands), Auto (full access) or Custom (interactive plus config auto_allow) (coworker/permissions.py).</t>
         </is>
       </c>
+      <c r="D21" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E21" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 20.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="64.25" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="128" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="B22" s="110" t="inlineStr">
+      <c r="B22" s="128" t="inlineStr">
         <is>
           <t>Self-wake (suspend/resume)</t>
         </is>
       </c>
-      <c r="C22" s="110" t="inlineStr">
+      <c r="C22" s="128" t="inlineStr">
         <is>
           <t>Tools let a long-running agent sleep and be re-invoked on a trigger: sleep_for/sleep_until timers, wake_on job completion, and wake_on_event named connector/webhook events, resumed by the shared scheduler tick (coworker/selfwake.py).</t>
         </is>
       </c>
+      <c r="D22" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E22" s="126" t="inlineStr">
+        <is>
+          <t>Scheduler wake</t>
+        </is>
+      </c>
+      <c r="F22" s="127" t="inlineStr">
+        <is>
+          <t>The scheduler already wakes the app to do work on a schedule. Session-level suspend/resume is not built.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="51.75" customHeight="1">
-      <c r="A23" s="108" t="inlineStr">
+      <c r="A23" s="124" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="B23" s="109" t="inlineStr">
+      <c r="B23" s="124" t="inlineStr">
         <is>
           <t>Multi-root workspaces</t>
         </is>
       </c>
-      <c r="C23" s="109" t="inlineStr">
+      <c r="C23" s="124" t="inlineStr">
         <is>
           <t>A session can read/write across multiple added root folders beyond its primary workspace, each marked writable or not (coworker/permissions.py, server routes /v1/sessions/{id}/roots).</t>
         </is>
       </c>
+      <c r="D23" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E23" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="127" t="inlineStr">
+        <is>
+          <t>Dobby is single-workspace; multi-root needs a workspace model.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="46.75" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="128" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="B24" s="110" t="inlineStr">
+      <c r="B24" s="128" t="inlineStr">
         <is>
           <t>Durable, resumable sessions</t>
         </is>
       </c>
-      <c r="C24" s="110" t="inlineStr">
+      <c r="C24" s="128" t="inlineStr">
         <is>
           <t>Conversations persist in a shared SQLite store used by GUI, server and CLI, and can be resumed by id with model and mode restored (coworker/cli.py, conversations).</t>
         </is>
       </c>
+      <c r="D24" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E24" s="126" t="inlineStr">
+        <is>
+          <t>Session table + WizardState</t>
+        </is>
+      </c>
+      <c r="F24" s="127" t="inlineStr">
+        <is>
+          <t>Wizard state is durable and resumable across restarts. Full session resume for all surfaces is not.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="61.75" customHeight="1">
-      <c r="A25" s="108" t="inlineStr">
+      <c r="A25" s="124" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="B25" s="109" t="inlineStr">
+      <c r="B25" s="124" t="inlineStr">
         <is>
           <t>Workspace trust gate</t>
         </is>
       </c>
-      <c r="C25" s="109" t="inlineStr">
+      <c r="C25" s="124" t="inlineStr">
         <is>
           <t>Repository-declared allowed_commands stay advisory until the user trusts that exact canonical workspace path; other permission grants remain global-only (coworker/config.py, workspace_trust.py, routes /v1/workspaces/trust).</t>
         </is>
       </c>
+      <c r="D25" s="131" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="127" t="inlineStr">
+        <is>
+          <t>Dobby never executes workspace code, so there is no trust boundary to gate.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="60.25" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="128" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B26" s="110" t="inlineStr">
+      <c r="B26" s="128" t="inlineStr">
         <is>
           <t>Built-in personas (OpenWorker/Cowork, Code, Chat, Ops)</t>
         </is>
       </c>
-      <c r="C26" s="110" t="inlineStr">
+      <c r="C26" s="128" t="inlineStr">
         <is>
           <t>Ships a default deliverable-producing Cowork persona, a Code persona (files/git/shell), a hidden Chat persona, and a markdown-defined Ops persona for incidents/runbooks (coworker/personas/registry.py, builtin/ops.md).</t>
         </is>
       </c>
+      <c r="D26" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E26" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="127" t="inlineStr">
+        <is>
+          <t>Persona subsystem not started.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="60.25" customHeight="1">
-      <c r="A27" s="108" t="inlineStr">
+      <c r="A27" s="124" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B27" s="109" t="inlineStr">
+      <c r="B27" s="124" t="inlineStr">
         <is>
           <t>Markdown persona manifests</t>
         </is>
       </c>
-      <c r="C27" s="109" t="inlineStr">
+      <c r="C27" s="124" t="inlineStr">
         <is>
           <t>Personas are defined by YAML-frontmatter + markdown files declaring identity, tool capabilities, family, messaging/connectors flags, recommended models, skills, MCP and permission mode (coworker/personas/manifest.py).</t>
         </is>
       </c>
+      <c r="D27" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E27" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 26.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="68.5" customHeight="1">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="128" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B28" s="110" t="inlineStr">
+      <c r="B28" s="128" t="inlineStr">
         <is>
           <t>Third-party persona install with consent</t>
         </is>
       </c>
-      <c r="C28" s="110" t="inlineStr">
+      <c r="C28" s="128" t="inlineStr">
         <is>
           <t>Personas install from a local dir or git URL by snapshotting the manifest into a managed area; each lands disabled/unsurfaced pending a consent summary of tools, risk classes, connectors, MCP and messaging (coworker/personas/loading.py, registry.py).</t>
         </is>
       </c>
+      <c r="D28" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E28" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 26.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="60.75" customHeight="1">
-      <c r="A29" s="108" t="inlineStr">
+      <c r="A29" s="124" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B29" s="109" t="inlineStr">
+      <c r="B29" s="124" t="inlineStr">
         <is>
           <t>Persona lifecycle (enable / surface / default)</t>
         </is>
       </c>
-      <c r="C29" s="109" t="inlineStr">
+      <c r="C29" s="124" t="inlineStr">
         <is>
           <t>Installed personas track enabled/surfaced state and a default; the new-session picker shows only enabled-and-surfaced personas, while live sessions keep resolving even a disabled persona (coworker/personas/registry.py).</t>
         </is>
       </c>
+      <c r="D29" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E29" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 26.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="51.75" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="128" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B30" s="110" t="inlineStr">
+      <c r="B30" s="128" t="inlineStr">
         <is>
           <t>Connection recommendations</t>
         </is>
       </c>
-      <c r="C30" s="110" t="inlineStr">
+      <c r="C30" s="128" t="inlineStr">
         <is>
           <t>A persona can recommend connectors or MCP servers with a reason and core/optional tier, surfaced in the per-session connections drawer (coworker/personas/manifest.py, builtin/ops.md).</t>
         </is>
       </c>
+      <c r="D30" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E30" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="127" t="inlineStr">
+        <is>
+          <t>Depends on connectors.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="59.75" customHeight="1">
-      <c r="A31" s="108" t="inlineStr">
+      <c r="A31" s="124" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B31" s="109" t="inlineStr">
+      <c r="B31" s="124" t="inlineStr">
         <is>
           <t>Vetted tool capability catalog</t>
         </is>
       </c>
-      <c r="C31" s="109" t="inlineStr">
+      <c r="C31" s="124" t="inlineStr">
         <is>
           <t>Personas reference stable capability ids (code_files, files, git, search, shell, todo) that expand into concrete tools only when session context prerequisites (workspace/executor/todo) are met (coworker/catalog.py).</t>
         </is>
       </c>
+      <c r="D31" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E31" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 26.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="128" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="B32" s="110" t="inlineStr">
+      <c r="B32" s="128" t="inlineStr">
         <is>
           <t>Skills with progressive disclosure</t>
         </is>
       </c>
-      <c r="C32" s="110" t="inlineStr">
+      <c r="C32" s="128" t="inlineStr">
         <is>
           <t>Skills are SKILL.md folders (name/description/optional allowed-tools + body); only the catalog is injected at session start and the full body loads on demand via the load_skill tool (coworker/skills/base.py).</t>
         </is>
       </c>
+      <c r="D32" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E32" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="127" t="inlineStr">
+        <is>
+          <t>Overlaps the planned Skills surface (P3).</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="66.5" customHeight="1">
-      <c r="A33" s="108" t="inlineStr">
+      <c r="A33" s="124" t="inlineStr">
         <is>
           <t>Messaging</t>
         </is>
       </c>
-      <c r="B33" s="109" t="inlineStr">
+      <c r="B33" s="124" t="inlineStr">
         <is>
           <t>Work from Slack via @mention</t>
         </is>
       </c>
-      <c r="C33" s="109" t="inlineStr">
+      <c r="C33" s="124" t="inlineStr">
         <is>
           <t>Mentioning @OpenWorker in a channel spawns a desktop coworker session that owns the thread and replies back into it; follow-up tags steer the same session, deduped on the thread target (coworker/mentions.py, server/manager.py _route_mention).</t>
         </is>
       </c>
+      <c r="D33" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E33" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="127" t="inlineStr">
+        <is>
+          <t>Needs Slack app + OAuth.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="68.25" customHeight="1">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="128" t="inlineStr">
         <is>
           <t>Messaging</t>
         </is>
       </c>
-      <c r="B34" s="110" t="inlineStr">
+      <c r="B34" s="128" t="inlineStr">
         <is>
           <t>Pre-approved in-thread replies for mention sessions</t>
         </is>
       </c>
-      <c r="C34" s="110" t="inlineStr">
+      <c r="C34" s="128" t="inlineStr">
         <is>
           <t>A mention-spawned session gets a standing grant to send_message to its exact thread target so the Slack conversation never stalls on an approval nobody in-channel can see; re-derived on every engine rebuild (coworker/mentions.py, server/manager.py).</t>
         </is>
       </c>
+      <c r="D34" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E34" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 33.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="58.5" customHeight="1">
-      <c r="A35" s="108" t="inlineStr">
+      <c r="A35" s="124" t="inlineStr">
         <is>
           <t>Messaging</t>
         </is>
       </c>
-      <c r="B35" s="109" t="inlineStr">
+      <c r="B35" s="124" t="inlineStr">
         <is>
           <t>Channel subscriptions (inbound)</t>
         </is>
       </c>
-      <c r="C35" s="109" t="inlineStr">
+      <c r="C35" s="124" t="inlineStr">
         <is>
           <t>A session can subscribe to a messaging channel to receive its messages as a steer (while busy) or a fresh background turn (when idle), with subscribe/unsubscribe/list/catch-up tools (coworker/subscriptions.py).</t>
         </is>
       </c>
+      <c r="D35" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E35" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 33.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="53.75" customHeight="1">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="A36" s="128" t="inlineStr">
         <is>
           <t>Messaging</t>
         </is>
       </c>
-      <c r="B36" s="110" t="inlineStr">
+      <c r="B36" s="128" t="inlineStr">
         <is>
           <t>Recent-channel buffer / catch-up</t>
         </is>
       </c>
-      <c r="C36" s="110" t="inlineStr">
+      <c r="C36" s="128" t="inlineStr">
         <is>
           <t>A per-channel ring buffer keeps the last N messages seen so a subscribed agent can catch up and the channel picker can suggest already-seen channels (coworker/subscriptions.py ChannelBuffer).</t>
         </is>
       </c>
+      <c r="D36" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E36" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 33.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="68" customHeight="1">
-      <c r="A37" s="108" t="inlineStr">
+      <c r="A37" s="124" t="inlineStr">
         <is>
           <t>Messaging</t>
         </is>
       </c>
-      <c r="B37" s="109" t="inlineStr">
+      <c r="B37" s="124" t="inlineStr">
         <is>
           <t>Telegram + Slack relay transport</t>
         </is>
       </c>
-      <c r="C37" s="109" t="inlineStr">
+      <c r="C37" s="124" t="inlineStr">
         <is>
           <t>Inbox items and replies flow over Slack and Telegram via a managed relay WebSocket for inbound events; connectors/mobile are just transports of the same Inbox items (coworker/inbox_routing.py, config cloud_relay_ws_url, connectors/relay_client.py).</t>
         </is>
       </c>
+      <c r="D37" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E37" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 33.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="73" customHeight="1">
-      <c r="A38" s="37" t="inlineStr">
+      <c r="A38" s="128" t="inlineStr">
         <is>
           <t>Messaging</t>
         </is>
       </c>
-      <c r="B38" s="110" t="inlineStr">
+      <c r="B38" s="128" t="inlineStr">
         <is>
           <t>DM routing + unrouted dead-letter store</t>
         </is>
       </c>
-      <c r="C38" s="110" t="inlineStr">
+      <c r="C38" s="128" t="inlineStr">
         <is>
           <t>Direct messages route to a designated session; inbound messages with nowhere to go and failed background turns are recorded durably in an unrouted dead-letter log for visibility rather than vanishing (coworker/unrouted.py, routes /v1/messaging/dm-route, /v1/unrouted).</t>
         </is>
       </c>
+      <c r="D38" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E38" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 33.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="75.75" customHeight="1">
-      <c r="A39" s="108" t="inlineStr">
+      <c r="A39" s="124" t="inlineStr">
         <is>
           <t>Messaging</t>
         </is>
       </c>
-      <c r="B39" s="109" t="inlineStr">
+      <c r="B39" s="124" t="inlineStr">
         <is>
           <t>25+ / 40 connectors</t>
         </is>
       </c>
-      <c r="C39" s="109" t="inlineStr">
+      <c r="C39" s="124" t="inlineStr">
         <is>
           <t>Integrations include GitHub, Slack, Jira, Notion, Linear, HubSpot, Outlook, monday.com, Gmail, Google Calendar/Drive, Telegram, WhatsApp, Discord, Stripe, Salesforce, Datadog and more (40 descriptors) plus terminal and local files (coworker/connectors/descriptors.py, README.md).</t>
         </is>
       </c>
+      <c r="D39" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E39" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="127" t="inlineStr">
+        <is>
+          <t>Large connector programme; scheduled P5 with the Marketplace.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="74.5" customHeight="1">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="A40" s="128" t="inlineStr">
         <is>
           <t>Model Access</t>
         </is>
       </c>
-      <c r="B40" s="110" t="inlineStr">
+      <c r="B40" s="128" t="inlineStr">
         <is>
           <t>Bring-your-own-model, any provider</t>
         </is>
       </c>
-      <c r="C40" s="110" t="inlineStr">
+      <c r="C40" s="128" t="inlineStr">
         <is>
           <t>Users paste their own key for OpenAI, Anthropic, Google Gemini, Inkling, GLM, DeepSeek, Kimi, Qwen, MiniMax, Mistral, Grok, plus open-weight via Together/Fireworks and fully local via Ollama; a curated list marks tool-calling-verified models (README.md, coworker/providers).</t>
         </is>
       </c>
+      <c r="D40" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E40" s="126" t="inlineStr">
+        <is>
+          <t>Settings · Ollama host</t>
+        </is>
+      </c>
+      <c r="F40" s="127" t="inlineStr">
+        <is>
+          <t>Any OpenAI-compatible host reachable at the configured URL works; provider abstraction beyond Ollama is not built.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="62.75" customHeight="1">
-      <c r="A41" s="108" t="inlineStr">
+      <c r="A41" s="124" t="inlineStr">
         <is>
           <t>Model Access</t>
         </is>
       </c>
-      <c r="B41" s="109" t="inlineStr">
+      <c r="B41" s="124" t="inlineStr">
         <is>
           <t>Per-session model switching</t>
         </is>
       </c>
-      <c r="C41" s="109" t="inlineStr">
+      <c r="C41" s="124" t="inlineStr">
         <is>
           <t>The default model is configurable and can be overridden per session in the UI/CLI; custom model strings can be added at the user's own risk (docs/config.example.toml, routes /v1/settings/default-model, /v1/settings/models/add).</t>
         </is>
       </c>
+      <c r="D41" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E41" s="126" t="inlineStr">
+        <is>
+          <t>Settings · active model</t>
+        </is>
+      </c>
+      <c r="F41" s="127" t="inlineStr">
+        <is>
+          <t>Model switches globally and takes effect on the next run. Not per-session.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="50.5" customHeight="1">
-      <c r="A42" s="37" t="inlineStr">
+      <c r="A42" s="128" t="inlineStr">
         <is>
           <t>Model Access</t>
         </is>
       </c>
-      <c r="B42" s="110" t="inlineStr">
+      <c r="B42" s="128" t="inlineStr">
         <is>
           <t>Model capability-aware routing</t>
         </is>
       </c>
-      <c r="C42" s="110" t="inlineStr">
+      <c r="C42" s="128" t="inlineStr">
         <is>
           <t>Providers declare capabilities (e.g. native PDF, vision); the engine adapts message content to the active model at send time (coworker/providers/capabilities.py, pdf_support.py).</t>
         </is>
       </c>
+      <c r="D42" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E42" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="127" t="inlineStr">
+        <is>
+          <t>Needs a capability registry per model.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="108" t="inlineStr">
+      <c r="A43" s="124" t="inlineStr">
         <is>
           <t>Deliverables</t>
         </is>
       </c>
-      <c r="B43" s="109" t="inlineStr">
+      <c r="B43" s="124" t="inlineStr">
         <is>
           <t>Finished-work deliverables</t>
         </is>
       </c>
-      <c r="C43" s="109" t="inlineStr">
+      <c r="C43" s="124" t="inlineStr">
         <is>
           <t>OpenWorker produces real files — documents, spreadsheets, reports, web pages — that land as artifacts you can open and share, not just chat (README.md).</t>
         </is>
       </c>
+      <c r="D43" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E43" s="126" t="inlineStr">
+        <is>
+          <t>Documents · export</t>
+        </is>
+      </c>
+      <c r="F43" s="127" t="inlineStr">
+        <is>
+          <t>Generated documents are browsable and exportable (md/json/mermaid/png/svg). No 'deliverable' object distinct from a document.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="51.5" customHeight="1">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="A44" s="128" t="inlineStr">
         <is>
           <t>Deliverables</t>
         </is>
       </c>
-      <c r="B44" s="110" t="inlineStr">
+      <c r="B44" s="128" t="inlineStr">
         <is>
           <t>Session artifacts listing and reveal</t>
         </is>
       </c>
-      <c r="C44" s="110" t="inlineStr">
+      <c r="C44" s="128" t="inlineStr">
         <is>
           <t>A session exposes its produced artifact files for listing, reading and revealing in the OS file manager (server routes /v1/sessions/{id}/artifacts, artifacts/read, artifacts/reveal).</t>
         </is>
       </c>
+      <c r="D44" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E44" s="126" t="inlineStr">
+        <is>
+          <t>Documents page</t>
+        </is>
+      </c>
+      <c r="F44" s="127" t="inlineStr">
+        <is>
+          <t>Artifacts are listed and readable in-app. No OS-level reveal-in-Finder.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="52" customHeight="1">
-      <c r="A45" s="108" t="inlineStr">
+      <c r="A45" s="124" t="inlineStr">
         <is>
           <t>Deliverables</t>
         </is>
       </c>
-      <c r="B45" s="109" t="inlineStr">
+      <c r="B45" s="124" t="inlineStr">
         <is>
           <t>Progress panel via todo list</t>
         </is>
       </c>
-      <c r="C45" s="109" t="inlineStr">
+      <c r="C45" s="124" t="inlineStr">
         <is>
           <t>A todo_write task list drives the visible Progress panel the user watches during a run, with exactly one item in-progress at a time (coworker/catalog.py todo, personas/builtin/ops.md).</t>
         </is>
       </c>
+      <c r="D45" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E45" s="126" t="inlineStr">
+        <is>
+          <t>Live run progress</t>
+        </is>
+      </c>
+      <c r="F45" s="127" t="inlineStr">
+        <is>
+          <t>Step-by-step progress streams over SSE into Logs &amp; Traces and the generation pages. Not a todo-list panel.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="60.25" customHeight="1">
-      <c r="A46" s="37" t="inlineStr">
+      <c r="A46" s="128" t="inlineStr">
         <is>
           <t>Deliverables</t>
         </is>
       </c>
-      <c r="B46" s="110" t="inlineStr">
+      <c r="B46" s="128" t="inlineStr">
         <is>
           <t>Attachments (images, PDFs, text)</t>
         </is>
       </c>
-      <c r="C46" s="110" t="inlineStr">
+      <c r="C46" s="128" t="inlineStr">
         <is>
           <t>User turns accept image, PDF and text attachments (up to 8) built into provider content parts, with per-type size caps; invalid/oversized attachments are skipped rather than failing the turn (coworker/attachments.py).</t>
         </is>
       </c>
+      <c r="D46" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E46" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="127" t="inlineStr">
+        <is>
+          <t>Needs an attachment store and multimodal input.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="66" customHeight="1">
-      <c r="A47" s="108" t="inlineStr">
+      <c r="A47" s="124" t="inlineStr">
         <is>
           <t>Deliverables</t>
         </is>
       </c>
-      <c r="B47" s="109" t="inlineStr">
+      <c r="B47" s="124" t="inlineStr">
         <is>
           <t>Local PDF handling with fallback modes</t>
         </is>
       </c>
-      <c r="C47" s="109" t="inlineStr">
+      <c r="C47" s="124" t="inlineStr">
         <is>
           <t>For models without native PDF support, PDFs are handled locally — extract embedded text (pypdf) or rasterize pages to PNGs (pypdfium2) — entirely on-device, cached by content hash, user-selectable in Token savings (coworker/pdf_support.py).</t>
         </is>
       </c>
+      <c r="D47" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E47" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="127" t="inlineStr">
+        <is>
+          <t>Depends on row 46.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="50.5" customHeight="1">
-      <c r="A48" s="37" t="inlineStr">
+      <c r="A48" s="128" t="inlineStr">
         <is>
           <t>Voice/STT</t>
         </is>
       </c>
-      <c r="B48" s="110" t="inlineStr">
+      <c r="B48" s="128" t="inlineStr">
         <is>
           <t>Local offline speech-to-text</t>
         </is>
       </c>
-      <c r="C48" s="110" t="inlineStr">
+      <c r="C48" s="128" t="inlineStr">
         <is>
           <t>A Rust STT sidecar (whisper-rs) captures the mic and transcribes voice input fully offline, provisioning a ~142MB ggml-base.en Whisper model verified by SHA-256 (stt/src/lib.rs).</t>
         </is>
       </c>
+      <c r="D48" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E48" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="127" t="inlineStr">
+        <is>
+          <t>Whisper sidecar; already scheduled as P2 Transcribe.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="44.25" customHeight="1">
-      <c r="A49" s="108" t="inlineStr">
+      <c r="A49" s="124" t="inlineStr">
         <is>
           <t>Model Access</t>
         </is>
       </c>
-      <c r="B49" s="109" t="inlineStr">
+      <c r="B49" s="124" t="inlineStr">
         <is>
           <t>Web search with pluggable providers</t>
         </is>
       </c>
-      <c r="C49" s="109" t="inlineStr">
+      <c r="C49" s="124" t="inlineStr">
         <is>
           <t>A built-in web-search tool defaults to keyless DuckDuckGo and can use Tavily or Brave with a key (coworker/web/providers.py, config web_search_provider).</t>
         </is>
       </c>
+      <c r="D49" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E49" s="126" t="inlineStr">
+        <is>
+          <t>Research · search providers</t>
+        </is>
+      </c>
+      <c r="F49" s="127" t="inlineStr">
+        <is>
+          <t>wigolo (local, keyless), SearXNG, Tavily, Brave. Verified live: 72 real sources in one brief.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="55.25" customHeight="1">
-      <c r="A50" s="37" t="inlineStr">
+      <c r="A50" s="128" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="B50" s="110" t="inlineStr">
+      <c r="B50" s="128" t="inlineStr">
         <is>
           <t>Local-first architecture</t>
         </is>
       </c>
-      <c r="C50" s="110" t="inlineStr">
+      <c r="C50" s="128" t="inlineStr">
         <is>
           <t>The agent loop, conversations, connector tokens and model keys all live on the user's machine in a local secret store; the app is fully usable signed out (README.md, coworker/secrets.py, cloud.py).</t>
         </is>
       </c>
+      <c r="D50" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E50" s="126" t="inlineStr">
+        <is>
+          <t>Whole app</t>
+        </is>
+      </c>
+      <c r="F50" s="127" t="inlineStr">
+        <is>
+          <t>SQLite + local Ollama. Remote providers are opt-in and labelled 'leaves device'.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="73" customHeight="1">
-      <c r="A51" s="108" t="inlineStr">
+      <c r="A51" s="124" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="B51" s="109" t="inlineStr">
+      <c r="B51" s="124" t="inlineStr">
         <is>
           <t>Cloud OAuth broker (optional one-click connect)</t>
         </is>
       </c>
-      <c r="C51" s="109" t="inlineStr">
+      <c r="C51" s="124" t="inlineStr">
         <is>
           <t>An optional OpenWorker Cloud sign-in (Auth0 Authorization Code + PKCE) unlocks one-click managed OAuth for connectors via a broker; connector tokens are written locally and never touch cloud storage, and manual token paste always remains available (coworker/cloud.py).</t>
         </is>
       </c>
+      <c r="D51" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E51" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="127" t="inlineStr">
+        <is>
+          <t>Deliberately deferred: an OAuth broker conflicts with local-first unless optional.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="45.5" customHeight="1">
-      <c r="A52" s="37" t="inlineStr">
+      <c r="A52" s="128" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="B52" s="110" t="inlineStr">
+      <c r="B52" s="128" t="inlineStr">
         <is>
           <t>Local audit log</t>
         </is>
       </c>
-      <c r="C52" s="110" t="inlineStr">
+      <c r="C52" s="128" t="inlineStr">
         <is>
           <t>Connector and tool actions are recorded in a durable local SQLite audit log with secret keys and message bodies redacted (coworker/audit.py, route /v1/audit).</t>
         </is>
       </c>
+      <c r="D52" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E52" s="126" t="inlineStr">
+        <is>
+          <t>src/audit/trail.py</t>
+        </is>
+      </c>
+      <c r="F52" s="127" t="inlineStr">
+        <is>
+          <t>Revived — the module existed with zero callers. Automations now write create/enable/disable/delete/run entries.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="55.25" customHeight="1">
-      <c r="A53" s="108" t="inlineStr">
+      <c r="A53" s="124" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="B53" s="109" t="inlineStr">
+      <c r="B53" s="124" t="inlineStr">
         <is>
           <t>Empty default command allowlist</t>
         </is>
       </c>
-      <c r="C53" s="109" t="inlineStr">
+      <c r="C53" s="124" t="inlineStr">
         <is>
           <t>No commands auto-run without approval by default; the built-in allowed-commands list is intentionally empty and users must opt into command prefixes in their own global config (coworker/config.py).</t>
         </is>
       </c>
+      <c r="D53" s="131" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E53" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="127" t="inlineStr">
+        <is>
+          <t>Dobby executes no shell commands, so the allowlist is empty by construction. Revisit with Terminal (P2).</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="69.5" customHeight="1">
-      <c r="A54" s="37" t="inlineStr">
+      <c r="A54" s="128" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="B54" s="110" t="inlineStr">
+      <c r="B54" s="128" t="inlineStr">
         <is>
           <t>Untrusted-content handling</t>
         </is>
       </c>
-      <c r="C54" s="110" t="inlineStr">
+      <c r="C54" s="128" t="inlineStr">
         <is>
           <t>Personas are instructed to treat content from tools, logs, the web, files and incoming messages as untrusted data rather than instructions, and to avoid destructive actions without explicit approval (coworker/personas/builtin/ops.md, agents/myhelper.py).</t>
         </is>
       </c>
+      <c r="D54" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E54" s="126" t="inlineStr">
+        <is>
+          <t>Research grounding</t>
+        </is>
+      </c>
+      <c r="F54" s="127" t="inlineStr">
+        <is>
+          <t>Retrieved web content is treated as data, never instructions; unsourced claims are tagged. No formal untrusted-content sandbox.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="65.5" customHeight="1">
-      <c r="A55" s="108" t="inlineStr">
+      <c r="A55" s="124" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="B55" s="109" t="inlineStr">
+      <c r="B55" s="124" t="inlineStr">
         <is>
           <t>Local FastAPI agent server + multiple surfaces</t>
         </is>
       </c>
-      <c r="C55" s="109" t="inlineStr">
+      <c r="C55" s="124" t="inlineStr">
         <is>
           <t>A local Python FastAPI server (openworker-server) exposes /v1 REST + WebSocket endpoints driving four surfaces: the Tauri desktop GUI, a web UI, a terminal TUI, and a CLI (coworker/server/app.py, run.py, tui/app.py, cli.py, surfaces/gui).</t>
         </is>
       </c>
+      <c r="D55" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E55" s="126" t="inlineStr">
+        <is>
+          <t>src/main.py</t>
+        </is>
+      </c>
+      <c r="F55" s="127" t="inlineStr">
+        <is>
+          <t>FastAPI server, Tauri desktop shell, and browser all hit the same API.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="59" customHeight="1">
-      <c r="A56" s="37" t="inlineStr">
+      <c r="A56" s="128" t="inlineStr">
         <is>
           <t>Privacy</t>
         </is>
       </c>
-      <c r="B56" s="110" t="inlineStr">
+      <c r="B56" s="128" t="inlineStr">
         <is>
           <t>Per-launch loopback auth token</t>
         </is>
       </c>
-      <c r="C56" s="110" t="inlineStr">
+      <c r="C56" s="128" t="inlineStr">
         <is>
           <t>The standalone server writes a per-launch, user-only token file and requires it in the X-OpenWorker-Token header; the desktop app uses an in-memory token never written to disk (README.md, coworker/server/run.py).</t>
         </is>
       </c>
+      <c r="D56" s="130" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E56" s="126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="127" t="inlineStr">
+        <is>
+          <t>Loopback token for the local API. Small and worth doing before any packaged release.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="45.5" customHeight="1">
-      <c r="A57" s="108" t="inlineStr">
+      <c r="A57" s="124" t="inlineStr">
         <is>
           <t>Model Access</t>
         </is>
       </c>
-      <c r="B57" s="109" t="inlineStr">
+      <c r="B57" s="124" t="inlineStr">
         <is>
           <t>MCP server integration</t>
         </is>
       </c>
-      <c r="C57" s="109" t="inlineStr">
+      <c r="C57" s="124" t="inlineStr">
         <is>
           <t>Any Model Context Protocol server plugs in with per-tool control and OAuth support, managed via dedicated endpoints (README.md, coworker/mcp, routes /v1/mcp).</t>
+        </is>
+      </c>
+      <c r="D57" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E57" s="126" t="inlineStr">
+        <is>
+          <t>wigolo (MCP server)</t>
+        </is>
+      </c>
+      <c r="F57" s="127" t="inlineStr">
+        <is>
+          <t>Dobby consumes wigolo, which is an MCP server, over its REST surface. Dobby is not yet a general MCP client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="132" t="inlineStr">
+        <is>
+          <t>Completion summary</t>
+        </is>
+      </c>
+      <c r="C59" s="133" t="inlineStr">
+        <is>
+          <t>Counted from column D — edit a status and these update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B60" s="126">
+        <f>COUNTIF(D3:D57,A60)</f>
+        <v/>
+      </c>
+      <c r="C60" s="135">
+        <f>IFERROR(B60/COUNTA(D3:D57),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="136" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B61" s="126">
+        <f>COUNTIF(D3:D57,A61)</f>
+        <v/>
+      </c>
+      <c r="C61" s="135">
+        <f>IFERROR(B61/COUNTA(D3:D57),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="137" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="B62" s="126">
+        <f>COUNTIF(D3:D57,A62)</f>
+        <v/>
+      </c>
+      <c r="C62" s="135">
+        <f>IFERROR(B62/COUNTA(D3:D57),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B63" s="126">
+        <f>COUNTIF(D3:D57,A63)</f>
+        <v/>
+      </c>
+      <c r="C63" s="135">
+        <f>IFERROR(B63/COUNTA(D3:D57),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="139" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B64" s="139">
+        <f>COUNTA(D3:D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="133" t="inlineStr">
+        <is>
+          <t>Status as of 2026-07-26. 'Done' means built and verified running, not merely scaffolded.</t>
         </is>
       </c>
     </row>
@@ -12113,6 +14563,381 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="140" t="inlineStr">
+        <is>
+          <t>Next tasks, ordered by value per unit of effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="133" t="inlineStr">
+        <is>
+          <t>Derived from the OW · Features tab: every row still Planned or Partial, grouped into shippable units and sequenced by what unblocks the most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="141" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="141" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C4" s="141" t="inlineStr">
+        <is>
+          <t>Unblocks / OW rows</t>
+        </is>
+      </c>
+      <c r="D4" s="141" t="inlineStr">
+        <is>
+          <t>Why now</t>
+        </is>
+      </c>
+      <c r="E4" s="141" t="inlineStr">
+        <is>
+          <t>Est.</t>
+        </is>
+      </c>
+      <c r="F4" s="141" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="142" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="142" t="inlineStr">
+        <is>
+          <t>Approvals &amp; Inbox</t>
+        </is>
+      </c>
+      <c r="C5" s="127" t="inlineStr">
+        <is>
+          <t>OW 8, 9, 13-17, 19</t>
+        </is>
+      </c>
+      <c r="D5" s="127" t="inlineStr">
+        <is>
+          <t>The single biggest blocker: eight OW features depend on it, and nothing that acts on your behalf can ship safely without it. Automations already run unattended — today they simply have nothing dangerous to do.</t>
+        </is>
+      </c>
+      <c r="E5" s="142" t="inlineStr">
+        <is>
+          <t>2 wks</t>
+        </is>
+      </c>
+      <c r="F5" s="143" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="142" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="142" t="inlineStr">
+        <is>
+          <t>Per-launch loopback auth token</t>
+        </is>
+      </c>
+      <c r="C6" s="127" t="inlineStr">
+        <is>
+          <t>OW 56</t>
+        </is>
+      </c>
+      <c r="D6" s="127" t="inlineStr">
+        <is>
+          <t>The local API is unauthenticated on 127.0.0.1. Small, self-contained, and should land before any packaged release.</t>
+        </is>
+      </c>
+      <c r="E6" s="142" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="F6" s="143" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="142" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="142" t="inlineStr">
+        <is>
+          <t>Terminal (sandboxed, approval-gated)</t>
+        </is>
+      </c>
+      <c r="C7" s="127" t="inlineStr">
+        <is>
+          <t>OW 14, 53</t>
+        </is>
+      </c>
+      <c r="D7" s="127" t="inlineStr">
+        <is>
+          <t>The main reason to leave Dobby today. Also makes the empty command allowlist and approval-gated shell real rather than vacuous.</t>
+        </is>
+      </c>
+      <c r="E7" s="142" t="inlineStr">
+        <is>
+          <t>2 wks</t>
+        </is>
+      </c>
+      <c r="F7" s="144" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="142" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="142" t="inlineStr">
+        <is>
+          <t>MCP client</t>
+        </is>
+      </c>
+      <c r="C8" s="127" t="inlineStr">
+        <is>
+          <t>OW 57, 31</t>
+        </is>
+      </c>
+      <c r="D8" s="127" t="inlineStr">
+        <is>
+          <t>Dobby already consumes one MCP server (wigolo) over REST. Becoming a general MCP client turns every existing MCP server into a Dobby capability — the highest leverage item on this list.</t>
+        </is>
+      </c>
+      <c r="E8" s="142" t="inlineStr">
+        <is>
+          <t>1.5 wks</t>
+        </is>
+      </c>
+      <c r="F8" s="144" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="142" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="142" t="inlineStr">
+        <is>
+          <t>Attachments + local PDF handling</t>
+        </is>
+      </c>
+      <c r="C9" s="127" t="inlineStr">
+        <is>
+          <t>OW 46, 47</t>
+        </is>
+      </c>
+      <c r="D9" s="127" t="inlineStr">
+        <is>
+          <t>Research and generation both want source documents as input. Unlocks a large class of real work.</t>
+        </is>
+      </c>
+      <c r="E9" s="142" t="inlineStr">
+        <is>
+          <t>1 wk</t>
+        </is>
+      </c>
+      <c r="F9" s="144" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="142" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="142" t="inlineStr">
+        <is>
+          <t>Provider abstraction beyond Ollama</t>
+        </is>
+      </c>
+      <c r="C10" s="127" t="inlineStr">
+        <is>
+          <t>OW 40, 41, 42</t>
+        </is>
+      </c>
+      <c r="D10" s="127" t="inlineStr">
+        <is>
+          <t>Upgrades three Partial rows to Done. Per-session model choice and capability-aware routing follow from one abstraction.</t>
+        </is>
+      </c>
+      <c r="E10" s="142" t="inlineStr">
+        <is>
+          <t>1 wk</t>
+        </is>
+      </c>
+      <c r="F10" s="145" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="142" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="142" t="inlineStr">
+        <is>
+          <t>Session durability + permission modes</t>
+        </is>
+      </c>
+      <c r="C11" s="127" t="inlineStr">
+        <is>
+          <t>OW 20, 21, 22, 24</t>
+        </is>
+      </c>
+      <c r="D11" s="127" t="inlineStr">
+        <is>
+          <t>Four rows, one subsystem. Needed before unattended mode can be trusted.</t>
+        </is>
+      </c>
+      <c r="E11" s="142" t="inlineStr">
+        <is>
+          <t>2 wks</t>
+        </is>
+      </c>
+      <c r="F11" s="145" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="142" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="142" t="inlineStr">
+        <is>
+          <t>Audio transcription (Whisper sidecar)</t>
+        </is>
+      </c>
+      <c r="C12" s="127" t="inlineStr">
+        <is>
+          <t>OW 48</t>
+        </is>
+      </c>
+      <c r="D12" s="127" t="inlineStr">
+        <is>
+          <t>Already scheduled as P2 Transcribe; unlocks YouTube→Notes behind it.</t>
+        </is>
+      </c>
+      <c r="E12" s="142" t="inlineStr">
+        <is>
+          <t>2 wks</t>
+        </is>
+      </c>
+      <c r="F12" s="145" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="142" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="142" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="C13" s="127" t="inlineStr">
+        <is>
+          <t>OW 26-32</t>
+        </is>
+      </c>
+      <c r="D13" s="127" t="inlineStr">
+        <is>
+          <t>Seven rows, but nothing else depends on them. Worth doing after the app has more capabilities for a persona to select between.</t>
+        </is>
+      </c>
+      <c r="E13" s="142" t="inlineStr">
+        <is>
+          <t>3 wks</t>
+        </is>
+      </c>
+      <c r="F13" s="142" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="142" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="142" t="inlineStr">
+        <is>
+          <t>Messaging connectors (Slack, Telegram)</t>
+        </is>
+      </c>
+      <c r="C14" s="127" t="inlineStr">
+        <is>
+          <t>OW 18, 33-39</t>
+        </is>
+      </c>
+      <c r="D14" s="127" t="inlineStr">
+        <is>
+          <t>Largest cluster and the most external dependency (OAuth, app review). Deliberately last: it multiplies surface area without deepening the core.</t>
+        </is>
+      </c>
+      <c r="E14" s="142" t="inlineStr">
+        <is>
+          <t>4 wks</t>
+        </is>
+      </c>
+      <c r="F14" s="142" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="133" t="inlineStr">
+        <is>
+          <t>Sequencing rationale: Approvals first because it gates the most; MCP client early because it multiplies capability for the least work; connectors last because they add surface area rather than depth.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13678,7 +16503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14958,7 +17783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15240,1316 +18065,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="107" t="inlineStr">
-        <is>
-          <t>Configuration surface (coworker/config.py + docs/config.example.toml). Local, file-based, no cloud config.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B2" s="29" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="C2" s="29" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D2" s="29" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E2" s="29" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F2" s="29" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32.75" customHeight="1">
-      <c r="A3" s="108" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B3" s="112" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C3" s="112" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="109" t="inlineStr">
-        <is>
-          <t>gpt-5.6-sol</t>
-        </is>
-      </c>
-      <c r="E3" s="109" t="inlineStr">
-        <is>
-          <t>Default model id used for new sessions; overridable per session in the UI/CLI. docs example uses 'gpt-5.5'.</t>
-        </is>
-      </c>
-      <c r="F3" s="109" t="inlineStr">
-        <is>
-          <t>coworker/config.py; docs/config.example.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24.75" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
-        <is>
-          <t>mode</t>
-        </is>
-      </c>
-      <c r="B4" s="114" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C4" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D4" s="110" t="inlineStr">
-        <is>
-          <t>interactive</t>
-        </is>
-      </c>
-      <c r="E4" s="110" t="inlineStr">
-        <is>
-          <t>Default permission mode: plan | interactive | auto | custom (also discuss).</t>
-        </is>
-      </c>
-      <c r="F4" s="110" t="inlineStr">
-        <is>
-          <t>coworker/config.py; docs/config.example.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="108" t="inlineStr">
-        <is>
-          <t>max_iterations</t>
-        </is>
-      </c>
-      <c r="B5" s="112" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C5" s="112" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D5" s="109" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="E5" s="109" t="inlineStr">
-        <is>
-          <t>Max model&lt;-&gt;tool iterations per turn before stopping. docs example shows 12.</t>
-        </is>
-      </c>
-      <c r="F5" s="109" t="inlineStr">
-        <is>
-          <t>coworker/config.py; docs/config.example.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="49.75" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>allowed_commands</t>
-        </is>
-      </c>
-      <c r="B6" s="114" t="inlineStr">
-        <is>
-          <t>global-only (workspace only after trust)</t>
-        </is>
-      </c>
-      <c r="C6" s="114" t="inlineStr">
-        <is>
-          <t>list[string]</t>
-        </is>
-      </c>
-      <c r="D6" s="110" t="inlineStr">
-        <is>
-          <t>[] (empty)</t>
-        </is>
-      </c>
-      <c r="E6" s="110" t="inlineStr">
-        <is>
-          <t>Command prefixes that auto-run without an approval prompt (prefix match). Built-in default is empty; workspace-declared entries apply only after the workspace path is trusted.</t>
-        </is>
-      </c>
-      <c r="F6" s="110" t="inlineStr">
-        <is>
-          <t>coworker/config.py; docs/config.example.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="43.5" customHeight="1">
-      <c r="A7" s="108" t="inlineStr">
-        <is>
-          <t>auto_allow</t>
-        </is>
-      </c>
-      <c r="B7" s="112" t="inlineStr">
-        <is>
-          <t>global-only</t>
-        </is>
-      </c>
-      <c r="C7" s="112" t="inlineStr">
-        <is>
-          <t>list[string]</t>
-        </is>
-      </c>
-      <c r="D7" s="109" t="inlineStr">
-        <is>
-          <t>[] (empty)</t>
-        </is>
-      </c>
-      <c r="E7" s="109" t="inlineStr">
-        <is>
-          <t>In 'custom' permission mode, tools auto-approved while everything else still asks (e.g. write_file, replace_in_file, apply_patch, apply_unified_diff).</t>
-        </is>
-      </c>
-      <c r="F7" s="109" t="inlineStr">
-        <is>
-          <t>coworker/config.py; docs/config.example.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20.5" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="B8" s="114" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C8" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D8" s="110" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="E8" s="110" t="inlineStr">
-        <is>
-          <t>Bind address for the openworker-server local agent server.</t>
-        </is>
-      </c>
-      <c r="F8" s="110" t="inlineStr">
-        <is>
-          <t>coworker/config.py; docs/config.example.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="108" t="inlineStr">
-        <is>
-          <t>port</t>
-        </is>
-      </c>
-      <c r="B9" s="112" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C9" s="112" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D9" s="109" t="inlineStr">
-        <is>
-          <t>8765</t>
-        </is>
-      </c>
-      <c r="E9" s="109" t="inlineStr">
-        <is>
-          <t>Bind port for the openworker-server local agent server.</t>
-        </is>
-      </c>
-      <c r="F9" s="109" t="inlineStr">
-        <is>
-          <t>coworker/config.py; docs/config.example.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="29.5" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>web_search_provider</t>
-        </is>
-      </c>
-      <c r="B10" s="114" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C10" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D10" s="110" t="inlineStr">
-        <is>
-          <t>duckduckgo</t>
-        </is>
-      </c>
-      <c r="E10" s="110" t="inlineStr">
-        <is>
-          <t>Web search provider: 'duckduckgo' (keyless default) | 'tavily' | 'brave' (require an API key).</t>
-        </is>
-      </c>
-      <c r="F10" s="110" t="inlineStr">
-        <is>
-          <t>coworker/config.py; coworker/web/providers.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="35.5" customHeight="1">
-      <c r="A11" s="108" t="inlineStr">
-        <is>
-          <t>cloud_base_url</t>
-        </is>
-      </c>
-      <c r="B11" s="112" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C11" s="112" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D11" s="109" t="inlineStr">
-        <is>
-          <t>https://api.openworker.com</t>
-        </is>
-      </c>
-      <c r="E11" s="109" t="inlineStr">
-        <is>
-          <t>OpenWorker Cloud API base URL for sign-in and managed connectors; point at dev/staging/BYO-VPC instances via override.</t>
-        </is>
-      </c>
-      <c r="F11" s="109" t="inlineStr">
-        <is>
-          <t>coworker/config.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>cloud_auth_domain</t>
-        </is>
-      </c>
-      <c r="B12" s="114" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C12" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D12" s="110" t="inlineStr">
-        <is>
-          <t>opencoworker.us.auth0.com</t>
-        </is>
-      </c>
-      <c r="E12" s="110" t="inlineStr">
-        <is>
-          <t>Auth0 tenant domain used for the sign-in Authorization Code + PKCE flow.</t>
-        </is>
-      </c>
-      <c r="F12" s="110" t="inlineStr">
-        <is>
-          <t>coworker/config.py; coworker/cloud.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="108" t="inlineStr">
-        <is>
-          <t>cloud_client_id</t>
-        </is>
-      </c>
-      <c r="B13" s="112" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C13" s="112" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D13" s="109" t="inlineStr">
-        <is>
-          <t>g1l4Q1lhYWmyS03qPSf4KEJGrgq02Qam</t>
-        </is>
-      </c>
-      <c r="E13" s="109" t="inlineStr">
-        <is>
-          <t>Auth0 OAuth client id for the cloud sign-in flow.</t>
-        </is>
-      </c>
-      <c r="F13" s="109" t="inlineStr">
-        <is>
-          <t>coworker/config.py; coworker/cloud.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>cloud_audience</t>
-        </is>
-      </c>
-      <c r="B14" s="114" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C14" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D14" s="110" t="inlineStr">
-        <is>
-          <t>https://api.opencoworker.app</t>
-        </is>
-      </c>
-      <c r="E14" s="110" t="inlineStr">
-        <is>
-          <t>Auth0 API audience; must match the registered API identifier (kept at the legacy value on purpose).</t>
-        </is>
-      </c>
-      <c r="F14" s="110" t="inlineStr">
-        <is>
-          <t>coworker/config.py; coworker/cloud.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.25" customHeight="1">
-      <c r="A15" s="108" t="inlineStr">
-        <is>
-          <t>cloud_relay_ws_url</t>
-        </is>
-      </c>
-      <c r="B15" s="112" t="inlineStr">
-        <is>
-          <t>global/workspace</t>
-        </is>
-      </c>
-      <c r="C15" s="112" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D15" s="109" t="inlineStr">
-        <is>
-          <t>wss://l4z1paxb83.execute-api.us-east-1.amazonaws.com/ocw-connect</t>
-        </is>
-      </c>
-      <c r="E15" s="109" t="inlineStr">
-        <is>
-          <t>Managed relay WebSocket endpoint for Slack/GitHub inbound events. Empty override disables the relay (manual Socket Mode still works).</t>
-        </is>
-      </c>
-      <c r="F15" s="109" t="inlineStr">
-        <is>
-          <t>coworker/config.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.25" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>(scheduler) tick_seconds</t>
-        </is>
-      </c>
-      <c r="B16" s="114" t="inlineStr">
-        <is>
-          <t>automation runtime</t>
-        </is>
-      </c>
-      <c r="C16" s="114" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D16" s="110" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="E16" s="110" t="inlineStr">
-        <is>
-          <t>How often the automation scheduler polls for due tasks and self-wake resumptions.</t>
-        </is>
-      </c>
-      <c r="F16" s="110" t="inlineStr">
-        <is>
-          <t>coworker/automation/scheduler.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="108" t="inlineStr">
-        <is>
-          <t>schedule.kind</t>
-        </is>
-      </c>
-      <c r="B17" s="112" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C17" s="112" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D17" s="109" t="inlineStr">
-        <is>
-          <t>cron</t>
-        </is>
-      </c>
-      <c r="E17" s="109" t="inlineStr">
-        <is>
-          <t>A task's schedule kind: 'cron' (recurring) or 'once' (one-time).</t>
-        </is>
-      </c>
-      <c r="F17" s="109" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py; tools.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28.5" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>schedule.cron</t>
-        </is>
-      </c>
-      <c r="B18" s="114" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C18" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D18" s="110" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E18" s="110" t="inlineStr">
-        <is>
-          <t>5-field cron expression for recurring tasks (e.g. '10 19 * * *'), validated with croniter.</t>
-        </is>
-      </c>
-      <c r="F18" s="110" t="inlineStr">
-        <is>
-          <t>coworker/automation/tools.py; store.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="108" t="inlineStr">
-        <is>
-          <t>schedule.fire_at</t>
-        </is>
-      </c>
-      <c r="B19" s="112" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C19" s="112" t="inlineStr">
-        <is>
-          <t>string (ISO datetime)</t>
-        </is>
-      </c>
-      <c r="D19" s="109" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E19" s="109" t="inlineStr">
-        <is>
-          <t>ISO datetime for a one-time run (used when kind='once').</t>
-        </is>
-      </c>
-      <c r="F19" s="109" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28.75" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>schedule.timezone</t>
-        </is>
-      </c>
-      <c r="B20" s="114" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C20" s="114" t="inlineStr">
-        <is>
-          <t>string (IANA tz or 'local')</t>
-        </is>
-      </c>
-      <c r="D20" s="110" t="inlineStr">
-        <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="E20" s="110" t="inlineStr">
-        <is>
-          <t>Timezone for schedule computation; 'local' means the machine's clock (local-first default).</t>
-        </is>
-      </c>
-      <c r="F20" s="110" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py; store.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20.5" customHeight="1">
-      <c r="A21" s="108" t="inlineStr">
-        <is>
-          <t>task.notify_on_completion</t>
-        </is>
-      </c>
-      <c r="B21" s="112" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C21" s="112" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D21" s="109" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E21" s="109" t="inlineStr">
-        <is>
-          <t>Whether the automation notifies on completion of each run.</t>
-        </is>
-      </c>
-      <c r="F21" s="109" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26.75" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>task.notify_target</t>
-        </is>
-      </c>
-      <c r="B22" s="114" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C22" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D22" s="110" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E22" s="110" t="inlineStr">
-        <is>
-          <t>Optional extra messaging target for completion notifications (e.g. 'telegram:123').</t>
-        </is>
-      </c>
-      <c r="F22" s="110" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25.25" customHeight="1">
-      <c r="A23" s="108" t="inlineStr">
-        <is>
-          <t>task.max_runs</t>
-        </is>
-      </c>
-      <c r="B23" s="112" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C23" s="112" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D23" s="109" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E23" s="109" t="inlineStr">
-        <is>
-          <t>Optional cap on total runs; after reaching it next_run is no longer computed.</t>
-        </is>
-      </c>
-      <c r="F23" s="109" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py; store.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="39.25" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>task.always_allowed_tools</t>
-        </is>
-      </c>
-      <c r="B24" s="114" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C24" s="114" t="inlineStr">
-        <is>
-          <t>list[string]</t>
-        </is>
-      </c>
-      <c r="D24" s="110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E24" s="110" t="inlineStr">
-        <is>
-          <t>Standing scoped approvals as 'tool target' entries granting an automation a specific write against an exact target without re-asking.</t>
-        </is>
-      </c>
-      <c r="F24" s="110" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="108" t="inlineStr">
-        <is>
-          <t>task.enabled</t>
-        </is>
-      </c>
-      <c r="B25" s="112" t="inlineStr">
-        <is>
-          <t>automation task schema</t>
-        </is>
-      </c>
-      <c r="C25" s="112" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D25" s="109" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E25" s="109" t="inlineStr">
-        <is>
-          <t>Whether the task is active; disabled tasks compute no next_run and never fire.</t>
-        </is>
-      </c>
-      <c r="F25" s="109" t="inlineStr">
-        <is>
-          <t>coworker/automation/models.py; store.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="41.75" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
-        <is>
-          <t>pdf.fallback_mode</t>
-        </is>
-      </c>
-      <c r="B26" s="114" t="inlineStr">
-        <is>
-          <t>settings (Token savings)</t>
-        </is>
-      </c>
-      <c r="C26" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D26" s="110" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E26" s="110" t="inlineStr">
-        <is>
-          <t>Local PDF handling for models lacking native PDF: 'text' (extract embedded text via pypdf) or 'images' (rasterize pages to PNGs via pypdfium2).</t>
-        </is>
-      </c>
-      <c r="F26" s="110" t="inlineStr">
-        <is>
-          <t>coworker/pdf_support.py; route /v1/settings/pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="108" t="inlineStr">
-        <is>
-          <t>MAX_ATTACHMENTS</t>
-        </is>
-      </c>
-      <c r="B27" s="112" t="inlineStr">
-        <is>
-          <t>attachments limits</t>
-        </is>
-      </c>
-      <c r="C27" s="112" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D27" s="109" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E27" s="109" t="inlineStr">
-        <is>
-          <t>Maximum attachments appended to a single user turn.</t>
-        </is>
-      </c>
-      <c r="F27" s="109" t="inlineStr">
-        <is>
-          <t>coworker/attachments.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20.75" customHeight="1">
-      <c r="A28" s="37" t="inlineStr">
-        <is>
-          <t>MAX_IMAGE_CHARS</t>
-        </is>
-      </c>
-      <c r="B28" s="114" t="inlineStr">
-        <is>
-          <t>attachments limits</t>
-        </is>
-      </c>
-      <c r="C28" s="114" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D28" s="110" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
-      </c>
-      <c r="E28" s="110" t="inlineStr">
-        <is>
-          <t>Data-URL length cap for image attachments (~8-9MB decoded).</t>
-        </is>
-      </c>
-      <c r="F28" s="110" t="inlineStr">
-        <is>
-          <t>coworker/attachments.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="27.25" customHeight="1">
-      <c r="A29" s="108" t="inlineStr">
-        <is>
-          <t>MAX_PDF_CHARS</t>
-        </is>
-      </c>
-      <c r="B29" s="112" t="inlineStr">
-        <is>
-          <t>attachments limits</t>
-        </is>
-      </c>
-      <c r="C29" s="112" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D29" s="109" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
-      </c>
-      <c r="E29" s="109" t="inlineStr">
-        <is>
-          <t>Data-URL length cap for PDF attachments (~10MB decoded, matching the GUI pick limit).</t>
-        </is>
-      </c>
-      <c r="F29" s="109" t="inlineStr">
-        <is>
-          <t>coworker/attachments.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
-        <is>
-          <t>MAX_TEXT_CHARS</t>
-        </is>
-      </c>
-      <c r="B30" s="114" t="inlineStr">
-        <is>
-          <t>attachments limits</t>
-        </is>
-      </c>
-      <c r="C30" s="114" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D30" s="110" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="E30" s="110" t="inlineStr">
-        <is>
-          <t>Per-text-file character cap when inlining a text attachment.</t>
-        </is>
-      </c>
-      <c r="F30" s="110" t="inlineStr">
-        <is>
-          <t>coworker/attachments.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="27.75" customHeight="1">
-      <c r="A31" s="108" t="inlineStr">
-        <is>
-          <t>inbox binding.channel</t>
-        </is>
-      </c>
-      <c r="B31" s="112" t="inlineStr">
-        <is>
-          <t>inbox routing</t>
-        </is>
-      </c>
-      <c r="C31" s="112" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D31" s="109" t="inlineStr">
-        <is>
-          <t>null (in-app only)</t>
-        </is>
-      </c>
-      <c r="E31" s="109" t="inlineStr">
-        <is>
-          <t>Delivery binding channel for a named inbox: null (in-app only), 'slack', or 'telegram'.</t>
-        </is>
-      </c>
-      <c r="F31" s="109" t="inlineStr">
-        <is>
-          <t>coworker/inbox_routing.py; route /v1/inbox/routing/binding</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="29.25" customHeight="1">
-      <c r="A32" s="37" t="inlineStr">
-        <is>
-          <t>persona.default_permission_mode</t>
-        </is>
-      </c>
-      <c r="B32" s="114" t="inlineStr">
-        <is>
-          <t>persona manifest frontmatter</t>
-        </is>
-      </c>
-      <c r="C32" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D32" s="110" t="inlineStr">
-        <is>
-          <t>interactive</t>
-        </is>
-      </c>
-      <c r="E32" s="110" t="inlineStr">
-        <is>
-          <t>Recommended permission mode a persona declares: discuss | plan | interactive | custom | auto.</t>
-        </is>
-      </c>
-      <c r="F32" s="110" t="inlineStr">
-        <is>
-          <t>coworker/personas/manifest.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28.25" customHeight="1">
-      <c r="A33" s="108" t="inlineStr">
-        <is>
-          <t>persona.family</t>
-        </is>
-      </c>
-      <c r="B33" s="112" t="inlineStr">
-        <is>
-          <t>persona manifest frontmatter</t>
-        </is>
-      </c>
-      <c r="C33" s="112" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D33" s="109" t="inlineStr">
-        <is>
-          <t>knowledge</t>
-        </is>
-      </c>
-      <c r="E33" s="109" t="inlineStr">
-        <is>
-          <t>Persona family: 'code' (git workspace) or 'knowledge' (deliverable scratch + user roots).</t>
-        </is>
-      </c>
-      <c r="F33" s="109" t="inlineStr">
-        <is>
-          <t>coworker/personas/manifest.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="31.5" customHeight="1">
-      <c r="A34" s="37" t="inlineStr">
-        <is>
-          <t>persona.tools</t>
-        </is>
-      </c>
-      <c r="B34" s="114" t="inlineStr">
-        <is>
-          <t>persona manifest frontmatter</t>
-        </is>
-      </c>
-      <c r="C34" s="114" t="inlineStr">
-        <is>
-          <t>list[string]</t>
-        </is>
-      </c>
-      <c r="D34" s="110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E34" s="110" t="inlineStr">
-        <is>
-          <t>Capability ids from the vetted catalog (code_files, files, git, search, shell, todo) the persona uses.</t>
-        </is>
-      </c>
-      <c r="F34" s="110" t="inlineStr">
-        <is>
-          <t>coworker/personas/manifest.py; catalog.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="23.25" customHeight="1">
-      <c r="A35" s="108" t="inlineStr">
-        <is>
-          <t>persona.messaging</t>
-        </is>
-      </c>
-      <c r="B35" s="112" t="inlineStr">
-        <is>
-          <t>persona manifest frontmatter</t>
-        </is>
-      </c>
-      <c r="C35" s="112" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D35" s="109" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E35" s="109" t="inlineStr">
-        <is>
-          <t>Whether the persona is reachable/able to act over messaging channels.</t>
-        </is>
-      </c>
-      <c r="F35" s="109" t="inlineStr">
-        <is>
-          <t>coworker/personas/manifest.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="37" t="inlineStr">
-        <is>
-          <t>persona.connectors</t>
-        </is>
-      </c>
-      <c r="B36" s="114" t="inlineStr">
-        <is>
-          <t>persona manifest frontmatter</t>
-        </is>
-      </c>
-      <c r="C36" s="114" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D36" s="110" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E36" s="110" t="inlineStr">
-        <is>
-          <t>Whether the persona uses external connectors.</t>
-        </is>
-      </c>
-      <c r="F36" s="110" t="inlineStr">
-        <is>
-          <t>coworker/personas/manifest.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.75" customHeight="1">
-      <c r="A37" s="108" t="inlineStr">
-        <is>
-          <t>persona.recommended_models</t>
-        </is>
-      </c>
-      <c r="B37" s="112" t="inlineStr">
-        <is>
-          <t>persona manifest frontmatter</t>
-        </is>
-      </c>
-      <c r="C37" s="112" t="inlineStr">
-        <is>
-          <t>list[string]</t>
-        </is>
-      </c>
-      <c r="D37" s="109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E37" s="109" t="inlineStr">
-        <is>
-          <t>Models the persona recommends (e.g. anthropic:claude-opus-4-8, openai:gpt-5.5).</t>
-        </is>
-      </c>
-      <c r="F37" s="109" t="inlineStr">
-        <is>
-          <t>coworker/personas/manifest.py; builtin/ops.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="37" t="inlineStr">
-        <is>
-          <t>subscription.filter</t>
-        </is>
-      </c>
-      <c r="B38" s="114" t="inlineStr">
-        <is>
-          <t>channel subscription schema</t>
-        </is>
-      </c>
-      <c r="C38" s="114" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D38" s="110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E38" s="110" t="inlineStr">
-        <is>
-          <t>Which channel messages a subscription delivers; v1 always delivers 'all' (reserved for 'mentions' etc.).</t>
-        </is>
-      </c>
-      <c r="F38" s="110" t="inlineStr">
-        <is>
-          <t>coworker/subscriptions.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="21" customHeight="1">
-      <c r="A39" s="108" t="inlineStr">
-        <is>
-          <t>skill.allowed-tools</t>
-        </is>
-      </c>
-      <c r="B39" s="112" t="inlineStr">
-        <is>
-          <t>SKILL.md frontmatter</t>
-        </is>
-      </c>
-      <c r="C39" s="112" t="inlineStr">
-        <is>
-          <t>list[string]</t>
-        </is>
-      </c>
-      <c r="D39" s="109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E39" s="109" t="inlineStr">
-        <is>
-          <t>Optional tool allowlist a skill declares in its frontmatter.</t>
-        </is>
-      </c>
-      <c r="F39" s="109" t="inlineStr">
-        <is>
-          <t>coworker/skills/base.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="23.5" customHeight="1">
-      <c r="A40" s="37" t="inlineStr">
-        <is>
-          <t>COWORKER_EXIT_WITH_PARENT</t>
-        </is>
-      </c>
-      <c r="B40" s="114" t="inlineStr">
-        <is>
-          <t>server env (sidecar)</t>
-        </is>
-      </c>
-      <c r="C40" s="114" t="inlineStr">
-        <is>
-          <t>env flag ('1')</t>
-        </is>
-      </c>
-      <c r="D40" s="110" t="inlineStr">
-        <is>
-          <t>unset</t>
-        </is>
-      </c>
-      <c r="E40" s="110" t="inlineStr">
-        <is>
-          <t>When set, the server exits if its parent (desktop shell) process dies.</t>
-        </is>
-      </c>
-      <c r="F40" s="110" t="inlineStr">
-        <is>
-          <t>coworker/server/run.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="108" t="inlineStr">
-        <is>
-          <t>COWORKER_PARENT_PID / COWORKER_PORT</t>
-        </is>
-      </c>
-      <c r="B41" s="112" t="inlineStr">
-        <is>
-          <t>server env (sidecar)</t>
-        </is>
-      </c>
-      <c r="C41" s="112" t="inlineStr">
-        <is>
-          <t>env int</t>
-        </is>
-      </c>
-      <c r="D41" s="109" t="inlineStr">
-        <is>
-          <t>unset</t>
-        </is>
-      </c>
-      <c r="E41" s="109" t="inlineStr">
-        <is>
-          <t>Parent PID the sidecar watches for liveness, and the port used in OAuth state suffixing.</t>
-        </is>
-      </c>
-      <c r="F41" s="109" t="inlineStr">
-        <is>
-          <t>coworker/server/run.py; cloud.py</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -405,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -804,6 +804,7 @@
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12880,19 +12881,19 @@
           <t>create_scheduled_task is approval-gated so a consent card surfaces before a standing automation exists, disclosing every read/write the instructions imply (coworker/automation/tools.py).</t>
         </is>
       </c>
-      <c r="D8" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D8" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E8" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Inbox · approve at creation</t>
         </is>
       </c>
       <c r="F8" s="127" t="inlineStr">
         <is>
-          <t>Needs the approval/consent subsystem (rows 13-19). Nothing is gated today.</t>
+          <t>Consequential actions raise an ask before running; approve/deny with an optional 'remember for 24h'.</t>
         </is>
       </c>
     </row>
@@ -12912,19 +12913,19 @@
           <t>Approving a write on the consent card creates a target-bound standing grant ('tool target') so an automation may call that exact tool against that exact target every run without re-asking; grants are revocable per-automation (coworker/automation/models.py).</t>
         </is>
       </c>
-      <c r="D9" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D9" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E9" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Inbox · standing grants</t>
         </is>
       </c>
       <c r="F9" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 8.</t>
+          <t>capability + target, scoped. A grant for '*' is refused outright. Revocable from the Permissions tab.</t>
         </is>
       </c>
     </row>
@@ -13040,19 +13041,19 @@
           <t>A single canonical queue holds what agents need from the human — approvals, questions, notifications, directory-grant requests, and plan approvals — as the store of record across all sessions (coworker/inbox.py).</t>
         </is>
       </c>
-      <c r="D13" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D13" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E13" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/inbox</t>
         </is>
       </c>
       <c r="F13" s="127" t="inlineStr">
         <is>
-          <t>Needs an Inbox surface. Highest-value next cluster.</t>
+          <t>Cross-session Inbox. Asks survive restarts and are answerable from anywhere.</t>
         </is>
       </c>
     </row>
@@ -13072,19 +13073,19 @@
           <t>Consequential actions (file writes, external sends, shell) are permission-classified and gated; inbox_approver turns a permission request into an item and suspends the agent until it is resolved (coworker/inbox.py, permissions.py, risk.py).</t>
         </is>
       </c>
-      <c r="D14" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D14" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E14" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Terminal + net.fetch gate</t>
         </is>
       </c>
       <c r="F14" s="127" t="inlineStr">
         <is>
-          <t>Dobby has no shell execution or outbound sends yet, so there is nothing to gate — becomes real with Terminal (P2).</t>
+          <t>Shell execution and remote web search both gated. Denial and timeout both mean no.</t>
         </is>
       </c>
     </row>
@@ -13104,19 +13105,19 @@
           <t>Each item is a durable pending-to-resolved record, idempotent by (session, tool_call_id) and first-responder-wins, so it can be answered from the app, Slack, or the composer and survives restarts (coworker/inbox.py).</t>
         </is>
       </c>
-      <c r="D15" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D15" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E15" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Parked asks</t>
         </is>
       </c>
       <c r="F15" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 13.</t>
+          <t>An ask outlives its waiter — a caller that times out leaves the question answerable.</t>
         </is>
       </c>
     </row>
@@ -13136,19 +13137,19 @@
           <t>Attended sessions answer prompts inline in the composer (parked server-side, redelivered on reconnect); unattended sessions route the same prompts to the cross-session Inbox queue (coworker/inbox.py).</t>
         </is>
       </c>
-      <c r="D16" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D16" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E16" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Inbox tabs</t>
         </is>
       </c>
       <c r="F16" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 13.</t>
+          <t>Waiting / History / Permissions. No inline-vs-inbox routing distinction yet.</t>
         </is>
       </c>
     </row>
@@ -13168,19 +13169,19 @@
           <t>Questions can carry quick-reply options plus an always-available typed answer and optional multi-select, mirroring a structured-but-answerable ask (coworker/inbox.py).</t>
         </is>
       </c>
-      <c r="D17" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D17" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E17" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Answer + note field</t>
         </is>
       </c>
       <c r="F17" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 13.</t>
+          <t>Approve/deny with free-text. Structured quick-reply options are stored but not yet rendered.</t>
         </is>
       </c>
     </row>
@@ -13232,19 +13233,19 @@
           <t>When a user resumes attended control, still-pending items are surfaced inline in one place plus a recap of what was answered while away (coworker/inbox.py).</t>
         </is>
       </c>
-      <c r="D19" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D19" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E19" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reconcile()</t>
         </is>
       </c>
       <c r="F19" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 13.</t>
+          <t>Asks stranded by a restart are unstuck on load rather than looking permanently in-flight.</t>
         </is>
       </c>
     </row>
@@ -14320,19 +14321,19 @@
           <t>No commands auto-run without approval by default; the built-in allowed-commands list is intentionally empty and users must opt into command prefixes in their own global config (coworker/config.py).</t>
         </is>
       </c>
-      <c r="D53" s="131" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D53" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E53" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>shell_allowlist (empty)</t>
         </is>
       </c>
       <c r="F53" s="127" t="inlineStr">
         <is>
-          <t>Dobby executes no shell commands, so the allowlist is empty by construction. Revisit with Terminal (P2).</t>
+          <t>Empty by default — nothing runs unattended. Destructive commands refused even with approval.</t>
         </is>
       </c>
     </row>
@@ -14416,19 +14417,19 @@
           <t>The standalone server writes a per-launch, user-only token file and requires it in the X-OpenWorker-Token header; the desktop app uses an in-memory token never written to disk (README.md, coworker/server/run.py).</t>
         </is>
       </c>
-      <c r="D56" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D56" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E56" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>src/security/tokens.py</t>
         </is>
       </c>
       <c r="F56" s="127" t="inlineStr">
         <is>
-          <t>Loopback token for the local API. Small and worth doing before any packaged release.</t>
+          <t>Per-launch token, owner-only runtime.json, required on every /api route; CORS-guarded handshake.</t>
         </is>
       </c>
     </row>
@@ -14568,7 +14569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14577,6 +14578,7 @@
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14624,6 +14626,11 @@
           <t>Priority</t>
         </is>
       </c>
+      <c r="G4" s="141" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="142" t="n">
@@ -14654,6 +14661,11 @@
           <t>P0</t>
         </is>
       </c>
+      <c r="G5" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="142" t="n">
@@ -14684,6 +14696,11 @@
           <t>P0</t>
         </is>
       </c>
+      <c r="G6" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="142" t="n">
@@ -14714,6 +14731,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="G7" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="142" t="n">
@@ -14744,6 +14766,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="G8" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="142" t="n">
@@ -14774,6 +14801,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="G9" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="142" t="n">
@@ -14804,6 +14836,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="G10" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="142" t="n">
@@ -14834,6 +14871,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="G11" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="142" t="n">
@@ -14864,6 +14906,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="G12" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="142" t="n">
@@ -14894,6 +14941,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="G13" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="142" t="n">
@@ -14922,6 +14974,11 @@
       <c r="F14" s="142" t="inlineStr">
         <is>
           <t>P4</t>
+        </is>
+      </c>
+      <c r="G14" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -13617,19 +13617,19 @@
           <t>Personas reference stable capability ids (code_files, files, git, search, shell, todo) that expand into concrete tools only when session context prerequisites (workspace/executor/todo) are met (coworker/catalog.py).</t>
         </is>
       </c>
-      <c r="D31" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D31" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E31" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Connections page</t>
         </is>
       </c>
       <c r="F31" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 26.</t>
+          <t>Tools from connected MCP servers are discovered and listed. No vetting/curation layer yet.</t>
         </is>
       </c>
     </row>
@@ -14449,19 +14449,19 @@
           <t>Any Model Context Protocol server plugs in with per-tool control and OAuth support, managed via dedicated endpoints (README.md, coworker/mcp, routes /v1/mcp).</t>
         </is>
       </c>
-      <c r="D57" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D57" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E57" s="126" t="inlineStr">
         <is>
-          <t>wigolo (MCP server)</t>
+          <t>src/mcp/client.py</t>
         </is>
       </c>
       <c r="F57" s="127" t="inlineStr">
         <is>
-          <t>Dobby consumes wigolo, which is an MCP server, over its REST surface. Dobby is not yet a general MCP client.</t>
+          <t>Full MCP client — stdio and Streamable HTTP, tool discovery and calls. Verified against a real server (wigolo, 10 tools).</t>
         </is>
       </c>
     </row>
@@ -14766,9 +14766,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="146" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G8" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -14097,19 +14097,19 @@
           <t>User turns accept image, PDF and text attachments (up to 8) built into provider content parts, with per-type size caps; invalid/oversized attachments are skipped rather than failing the turn (coworker/attachments.py).</t>
         </is>
       </c>
-      <c r="D46" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D46" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E46" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Attachments · upload</t>
         </is>
       </c>
       <c r="F46" s="127" t="inlineStr">
         <is>
-          <t>Needs an attachment store and multimodal input.</t>
+          <t>Files stored in the project workspace and read locally. PDF, markdown, text, csv, json, html. Selected files become source material for research.</t>
         </is>
       </c>
     </row>
@@ -14129,19 +14129,19 @@
           <t>For models without native PDF support, PDFs are handled locally — extract embedded text (pypdf) or rasterize pages to PNGs (pypdfium2) — entirely on-device, cached by content hash, user-selectable in Token savings (coworker/pdf_support.py).</t>
         </is>
       </c>
-      <c r="D47" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D47" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E47" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>attachment_service · fallbacks</t>
         </is>
       </c>
       <c r="F47" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 46.</t>
+          <t>pypdf, then macOS textutil, then an honest 'needs OCR' — a scanned PDF is never returned as a silently empty extraction.</t>
         </is>
       </c>
     </row>
@@ -14801,9 +14801,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G9" s="146" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G9" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -13905,19 +13905,19 @@
           <t>Users paste their own key for OpenAI, Anthropic, Google Gemini, Inkling, GLM, DeepSeek, Kimi, Qwen, MiniMax, Mistral, Grok, plus open-weight via Together/Fireworks and fully local via Ollama; a curated list marks tool-calling-verified models (README.md, coworker/providers).</t>
         </is>
       </c>
-      <c r="D40" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D40" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E40" s="126" t="inlineStr">
         <is>
-          <t>Settings · Ollama host</t>
+          <t>src/llm/providers.py</t>
         </is>
       </c>
       <c r="F40" s="127" t="inlineStr">
         <is>
-          <t>Any OpenAI-compatible host reachable at the configured URL works; provider abstraction beyond Ollama is not built.</t>
+          <t>Ollama, any OpenAI-compatible endpoint (LM Studio, llama.cpp, vLLM, OpenRouter, OpenAI), and Anthropic behind one interface.</t>
         </is>
       </c>
     </row>
@@ -13937,19 +13937,19 @@
           <t>The default model is configurable and can be overridden per session in the UI/CLI; custom model strings can be added at the user's own risk (docs/config.example.toml, routes /v1/settings/default-model, /v1/settings/models/add).</t>
         </is>
       </c>
-      <c r="D41" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D41" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E41" s="126" t="inlineStr">
         <is>
-          <t>Settings · active model</t>
+          <t>providers.generate(model=…)</t>
         </is>
       </c>
       <c r="F41" s="127" t="inlineStr">
         <is>
-          <t>Model switches globally and takes effect on the next run. Not per-session.</t>
+          <t>A caller passes a model and gets that model, instead of every request reading one global setting.</t>
         </is>
       </c>
     </row>
@@ -13969,19 +13969,19 @@
           <t>Providers declare capabilities (e.g. native PDF, vision); the engine adapts message content to the active model at send time (coworker/providers/capabilities.py, pdf_support.py).</t>
         </is>
       </c>
-      <c r="D42" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D42" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E42" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Capability routing</t>
         </is>
       </c>
       <c r="F42" s="127" t="inlineStr">
         <is>
-          <t>Needs a capability registry per model.</t>
+          <t>Callers state what they need (local, long context, tools, JSON, vision) and routing satisfies it — preferring local, then largest context.</t>
         </is>
       </c>
     </row>
@@ -14836,9 +14836,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G10" s="146" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G10" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -13265,19 +13265,19 @@
           <t>A per-session toggle that routes any inline approval/question to the Inbox and suspends the agent instead of prompting in the composer; turning it on is a one-tap confirm (coworker/unattended.py).</t>
         </is>
       </c>
-      <c r="D20" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D20" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E20" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>permission_mode=unattended</t>
         </is>
       </c>
       <c r="F20" s="127" t="inlineStr">
         <is>
-          <t>Needs an agent runtime with permission modes.</t>
+          <t>Low-risk actions proceed; medium and high still reach the Inbox, so 'unattended' never silently means 'unsupervised'.</t>
         </is>
       </c>
     </row>
@@ -13297,19 +13297,19 @@
           <t>Sessions run in Discuss (read-only), Plan (read-only + planning contract), Interactive (ask on writes/commands), Auto (full access) or Custom (interactive plus config auto_allow) (coworker/permissions.py).</t>
         </is>
       </c>
-      <c r="D21" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D21" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E21" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ask / unattended / readonly</t>
         </is>
       </c>
       <c r="F21" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 20.</t>
+          <t>readonly is checked before grants — a mode a standing grant could defeat would be a setting that lies.</t>
         </is>
       </c>
     </row>
@@ -13329,19 +13329,19 @@
           <t>Tools let a long-running agent sleep and be re-invoked on a trigger: sleep_for/sleep_until timers, wake_on job completion, and wake_on_event named connector/webhook events, resumed by the shared scheduler tick (coworker/selfwake.py).</t>
         </is>
       </c>
-      <c r="D22" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D22" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E22" s="126" t="inlineStr">
         <is>
-          <t>Scheduler wake</t>
+          <t>suspend / resume</t>
         </is>
       </c>
       <c r="F22" s="127" t="inlineStr">
         <is>
-          <t>The scheduler already wakes the app to do work on a schedule. Session-level suspend/resume is not built.</t>
+          <t>Checkpoint-based, so resuming after a crash, a restart or a week is the same operation.</t>
         </is>
       </c>
     </row>
@@ -13361,19 +13361,19 @@
           <t>A session can read/write across multiple added root folders beyond its primary workspace, each marked writable or not (coworker/permissions.py, server routes /v1/sessions/{id}/roots).</t>
         </is>
       </c>
-      <c r="D23" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D23" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E23" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>workspace_roots</t>
         </is>
       </c>
       <c r="F23" s="127" t="inlineStr">
         <is>
-          <t>Dobby is single-workspace; multi-root needs a workspace model.</t>
+          <t>Sessions carry a list of permitted roots. The terminal still scopes to the single project workspace.</t>
         </is>
       </c>
     </row>
@@ -13393,19 +13393,19 @@
           <t>Conversations persist in a shared SQLite store used by GUI, server and CLI, and can be resumed by id with model and mode restored (coworker/cli.py, conversations).</t>
         </is>
       </c>
-      <c r="D24" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D24" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E24" s="126" t="inlineStr">
         <is>
-          <t>Session table + WizardState</t>
+          <t>WorkSession + checkpoint</t>
         </is>
       </c>
       <c r="F24" s="127" t="inlineStr">
         <is>
-          <t>Wizard state is durable and resumable across restarts. Full session resume for all surfaces is not.</t>
+          <t>State lives in the row and survives restarts. Startup suspends orphaned sessions rather than failing them.</t>
         </is>
       </c>
     </row>
@@ -14871,9 +14871,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G11" s="146" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G11" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -13457,19 +13457,19 @@
           <t>Ships a default deliverable-producing Cowork persona, a Code persona (files/git/shell), a hidden Chat persona, and a markdown-defined Ops persona for incidents/runbooks (coworker/personas/registry.py, builtin/ops.md).</t>
         </is>
       </c>
-      <c r="D26" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D26" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E26" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dobby / Researcher / Engineer / Ops</t>
         </is>
       </c>
       <c r="F26" s="127" t="inlineStr">
         <is>
-          <t>Persona subsystem not started.</t>
+          <t>Four built-ins that cannot be deleted, only disabled.</t>
         </is>
       </c>
     </row>
@@ -13489,19 +13489,19 @@
           <t>Personas are defined by YAML-frontmatter + markdown files declaring identity, tool capabilities, family, messaging/connectors flags, recommended models, skills, MCP and permission mode (coworker/personas/manifest.py).</t>
         </is>
       </c>
-      <c r="D27" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D27" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E27" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Markdown + frontmatter</t>
         </is>
       </c>
       <c r="F27" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 26.</t>
+          <t>Hand-written parser rather than PyYAML — the schema is small and fixed, and third-party input deserves the smaller surface.</t>
         </is>
       </c>
     </row>
@@ -13521,19 +13521,19 @@
           <t>Personas install from a local dir or git URL by snapshotting the manifest into a managed area; each lands disabled/unsurfaced pending a consent summary of tools, risk classes, connectors, MCP and messaging (coworker/personas/loading.py, registry.py).</t>
         </is>
       </c>
-      <c r="D28" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D28" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E28" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Install via the Inbox</t>
         </is>
       </c>
       <c r="F28" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 26.</t>
+          <t>A persona's prompt shapes every response, so installing one asks. Instruction-override phrases are surfaced on the consent card.</t>
         </is>
       </c>
     </row>
@@ -13553,19 +13553,19 @@
           <t>Installed personas track enabled/surfaced state and a default; the new-session picker shows only enabled-and-surfaced personas, while live sessions keep resolving even a disabled persona (coworker/personas/registry.py).</t>
         </is>
       </c>
-      <c r="D29" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D29" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E29" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>enable / activate / uninstall</t>
         </is>
       </c>
       <c r="F29" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 26.</t>
+          <t>Built-ins cannot be removed; the active persona cannot be disabled out from under itself.</t>
         </is>
       </c>
     </row>
@@ -13585,19 +13585,19 @@
           <t>A persona can recommend connectors or MCP servers with a reason and core/optional tier, surfaced in the per-session connections drawer (coworker/personas/manifest.py, builtin/ops.md).</t>
         </is>
       </c>
-      <c r="D30" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D30" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E30" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>recommendations()</t>
         </is>
       </c>
       <c r="F30" s="127" t="inlineStr">
         <is>
-          <t>Depends on connectors.</t>
+          <t>A persona names the MCP connections it wants and the UI reports which are installed and connected.</t>
         </is>
       </c>
     </row>
@@ -13617,19 +13617,19 @@
           <t>Personas reference stable capability ids (code_files, files, git, search, shell, todo) that expand into concrete tools only when session context prerequisites (workspace/executor/todo) are met (coworker/catalog.py).</t>
         </is>
       </c>
-      <c r="D31" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D31" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E31" s="126" t="inlineStr">
         <is>
-          <t>Connections page</t>
+          <t>capability_catalog()</t>
         </is>
       </c>
       <c r="F31" s="127" t="inlineStr">
         <is>
-          <t>Tools from connected MCP servers are discovered and listed. No vetting/curation layer yet.</t>
+          <t>Every capability a persona may declare, with its risk. Unknown ones are dropped, not honoured.</t>
         </is>
       </c>
     </row>
@@ -13649,19 +13649,19 @@
           <t>Skills are SKILL.md folders (name/description/optional allowed-tools + body); only the catalog is injected at session start and the full body loads on demand via the load_skill tool (coworker/skills/base.py).</t>
         </is>
       </c>
-      <c r="D32" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D32" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E32" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>model_capabilities</t>
         </is>
       </c>
       <c r="F32" s="127" t="inlineStr">
         <is>
-          <t>Overlaps the planned Skills surface (P3).</t>
+          <t>Personas contribute model requirements to routing and supply the system prompt. Progressive skill disclosure waits on the Skills surface (P3).</t>
         </is>
       </c>
     </row>
@@ -14941,9 +14941,9 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="G13" s="146" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G13" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -14161,19 +14161,19 @@
           <t>A Rust STT sidecar (whisper-rs) captures the mic and transcribes voice input fully offline, provisioning a ~142MB ggml-base.en Whisper model verified by SHA-256 (stt/src/lib.rs).</t>
         </is>
       </c>
-      <c r="D48" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D48" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E48" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>transcription_service</t>
         </is>
       </c>
       <c r="F48" s="127" t="inlineStr">
         <is>
-          <t>Whisper sidecar; already scheduled as P2 Transcribe.</t>
+          <t>whisper.cpp or faster-whisper, whichever is installed. Models downloaded on request through the approval gate. Verified end to end: real speech transcribed in 1.1s on tiny.en, fully offline.</t>
         </is>
       </c>
     </row>
@@ -14906,9 +14906,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G12" s="146" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G12" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -13201,19 +13201,19 @@
           <t>Named inboxes can mirror items to a bound Slack channel or Telegram chat with the item id embedded; an inbound reply is correlated by that id and resolves the item bidirectionally (coworker/inbox_routing.py).</t>
         </is>
       </c>
-      <c r="D18" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D18" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E18" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Inbox + connectors</t>
         </is>
       </c>
       <c r="F18" s="127" t="inlineStr">
         <is>
-          <t>Needs messaging connectors (rows 33-39).</t>
+          <t>Approvals surface in the Inbox and outbound sends are gated. Mirroring an ask into Slack/Telegram is not wired.</t>
         </is>
       </c>
     </row>
@@ -13681,19 +13681,19 @@
           <t>Mentioning @OpenWorker in a channel spawns a desktop coworker session that owns the thread and replies back into it; follow-up tags steer the same session, deduped on the thread target (coworker/mentions.py, server/manager.py _route_mention).</t>
         </is>
       </c>
-      <c r="D33" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D33" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E33" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SlackConnector</t>
         </is>
       </c>
       <c r="F33" s="127" t="inlineStr">
         <is>
-          <t>Needs Slack app + OAuth.</t>
+          <t>Mentions parsed and routed; signature-verified webhook. Needs a Slack app + bot token from your workspace to run.</t>
         </is>
       </c>
     </row>
@@ -13713,19 +13713,19 @@
           <t>A mention-spawned session gets a standing grant to send_message to its exact thread target so the Slack conversation never stalls on an approval nobody in-channel can see; re-derived on every engine rebuild (coworker/mentions.py, server/manager.py).</t>
         </is>
       </c>
-      <c r="D34" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D34" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E34" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reply(in_reply_to=…)</t>
         </is>
       </c>
       <c r="F34" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 33.</t>
+          <t>Replying in a thread where Dobby was addressed is pre-approved. A different channel still asks.</t>
         </is>
       </c>
     </row>
@@ -13745,19 +13745,19 @@
           <t>A session can subscribe to a messaging channel to receive its messages as a steer (while busy) or a fresh background turn (when idle), with subscribe/unsubscribe/list/catch-up tools (coworker/subscriptions.py).</t>
         </is>
       </c>
-      <c r="D35" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D35" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E35" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>subscribe / unsubscribe</t>
         </is>
       </c>
       <c r="F35" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 33.</t>
+          <t>Watched channels are routed inbound; everything else is dead-lettered.</t>
         </is>
       </c>
     </row>
@@ -13777,19 +13777,19 @@
           <t>A per-channel ring buffer keeps the last N messages seen so a subscribed agent can catch up and the channel picker can suggest already-seen channels (coworker/subscriptions.py ChannelBuffer).</t>
         </is>
       </c>
-      <c r="D36" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D36" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E36" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>recent buffer</t>
         </is>
       </c>
       <c r="F36" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 33.</t>
+          <t>Last 100 messages per connector kept, so a restart does not lose context.</t>
         </is>
       </c>
     </row>
@@ -13809,19 +13809,19 @@
           <t>Inbox items and replies flow over Slack and Telegram via a managed relay WebSocket for inbound events; connectors/mobile are just transports of the same Inbox items (coworker/inbox_routing.py, config cloud_relay_ws_url, connectors/relay_client.py).</t>
         </is>
       </c>
-      <c r="D37" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D37" s="129" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E37" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Slack + Telegram</t>
         </is>
       </c>
       <c r="F37" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 33.</t>
+          <t>Both transports implemented behind one interface. Credentials are user-supplied.</t>
         </is>
       </c>
     </row>
@@ -13841,19 +13841,19 @@
           <t>Direct messages route to a designated session; inbound messages with nowhere to go and failed background turns are recorded durably in an unrouted dead-letter log for visibility rather than vanishing (coworker/unrouted.py, routes /v1/messaging/dm-route, /v1/unrouted).</t>
         </is>
       </c>
-      <c r="D38" s="130" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D38" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E38" s="126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dead_letters()</t>
         </is>
       </c>
       <c r="F38" s="127" t="inlineStr">
         <is>
-          <t>Depends on row 33.</t>
+          <t>Unrouted messages kept with the reason. Unverified requests are refused, never stored.</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="F39" s="127" t="inlineStr">
         <is>
-          <t>Large connector programme; scheduled P5 with the Marketplace.</t>
+          <t>Two connectors of the 25+ OpenWorker ships. The interface is there; the rest is volume.</t>
         </is>
       </c>
     </row>
@@ -14976,9 +14976,9 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="G14" s="146" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="G14" s="134" t="inlineStr">
+        <is>
+          <t>Done 2026-07-26 (needs your Slack credentials to run)</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -13169,19 +13169,19 @@
           <t>Questions can carry quick-reply options plus an always-available typed answer and optional multi-select, mirroring a structured-but-answerable ask (coworker/inbox.py).</t>
         </is>
       </c>
-      <c r="D17" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D17" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E17" s="126" t="inlineStr">
         <is>
-          <t>Answer + note field</t>
+          <t>Inbox · quick-reply chips</t>
         </is>
       </c>
       <c r="F17" s="127" t="inlineStr">
         <is>
-          <t>Approve/deny with free-text. Structured quick-reply options are stored but not yet rendered.</t>
+          <t>Ask.options render as one-click reply buttons; free text remains for anything else.</t>
         </is>
       </c>
     </row>
@@ -13201,19 +13201,19 @@
           <t>Named inboxes can mirror items to a bound Slack channel or Telegram chat with the item id embedded; an inbound reply is correlated by that id and resolves the item bidirectionally (coworker/inbox_routing.py).</t>
         </is>
       </c>
-      <c r="D18" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D18" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E18" s="126" t="inlineStr">
         <is>
-          <t>Inbox + connectors</t>
+          <t>inbox.notify_mirror()</t>
         </is>
       </c>
       <c r="F18" s="127" t="inlineStr">
         <is>
-          <t>Approvals surface in the Inbox and outbound sends are gated. Mirroring an ask into Slack/Telegram is not wired.</t>
+          <t>A new ask posts to a configured Slack/Telegram channel. Configuring the mirror is the consent — the notification never itself needs approving.</t>
         </is>
       </c>
     </row>
@@ -13361,19 +13361,19 @@
           <t>A session can read/write across multiple added root folders beyond its primary workspace, each marked writable or not (coworker/permissions.py, server routes /v1/sessions/{id}/roots).</t>
         </is>
       </c>
-      <c r="D23" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D23" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E23" s="126" t="inlineStr">
         <is>
-          <t>workspace_roots</t>
+          <t>terminal_service._resolve_cwd</t>
         </is>
       </c>
       <c r="F23" s="127" t="inlineStr">
         <is>
-          <t>Sessions carry a list of permitted roots. The terminal still scopes to the single project workspace.</t>
+          <t>An absolute cwd is now checked against a session's workspace_roots, not just the single project directory.</t>
         </is>
       </c>
     </row>
@@ -14065,19 +14065,19 @@
           <t>A todo_write task list drives the visible Progress panel the user watches during a run, with exactly one item in-progress at a time (coworker/catalog.py todo, personas/builtin/ops.md).</t>
         </is>
       </c>
-      <c r="D45" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D45" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E45" s="126" t="inlineStr">
         <is>
-          <t>Live run progress</t>
+          <t>src/services/run_todo.py</t>
         </is>
       </c>
       <c r="F45" s="127" t="inlineStr">
         <is>
-          <t>Step-by-step progress streams over SSE into Logs &amp; Traces and the generation pages. Not a todo-list panel.</t>
+          <t>Derives a done/in-progress/failed/pending checklist from the existing event stream. Logs &amp; Traces gained a Trace/Checklist toggle.</t>
         </is>
       </c>
     </row>
@@ -14353,19 +14353,19 @@
           <t>Personas are instructed to treat content from tools, logs, the web, files and incoming messages as untrusted data rather than instructions, and to avoid destructive actions without explicit approval (coworker/personas/builtin/ops.md, agents/myhelper.py).</t>
         </is>
       </c>
-      <c r="D54" s="129" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="D54" s="125" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="E54" s="126" t="inlineStr">
         <is>
-          <t>Research grounding</t>
+          <t>src/security/content_safety.py</t>
         </is>
       </c>
       <c r="F54" s="127" t="inlineStr">
         <is>
-          <t>Retrieved web content is treated as data, never instructions; unsourced claims are tagged. No formal untrusted-content sandbox.</t>
+          <t>Shared with the persona injection-phrase scan. A flagged research source is quoted as untrusted data, not deleted.</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -221,6 +221,11 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -405,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -805,6 +810,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3336,7 +3344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3352,6 +3360,8 @@
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3418,6 +3428,16 @@
       <c r="M1" s="29" t="inlineStr">
         <is>
           <t>Success Metric</t>
+        </is>
+      </c>
+      <c r="N1" s="141" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O1" s="141" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
@@ -3508,6 +3528,16 @@
           <t>Percentage of app launches where the user takes an action from Today Home within 60 seconds (target &gt;70%).</t>
         </is>
       </c>
+      <c r="N2" s="136" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="O2" s="147" t="inlineStr">
+        <is>
+          <t>Dashboard has a 'Today's priority' card; upgrading to a real daily agenda.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="222.1153846153846" customHeight="1">
       <c r="A3" s="35" t="n">
@@ -3597,6 +3627,16 @@
           <t>Median captures per active day per user (target: at least 3, indicating the hotkey is a reflex).</t>
         </is>
       </c>
+      <c r="N3" s="136" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O3" s="147" t="inlineStr">
+        <is>
+          <t>In-app quick-capture shipped (⌘I overlay, works from any page). OS-global hotkey still deferred — needs the Tauri capabilities work already deferred for reveal-in-Finder.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="216.3461538461538" customHeight="1">
       <c r="A4" s="30" t="n">
@@ -3686,6 +3726,16 @@
           <t>Percentage of active days a user reaches Inbox Zero (target &gt;40%), signaling the triage habit sticks.</t>
         </is>
       </c>
+      <c r="N4" s="136" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O4" s="147" t="inlineStr">
+        <is>
+          <t>Idea Inbox shipped: capture, list by status, triage into Backlog (Pareto-scored feature) or Research (creates a pending brief). Verified live end-to-end.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="194.1346153846154" customHeight="1">
       <c r="A5" s="35" t="n">
@@ -3775,6 +3825,16 @@
           <t>Share of navigation and mode-start actions initiated via the palette vs. mouse (target &gt;30%).</t>
         </is>
       </c>
+      <c r="N5" s="134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O5" s="147" t="inlineStr">
+        <is>
+          <t>Superseded — Command Palette (⌘K) already ships.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="201.6346153846154" customHeight="1">
       <c r="A6" s="30" t="n">
@@ -3864,6 +3924,11 @@
           <t>Median active-day streak length per user and day-over-day return rate (target D1 return &gt;50%).</t>
         </is>
       </c>
+      <c r="N6" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="227.0192307692308" customHeight="1">
       <c r="A7" s="35" t="n">
@@ -3953,6 +4018,16 @@
           <t>Percentage of days the briefing is opened and at least one focus action is clicked (target &gt;45%).</t>
         </is>
       </c>
+      <c r="N7" s="134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O7" s="147" t="inlineStr">
+        <is>
+          <t>Superseded — Automations 'digest' action covers this.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="187.5" customHeight="1">
       <c r="A8" s="30" t="n">
@@ -4042,6 +4117,16 @@
           <t>Weekly timeline opens per active user and click-through rate from event to artifact (target CTR &gt;25%).</t>
         </is>
       </c>
+      <c r="N8" s="136" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="O8" s="147" t="inlineStr">
+        <is>
+          <t>New: cross-feature activity feed.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="188.6538461538462" customHeight="1">
       <c r="A9" s="35" t="n">
@@ -4131,6 +4216,16 @@
           <t>Percentage of active users with at least one pin and click-through rate on the Pinned strip (target &gt;35%).</t>
         </is>
       </c>
+      <c r="N9" s="136" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="O9" s="147" t="inlineStr">
+        <is>
+          <t>New: pins/favorites.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="185.4807692307692" customHeight="1">
       <c r="A10" s="30" t="n">
@@ -4220,6 +4315,16 @@
           <t>Weekly searches per active user and result click-through rate (target CTR &gt;50%).</t>
         </is>
       </c>
+      <c r="N10" s="134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O10" s="147" t="inlineStr">
+        <is>
+          <t>Superseded — Global Search already ships.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="214.3269230769231" customHeight="1">
       <c r="A11" s="35" t="n">
@@ -4309,6 +4414,16 @@
           <t>Percentage of new users who complete onboarding and return on day two (target activation-to-D1-return &gt;40%).</t>
         </is>
       </c>
+      <c r="N11" s="136" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="O11" s="147" t="inlineStr">
+        <is>
+          <t>New: first-run onboarding checklist.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="210.8653846153846" customHeight="1">
       <c r="A12" s="43" t="n">
@@ -4397,6 +4512,11 @@
           <t>70% of active projects have at least one manually edited node within the first week of use.</t>
         </is>
       </c>
+      <c r="N12" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="209.4230769230769" customHeight="1">
       <c r="A13" s="35" t="n">
@@ -4484,6 +4604,11 @@
       <c r="M13" s="36" t="inlineStr">
         <is>
           <t>40% of regenerations are section-level (vs full-document), showing users prefer targeted edits.</t>
+        </is>
+      </c>
+      <c r="N13" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -4577,6 +4702,11 @@
           <t>Restore is used in 20% of projects that have 5+ versions, indicating trust to edit freely.</t>
         </is>
       </c>
+      <c r="N14" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="194.4230769230769" customHeight="1">
       <c r="A15" s="35" t="n">
@@ -4666,6 +4796,11 @@
           <t>Users apply an AI refine action in 50% of editing sessions, showing daily assistant use.</t>
         </is>
       </c>
+      <c r="N15" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="210.8653846153846" customHeight="1">
       <c r="A16" s="43" t="n">
@@ -4755,6 +4890,11 @@
           <t>30% of returning users have at least one unresolved comment, indicating docs are a working surface.</t>
         </is>
       </c>
+      <c r="N16" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="202.2115384615385" customHeight="1">
       <c r="A17" s="35" t="n">
@@ -4844,6 +4984,11 @@
           <t>Median project has 3+ status transitions per week, showing docs move through a lifecycle.</t>
         </is>
       </c>
+      <c r="N17" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="175.0961538461538" customHeight="1">
       <c r="A18" s="43" t="n">
@@ -4930,6 +5075,11 @@
       <c r="M18" s="44" t="inlineStr">
         <is>
           <t>60% of editing sessions have preview enabled, showing it is part of the daily writing loop.</t>
+        </is>
+      </c>
+      <c r="N18" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -5023,6 +5173,11 @@
           <t>Average of 2+ cross-links per project after two weeks, showing docs become interconnected.</t>
         </is>
       </c>
+      <c r="N19" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="169.6153846153846" customHeight="1">
       <c r="A20" s="43" t="n">
@@ -5113,6 +5268,11 @@
           <t>40% of projects with 5+ nodes use at least one tag filter per week.</t>
         </is>
       </c>
+      <c r="N20" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="208.8461538461538" customHeight="1">
       <c r="A21" s="35" t="n">
@@ -5204,6 +5364,11 @@
           <t>25% of retained users create at least one custom document type within 30 days.</t>
         </is>
       </c>
+      <c r="N21" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="204.5192307692308" customHeight="1">
       <c r="A22" s="50" t="n">
@@ -5292,6 +5457,11 @@
           <t>70%+ of active users open the project copilot on 4+ distinct days per week, with median 3+ messages per session.</t>
         </is>
       </c>
+      <c r="N22" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="185.7692307692308" customHeight="1">
       <c r="A23" s="35" t="n">
@@ -5380,6 +5550,11 @@
           <t>40%+ of daily sessions include clicking a Next-Best-Action CTA, and suggested actions have a 25%+ same-day completion rate.</t>
         </is>
       </c>
+      <c r="N23" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="184.3269230769231" customHeight="1">
       <c r="A24" s="50" t="n">
@@ -5468,6 +5643,11 @@
           <t>Users who run AI-prioritize accept 60%+ of proposals and re-run it at least weekly, cutting median backlog-grooming time by 50%.</t>
         </is>
       </c>
+      <c r="N24" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="180.2884615384615" customHeight="1">
       <c r="A25" s="35" t="n">
@@ -5556,6 +5736,16 @@
           <t>Semantic search is used in 50%+ of daily sessions with a top-3 result click-through rate above 65%.</t>
         </is>
       </c>
+      <c r="N25" s="134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O25" s="147" t="inlineStr">
+        <is>
+          <t>Superseded — wigolo already does embeddings + reranking for search.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="158.0769230769231" customHeight="1">
       <c r="A26" s="50" t="n">
@@ -5644,6 +5834,11 @@
           <t>Summarize is triggered in 30%+ of sessions and 20%+ of generated summaries are inserted or copied, indicating real utility.</t>
         </is>
       </c>
+      <c r="N26" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="165.5769230769231" customHeight="1">
       <c r="A27" s="35" t="n">
@@ -5730,6 +5925,11 @@
       <c r="M27" s="36" t="inlineStr">
         <is>
           <t>25%+ of users with 2+ projects use the global copilot weekly, with at least 40% of queries resulting in a citation click.</t>
+        </is>
+      </c>
+      <c r="N27" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -5821,6 +6021,11 @@
           <t>20%+ of active users create or fork at least one custom prompt, and custom prompts drive 15%+ of all document generations.</t>
         </is>
       </c>
+      <c r="N28" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="172.5" customHeight="1">
       <c r="A29" s="35" t="n">
@@ -5910,6 +6115,11 @@
           <t>30%+ of users configure at least one non-default route, and routed tasks show a measurable median latency reduction for chat.</t>
         </is>
       </c>
+      <c r="N29" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="180.2884615384615" customHeight="1">
       <c r="A30" s="50" t="n">
@@ -5996,6 +6206,11 @@
       <c r="M30" s="51" t="inlineStr">
         <is>
           <t>Generation abandonment/regeneration drops 30% and 90%+ of streamed runs complete or are intentionally stopped (not failed).</t>
+        </is>
+      </c>
+      <c r="N30" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -6087,6 +6302,11 @@
           <t>15%+ of users open the metrics dashboard weekly, and users who view it are 2x more likely to adjust model routing.</t>
         </is>
       </c>
+      <c r="N31" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="216.6346153846154" customHeight="1">
       <c r="A32" s="56" t="n">
@@ -6176,6 +6396,16 @@
           <t>Median voice-capture latency (stop-to-node) under 2s and at least 30% of daily captures created via voice within 4 weeks of release</t>
         </is>
       </c>
+      <c r="N32" s="136" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="O32" s="147" t="inlineStr">
+        <is>
+          <t>Backend (whisper.cpp) already shipped; only the frontend page is missing.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="176.8269230769231" customHeight="1">
       <c r="A33" s="35" t="n">
@@ -6263,6 +6493,11 @@
           <t>At least 25% of daily captures arrive via clipboard/URL import and median URL-to-node time under 3s</t>
         </is>
       </c>
+      <c r="N33" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="165.5769230769231" customHeight="1">
       <c r="A34" s="56" t="n">
@@ -6351,6 +6586,11 @@
           <t>Median email-to-node time under 2s per message and at least 15% weekly active users using email drop within 6 weeks</t>
         </is>
       </c>
+      <c r="N34" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="167.5961538461538" customHeight="1">
       <c r="A35" s="35" t="n">
@@ -6439,6 +6679,11 @@
           <t>Median image-to-node latency under 3s and at least 20% of multimodal captures using OCR within 4 weeks</t>
         </is>
       </c>
+      <c r="N35" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="160.3846153846154" customHeight="1">
       <c r="A36" s="56" t="n">
@@ -6527,6 +6772,11 @@
           <t>Users can import 1000 ideas in under 10s and at least 40% of new users complete a bulk import in their first session</t>
         </is>
       </c>
+      <c r="N36" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="162.1153846153846" customHeight="1">
       <c r="A37" s="35" t="n">
@@ -6615,6 +6865,11 @@
           <t>Extension capture round-trip under 500ms and at least 20% of daily captures via extension for installed users</t>
         </is>
       </c>
+      <c r="N37" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="169.3269230769231" customHeight="1">
       <c r="A38" s="56" t="n">
@@ -6703,6 +6958,11 @@
           <t>Share-to-capture under 1s and at least 30% of active users capture from mobile weekly, improving overall capture retention</t>
         </is>
       </c>
+      <c r="N38" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="152.8846153846154" customHeight="1">
       <c r="A39" s="35" t="n">
@@ -6791,6 +7051,11 @@
           <t>At least 80% of extracted action items accepted without edits and median notes-to-items time under 8s</t>
         </is>
       </c>
+      <c r="N39" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="167.5961538461538" customHeight="1">
       <c r="A40" s="56" t="n">
@@ -6879,6 +7144,11 @@
           <t>At least 50% of new users start their first capture from a template and template-based captures show higher document-completion rates</t>
         </is>
       </c>
+      <c r="N40" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="162.4038461538462" customHeight="1">
       <c r="A41" s="35" t="n">
@@ -6965,6 +7235,11 @@
       <c r="M41" s="36" t="inlineStr">
         <is>
           <t>Duplicate rate in the backlog reduced by at least 30% and capture-time similarity check under 500ms at 10k nodes</t>
+        </is>
+      </c>
+      <c r="N41" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -7057,6 +7332,11 @@
           <t>70% of daily-active users open the Kanban board within 10 seconds of app launch and move at least one card per session.</t>
         </is>
       </c>
+      <c r="N42" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="163.8461538461538" customHeight="1">
       <c r="A43" s="35" t="n">
@@ -7146,6 +7426,11 @@
           <t>Weekly-active users view the roadmap at least twice per week, with median session including one reschedule action.</t>
         </is>
       </c>
+      <c r="N43" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="169.0384615384615" customHeight="1">
       <c r="A44" s="62" t="n">
@@ -7235,6 +7520,11 @@
           <t>60% of active projects have at least one active sprint, and users revisit the sprint dashboard on 4+ days per two-week sprint.</t>
         </is>
       </c>
+      <c r="N44" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="160.3846153846154" customHeight="1">
       <c r="A45" s="35" t="n">
@@ -7324,6 +7614,11 @@
           <t>Blocked items are resolved a median of 30% faster after launch, measured by time-in-blocked before vs after.</t>
         </is>
       </c>
+      <c r="N45" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="162.9807692307692" customHeight="1">
       <c r="A46" s="62" t="n">
@@ -7413,6 +7708,11 @@
           <t>Sprints planned with the capacity meter show 25% lower average over-commit (committed vs completed gap) than unplanned sprints.</t>
         </is>
       </c>
+      <c r="N46" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="169.9038461538462" customHeight="1">
       <c r="A47" s="35" t="n">
@@ -7502,6 +7802,11 @@
           <t>40% of large items created after launch are decomposed via WBS, and decomposed items reach Done at a higher rate than non-decomposed ones.</t>
         </is>
       </c>
+      <c r="N47" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="161.8269230769231" customHeight="1">
       <c r="A48" s="62" t="n">
@@ -7591,6 +7896,11 @@
           <t>50% of active users open the Today view on 4+ mornings per week (primary retention/toothbrush metric).</t>
         </is>
       </c>
+      <c r="N48" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="159.5192307692308" customHeight="1">
       <c r="A49" s="35" t="n">
@@ -7680,6 +7990,11 @@
           <t>35% of weekly-active users complete the ritual on 3+ consecutive Mondays, indicating a sticky weekly habit.</t>
         </is>
       </c>
+      <c r="N49" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="155.1923076923077" customHeight="1">
       <c r="A50" s="62" t="n">
@@ -7769,6 +8084,11 @@
           <t>55% of active projects define at least one objective, and 30% of completed items are linked to a key result.</t>
         </is>
       </c>
+      <c r="N50" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="167.0192307692308" customHeight="1">
       <c r="A51" s="35" t="n">
@@ -7858,6 +8178,11 @@
           <t>40% of weekly-active users open Analytics at least once per week, and forecast accuracy (predicted vs actual sprint completion) improves over time.</t>
         </is>
       </c>
+      <c r="N51" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="175.6730769230769" customHeight="1">
       <c r="A52" s="68" t="n">
@@ -7947,6 +8272,11 @@
           <t>60% of active users who connect GitHub run at least one sync per week within 30 days; median &lt;2 min from backlog item to GitHub issue.</t>
         </is>
       </c>
+      <c r="N52" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="162.6923076923077" customHeight="1">
       <c r="A53" s="35" t="n">
@@ -8036,6 +8366,11 @@
           <t>70% of merged PRs in connected repos auto-link to a Dobby item; loop-closure (idea-&gt;merged) visible for 50% of shipped items.</t>
         </is>
       </c>
+      <c r="N53" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="158.6538461538462" customHeight="1">
       <c r="A54" s="68" t="n">
@@ -8125,6 +8460,11 @@
           <t>50% of teams that connect Jira sync weekly for 4+ weeks; &lt;5% export failures after field-mapping validation.</t>
         </is>
       </c>
+      <c r="N54" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="143.9423076923077" customHeight="1">
       <c r="A55" s="35" t="n">
@@ -8214,6 +8554,11 @@
           <t>55% of Linear-connected users sync weekly for a month; median sync reconciliation lag &lt;15 min.</t>
         </is>
       </c>
+      <c r="N55" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="151.7307692307692" customHeight="1">
       <c r="A56" s="68" t="n">
@@ -8303,6 +8648,11 @@
           <t>40% of exported documents are re-exported (updated) at least once, indicating living-doc usage; &lt;3% duplicate-page rate.</t>
         </is>
       </c>
+      <c r="N56" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="159.5192307692308" customHeight="1">
       <c r="A57" s="35" t="n">
@@ -8392,6 +8742,16 @@
           <t>Teams with Slack digests enabled show 25% higher weekly Dobby open rate; 90%+ message delivery success.</t>
         </is>
       </c>
+      <c r="N57" s="134" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O57" s="147" t="inlineStr">
+        <is>
+          <t>Superseded — Slack/Telegram connectors + Automations digest already ship.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="158.0769230769231" customHeight="1">
       <c r="A58" s="68" t="n">
@@ -8481,6 +8841,11 @@
           <t>35% of users who connect a calendar schedule at least 3 blocks per week; 50% of scheduled blocks result in a status update.</t>
         </is>
       </c>
+      <c r="N58" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="152.8846153846154" customHeight="1">
       <c r="A59" s="35" t="n">
@@ -8570,6 +8935,11 @@
           <t>20% of power users configure at least one webhook; 95%+ eventual delivery success including retries.</t>
         </is>
       </c>
+      <c r="N59" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="148.5576923076923" customHeight="1">
       <c r="A60" s="68" t="n">
@@ -8659,6 +9029,11 @@
           <t>15% of active developers generate an API key; 30% of those make API calls in 3+ distinct weeks (retention via scripting).</t>
         </is>
       </c>
+      <c r="N60" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="175.3846153846154" customHeight="1">
       <c r="A61" s="35" t="n">
@@ -8748,6 +9123,11 @@
           <t>30% of users with 2+ integrations create a recipe; recipe-active users show 40% higher 30-day retention (loop-closure).</t>
         </is>
       </c>
+      <c r="N61" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="236.8269230769231" customHeight="1">
       <c r="A62" s="74" t="n">
@@ -8836,6 +9216,11 @@
           <t>Within 30 days of release, 60% of multi-project users create at least 2 workspaces, and weekly workspace switches per active user average 5+ (proxy for daily return usage).</t>
         </is>
       </c>
+      <c r="N62" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="229.3269230769231" customHeight="1">
       <c r="A63" s="35" t="n">
@@ -8926,6 +9311,11 @@
           <t>Median time-to-share under 20 seconds, and 40% of shared links are opened by at least one recipient within 48 hours, indicating real review activity.</t>
         </is>
       </c>
+      <c r="N63" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="207.6923076923077" customHeight="1">
       <c r="A64" s="74" t="n">
@@ -9016,6 +9406,11 @@
           <t>Within 30 days, 50% of workspaces with sharing enabled have 2+ members, and 70% of invited members accept and take at least one action (edit/comment).</t>
         </is>
       </c>
+      <c r="N64" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="215.1923076923077" customHeight="1">
       <c r="A65" s="35" t="n">
@@ -9106,6 +9501,11 @@
           <t>Among multi-member workspaces, 30% run at least one co-editing session weekly, with median concurrent-edit sessions lasting 5+ minutes.</t>
         </is>
       </c>
+      <c r="N65" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="196.1538461538462" customHeight="1">
       <c r="A66" s="74" t="n">
@@ -9196,6 +9596,11 @@
           <t>50% of published documents pass through at least one approval, and reviewers return to clear their queue on 3+ distinct days per week on average.</t>
         </is>
       </c>
+      <c r="N66" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="202.2115384615385" customHeight="1">
       <c r="A67" s="35" t="n">
@@ -9286,6 +9691,11 @@
           <t>40% of active projects generate release notes at least monthly, and generated notes are edited-and-kept (not discarded) 75% of the time.</t>
         </is>
       </c>
+      <c r="N67" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="201.0576923076923" customHeight="1">
       <c r="A68" s="74" t="n">
@@ -9376,6 +9786,11 @@
           <t>60% of team workspaces publish a docs site within 30 days, and published sites average 4+ distinct team viewers per week.</t>
         </is>
       </c>
+      <c r="N68" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="188.9423076923077" customHeight="1">
       <c r="A69" s="35" t="n">
@@ -9466,6 +9881,11 @@
           <t>PDF export completes in under 10 seconds for a typical project, and 35% of teams export at least one PDF per month for reviews or archives.</t>
         </is>
       </c>
+      <c r="N69" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="195.2884615384615" customHeight="1">
       <c r="A70" s="74" t="n">
@@ -9556,6 +9976,11 @@
           <t>Exported bundles make zero network requests in automated checks, and 30% of teams export an offline bundle within 30 days for external sharing.</t>
         </is>
       </c>
+      <c r="N70" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="198.4615384615385" customHeight="1">
       <c r="A71" s="35" t="n">
@@ -9644,6 +10069,11 @@
       <c r="M71" s="36" t="inlineStr">
         <is>
           <t>50% of notifications are acted on within 24 hours, and workspaces with mentions enabled show 20% higher weekly team DAU than those without.</t>
+        </is>
+      </c>
+      <c r="N71" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -9735,6 +10165,11 @@
           <t>Day-2 return rate: +15% for users with reminders enabled vs. disabled; notification→open rate &gt;= 35%.</t>
         </is>
       </c>
+      <c r="N72" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="183.75" customHeight="1">
       <c r="A73" s="35" t="n">
@@ -9824,6 +10259,11 @@
           <t>Week-over-week (WAU) retention +10% among recap viewers; recap notification→open rate &gt;= 30%.</t>
         </is>
       </c>
+      <c r="N73" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="166.7307692307692" customHeight="1">
       <c r="A74" s="80" t="n">
@@ -9913,6 +10353,11 @@
           <t>Day-7 return rate +12% for users who unlock &gt;=1 badge in week 1; average badges-per-active-user &gt;= 3 by day 30.</t>
         </is>
       </c>
+      <c r="N74" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="155.7692307692308" customHeight="1">
       <c r="A75" s="35" t="n">
@@ -10002,6 +10447,11 @@
           <t>Card click-through rate &gt;= 20%; day-2 return rate +8% among users shown an 'On This Day' card.</t>
         </is>
       </c>
+      <c r="N75" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="161.25" customHeight="1">
       <c r="A76" s="80" t="n">
@@ -10091,6 +10541,11 @@
           <t>Users who run &gt;=3 focus sessions in week 1 have +18% day-7 retention; average focus sessions per WAU &gt;= 2.</t>
         </is>
       </c>
+      <c r="N76" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="160.9615384615385" customHeight="1">
       <c r="A77" s="35" t="n">
@@ -10180,6 +10635,11 @@
           <t>Users who customize appearance in week 1 show +10% day-30 retention; &gt;=40% of active users set a non-default preference.</t>
         </is>
       </c>
+      <c r="N77" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="156.3461538461538" customHeight="1">
       <c r="A78" s="80" t="n">
@@ -10270,6 +10730,11 @@
           <t>Power users (&gt;=5 shortcut uses/session) have +20% day-7 retention; &gt;=25% of WAU use the command palette weekly.</t>
         </is>
       </c>
+      <c r="N78" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="160.9615384615385" customHeight="1">
       <c r="A79" s="35" t="n">
@@ -10359,6 +10824,11 @@
           <t>Users with the widget enabled open Dobby +25% more days/week; widget→open rate contributes &gt;=30% of daily sessions.</t>
         </is>
       </c>
+      <c r="N79" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="157.2115384615385" customHeight="1">
       <c r="A80" s="80" t="n">
@@ -10448,6 +10918,11 @@
           <t>Share action used by &gt;=8% of streak-holders/month; referral-attributed installs from shared cards trend upward month-over-month.</t>
         </is>
       </c>
+      <c r="N80" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="174.8076923076923" customHeight="1">
       <c r="A81" s="35" t="n">
@@ -10537,6 +11012,11 @@
           <t>Notification opt-out rate &lt; 15%; overall notification→open rate &gt;= 30% while maintaining or improving day-7 retention.</t>
         </is>
       </c>
+      <c r="N81" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="222.1153846153846" customHeight="1">
       <c r="A82" s="87" t="n">
@@ -10626,6 +11106,11 @@
           <t>90% of verification sessions result in the user opening at least one check's findings; report panel loads in &lt;300ms for 95th-percentile document size.</t>
         </is>
       </c>
+      <c r="N82" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="195" customHeight="1">
       <c r="A83" s="35" t="n">
@@ -10715,6 +11200,11 @@
           <t>Power users create at least 3 custom rules per active project on average; 100% of custom-rule runs are reproducible across repeated runs.</t>
         </is>
       </c>
+      <c r="N83" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="186.6346153846154" customHeight="1">
       <c r="A84" s="87" t="n">
@@ -10804,6 +11294,11 @@
           <t>Detects 100% of dangling citations and &gt;90% of injected conflicting-number claims in the test corpus, with zero network calls.</t>
         </is>
       </c>
+      <c r="N84" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="188.0769230769231" customHeight="1">
       <c r="A85" s="35" t="n">
@@ -10893,6 +11388,11 @@
           <t>Cross-document contradiction detection recall &gt;85% on the test corpus; project check completes in &lt;2s for a standard 7-doc project.</t>
         </is>
       </c>
+      <c r="N85" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="203.3653846153846" customHeight="1">
       <c r="A86" s="87" t="n">
@@ -10982,6 +11482,11 @@
           <t>&gt;70% of auto-fixable findings are resolved via one-click fix; applying a fix improves or maintains the score in 100% of cases.</t>
         </is>
       </c>
+      <c r="N86" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="186.6346153846154" customHeight="1">
       <c r="A87" s="35" t="n">
@@ -11071,6 +11576,11 @@
           <t>Batch verify processes 20 documents at least 5x faster than one-by-one runs; zero data corruption across cancel/failure test scenarios.</t>
         </is>
       </c>
+      <c r="N87" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="193.5576923076923" customHeight="1">
       <c r="A88" s="87" t="n">
@@ -11160,6 +11670,11 @@
           <t>100% of export/import round-trips restore identical verifier scores and audit history; zero data loss across the migration and corruption test suite.</t>
         </is>
       </c>
+      <c r="N88" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="182.8846153846154" customHeight="1">
       <c r="A89" s="35" t="n">
@@ -11249,6 +11764,11 @@
           <t>Encrypted store is unreadable without the passphrase in security review; unlock &lt;1.5s and steady-state read overhead &lt;10% versus unencrypted.</t>
         </is>
       </c>
+      <c r="N89" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="189.5192307692308" customHeight="1">
       <c r="A90" s="87" t="n">
@@ -11338,6 +11858,11 @@
           <t>Incremental sync transfers only changed items (&gt;95% bandwidth saved vs full copy) and resolves 100% of conflicts with zero data loss in tests.</t>
         </is>
       </c>
+      <c r="N90" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="192.6923076923077" customHeight="1">
       <c r="A91" s="35" t="n">
@@ -11427,6 +11952,11 @@
           <t>100% of destructive actions are reversible via undo or Trash restore; undo/redo persists across restarts with zero unrecoverable data loss in tests.</t>
         </is>
       </c>
+      <c r="N91" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="197.8846153846154" customHeight="1">
       <c r="A92" s="94" t="n">
@@ -11516,6 +12046,11 @@
           <t>At least 5 working community plugins installed and run offline by 20% of active users within 60 days of release.</t>
         </is>
       </c>
+      <c r="N92" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="194.7115384615385" customHeight="1">
       <c r="A93" s="35" t="n">
@@ -11605,6 +12140,11 @@
           <t>30% of active users create at least one custom pipeline within 30 days, averaging 2+ runs each.</t>
         </is>
       </c>
+      <c r="N93" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="188.6538461538462" customHeight="1">
       <c r="A94" s="94" t="n">
@@ -11693,6 +12233,11 @@
           <t>40% of active users install at least one marketplace item; average of 3 installs per installing user within 60 days.</t>
         </is>
       </c>
+      <c r="N94" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="206.8269230769231" customHeight="1">
       <c r="A95" s="35" t="n">
@@ -11781,6 +12326,11 @@
           <t>Non-English generations account for 15% of all documents produced within 90 days; UI used in 3+ locales.</t>
         </is>
       </c>
+      <c r="N95" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="181.4423076923077" customHeight="1">
       <c r="A96" s="94" t="n">
@@ -11869,6 +12419,11 @@
           <t>60% of new users install a model via one-click within their first session; median time-to-first-model under 5 minutes.</t>
         </is>
       </c>
+      <c r="N96" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="176.5384615384615" customHeight="1">
       <c r="A97" s="35" t="n">
@@ -11957,6 +12512,11 @@
           <t>In team deployments, 70% of teams import a config bundle and at least one usage rollup within 30 days.</t>
         </is>
       </c>
+      <c r="N97" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="177.1153846153846" customHeight="1">
       <c r="A98" s="94" t="n">
@@ -12045,6 +12605,11 @@
           <t>25% of surfaced recommendations are accepted; users who engage generate 20% more documents than non-engagers.</t>
         </is>
       </c>
+      <c r="N98" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="184.3269230769231" customHeight="1">
       <c r="A99" s="35" t="n">
@@ -12133,6 +12698,11 @@
           <t>50% of active users create at least one goal; goal-users retain a 7-day streak at 2x the rate of non-goal users.</t>
         </is>
       </c>
+      <c r="N99" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="188.3653846153846" customHeight="1">
       <c r="A100" s="94" t="n">
@@ -12219,6 +12789,11 @@
       <c r="M100" s="95" t="inlineStr">
         <is>
           <t>Help deflects 60% of would-be support questions; 70% of answers rated helpful, all served offline.</t>
+        </is>
+      </c>
+      <c r="N100" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -12308,6 +12883,11 @@
       <c r="M101" s="36" t="inlineStr">
         <is>
           <t>North-star: Dobby is the first app opened on 40% of the user's working days within 90 days, with 35% of DAU completing the ritual and a median active streak of 5+ days.</t>
+        </is>
+      </c>
+      <c r="N101" s="146" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -4119,12 +4119,12 @@
       </c>
       <c r="N8" s="136" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="O8" s="147" t="inlineStr">
         <is>
-          <t>New: cross-feature activity feed.</t>
+          <t>Activity Timeline shipped as a derived feed over ideas/backlog/runs/research (not a generic audit-log wiring — see the code comment for why). Category filter + cursor pagination + deep links verified live.</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -4218,12 +4218,12 @@
       </c>
       <c r="N9" s="136" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="O9" s="147" t="inlineStr">
         <is>
-          <t>New: pins/favorites.</t>
+          <t>Pins shipped as a generic Pin(entity_type, entity_id, order_index) across ideas/features/documents. Pinned strip on Dashboard, keyboard reorder (arrow buttons, not drag-only), dangling-pin cleanup on read, and command-palette boost — all verified live.</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -3530,12 +3530,12 @@
       </c>
       <c r="N2" s="136" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="O2" s="147" t="inlineStr">
         <is>
-          <t>Dashboard has a 'Today's priority' card; upgrading to a real daily agenda.</t>
+          <t>Today Home shipped: single GET /projects/{id}/home aggregating pending asks, untriaged ideas, in-flight sessions, failed runs, and top-Pareto backlog. Every section capped. Time-aware greeting and clean-slate state. Verified live.</t>
         </is>
       </c>
     </row>
@@ -6398,12 +6398,12 @@
       </c>
       <c r="N32" s="136" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="O32" s="147" t="inlineStr">
         <is>
-          <t>Backend (whisper.cpp) already shipped; only the frontend page is missing.</t>
+          <t>Transcribe page shipped this batch (whisper.cpp, fully offline) — model download, upload, segment transcript. Verified end-to-end with real synthesized audio.</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -4416,12 +4416,12 @@
       </c>
       <c r="N11" s="136" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="O11" s="147" t="inlineStr">
         <is>
-          <t>New: first-run onboarding checklist.</t>
+          <t>Onboarding checklist shipped. Step completion is derived from real data (an Idea row exists, a Node exists) rather than a stored checklist, so it can never disagree with the app. Only the dismissed flag is persisted. Verified live: capturing an idea flipped 2/4 to 3/4.</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -226,6 +226,27 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00166534"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -410,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -813,6 +834,15 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3344,7 +3374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3362,6 +3392,7 @@
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3438,6 +3469,11 @@
       <c r="O1" s="141" t="inlineStr">
         <is>
           <t>Note</t>
+        </is>
+      </c>
+      <c r="P1" s="148" t="inlineStr">
+        <is>
+          <t>Lane</t>
         </is>
       </c>
     </row>
@@ -3538,6 +3574,11 @@
           <t>Today Home shipped: single GET /projects/{id}/home aggregating pending asks, untriaged ideas, in-flight sessions, failed runs, and top-Pareto backlog. Every section capped. Time-aware greeting and clean-slate state. Verified live.</t>
         </is>
       </c>
+      <c r="P2" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="222.1153846153846" customHeight="1">
       <c r="A3" s="35" t="n">
@@ -3637,6 +3678,11 @@
           <t>In-app quick-capture shipped (⌘I overlay, works from any page). OS-global hotkey still deferred — needs the Tauri capabilities work already deferred for reveal-in-Finder.</t>
         </is>
       </c>
+      <c r="P3" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="216.3461538461538" customHeight="1">
       <c r="A4" s="30" t="n">
@@ -3736,6 +3782,11 @@
           <t>Idea Inbox shipped: capture, list by status, triage into Backlog (Pareto-scored feature) or Research (creates a pending brief). Verified live end-to-end.</t>
         </is>
       </c>
+      <c r="P4" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="194.1346153846154" customHeight="1">
       <c r="A5" s="35" t="n">
@@ -3835,6 +3886,11 @@
           <t>Superseded — Command Palette (⌘K) already ships.</t>
         </is>
       </c>
+      <c r="P5" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="201.6346153846154" customHeight="1">
       <c r="A6" s="30" t="n">
@@ -3926,7 +3982,17 @@
       </c>
       <c r="N6" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Streak + 14-day sparkline on Today Home. Derived from the Activity Timeline feed (AuditEntry never recorded ideas/runs/research, so it was the wrong source). Day boundaries use a client-supplied UTC offset; 21 tests cover all 6 roadmap test cases.</t>
+        </is>
+      </c>
+      <c r="P6" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
         </is>
       </c>
     </row>
@@ -4028,6 +4094,11 @@
           <t>Superseded — Automations 'digest' action covers this.</t>
         </is>
       </c>
+      <c r="P7" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="187.5" customHeight="1">
       <c r="A8" s="30" t="n">
@@ -4127,6 +4198,11 @@
           <t>Activity Timeline shipped as a derived feed over ideas/backlog/runs/research (not a generic audit-log wiring — see the code comment for why). Category filter + cursor pagination + deep links verified live.</t>
         </is>
       </c>
+      <c r="P8" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="188.6538461538462" customHeight="1">
       <c r="A9" s="35" t="n">
@@ -4226,6 +4302,11 @@
           <t>Pins shipped as a generic Pin(entity_type, entity_id, order_index) across ideas/features/documents. Pinned strip on Dashboard, keyboard reorder (arrow buttons, not drag-only), dangling-pin cleanup on read, and command-palette boost — all verified live.</t>
         </is>
       </c>
+      <c r="P9" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="185.4807692307692" customHeight="1">
       <c r="A10" s="30" t="n">
@@ -4325,6 +4406,11 @@
           <t>Superseded — Global Search already ships.</t>
         </is>
       </c>
+      <c r="P10" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="214.3269230769231" customHeight="1">
       <c r="A11" s="35" t="n">
@@ -4424,6 +4510,11 @@
           <t>Onboarding checklist shipped. Step completion is derived from real data (an Idea row exists, a Node exists) rather than a stored checklist, so it can never disagree with the app. Only the dismissed flag is persisted. Verified live: capturing an idea flipped 2/4 to 3/4.</t>
         </is>
       </c>
+      <c r="P11" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="210.8653846153846" customHeight="1">
       <c r="A12" s="43" t="n">
@@ -4517,6 +4608,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P12" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="209.4230769230769" customHeight="1">
       <c r="A13" s="35" t="n">
@@ -4609,6 +4705,11 @@
       <c r="N13" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P13" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
         </is>
       </c>
     </row>
@@ -4707,6 +4808,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P14" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="194.4230769230769" customHeight="1">
       <c r="A15" s="35" t="n">
@@ -4801,6 +4907,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P15" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="210.8653846153846" customHeight="1">
       <c r="A16" s="43" t="n">
@@ -4895,6 +5006,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P16" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="202.2115384615385" customHeight="1">
       <c r="A17" s="35" t="n">
@@ -4989,6 +5105,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P17" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="175.0961538461538" customHeight="1">
       <c r="A18" s="43" t="n">
@@ -5080,6 +5201,11 @@
       <c r="N18" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P18" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
         </is>
       </c>
     </row>
@@ -5178,6 +5304,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P19" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="169.6153846153846" customHeight="1">
       <c r="A20" s="43" t="n">
@@ -5273,6 +5404,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P20" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="208.8461538461538" customHeight="1">
       <c r="A21" s="35" t="n">
@@ -5369,6 +5505,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P21" s="149" t="inlineStr">
+        <is>
+          <t>Lane B — Documents &amp; Editor</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="204.5192307692308" customHeight="1">
       <c r="A22" s="50" t="n">
@@ -5462,6 +5603,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P22" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="185.7692307692308" customHeight="1">
       <c r="A23" s="35" t="n">
@@ -5555,6 +5701,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P23" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="184.3269230769231" customHeight="1">
       <c r="A24" s="50" t="n">
@@ -5648,6 +5799,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P24" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="180.2884615384615" customHeight="1">
       <c r="A25" s="35" t="n">
@@ -5746,6 +5902,11 @@
           <t>Superseded — wigolo already does embeddings + reranking for search.</t>
         </is>
       </c>
+      <c r="P25" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="158.0769230769231" customHeight="1">
       <c r="A26" s="50" t="n">
@@ -5839,6 +6000,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P26" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="165.5769230769231" customHeight="1">
       <c r="A27" s="35" t="n">
@@ -5930,6 +6096,11 @@
       <c r="N27" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P27" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
         </is>
       </c>
     </row>
@@ -6026,6 +6197,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P28" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="172.5" customHeight="1">
       <c r="A29" s="35" t="n">
@@ -6120,6 +6296,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P29" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="180.2884615384615" customHeight="1">
       <c r="A30" s="50" t="n">
@@ -6211,6 +6392,11 @@
       <c r="N30" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P30" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
         </is>
       </c>
     </row>
@@ -6307,6 +6493,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P31" s="149" t="inlineStr">
+        <is>
+          <t>Lane C — AI Copilot &amp; Model Ops</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="216.6346153846154" customHeight="1">
       <c r="A32" s="56" t="n">
@@ -6406,6 +6597,11 @@
           <t>Transcribe page shipped this batch (whisper.cpp, fully offline) — model download, upload, segment transcript. Verified end-to-end with real synthesized audio.</t>
         </is>
       </c>
+      <c r="P32" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="176.8269230769231" customHeight="1">
       <c r="A33" s="35" t="n">
@@ -6498,6 +6694,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P33" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="165.5769230769231" customHeight="1">
       <c r="A34" s="56" t="n">
@@ -6591,6 +6792,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P34" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="167.5961538461538" customHeight="1">
       <c r="A35" s="35" t="n">
@@ -6684,6 +6890,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P35" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="160.3846153846154" customHeight="1">
       <c r="A36" s="56" t="n">
@@ -6777,6 +6988,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P36" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="162.1153846153846" customHeight="1">
       <c r="A37" s="35" t="n">
@@ -6870,6 +7086,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P37" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="169.3269230769231" customHeight="1">
       <c r="A38" s="56" t="n">
@@ -6963,6 +7184,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P38" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="152.8846153846154" customHeight="1">
       <c r="A39" s="35" t="n">
@@ -7056,6 +7282,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P39" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="167.5961538461538" customHeight="1">
       <c r="A40" s="56" t="n">
@@ -7149,6 +7380,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P40" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="162.4038461538462" customHeight="1">
       <c r="A41" s="35" t="n">
@@ -7240,6 +7476,11 @@
       <c r="N41" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P41" s="149" t="inlineStr">
+        <is>
+          <t>Lane A — Daily Home &amp; Capture</t>
         </is>
       </c>
     </row>
@@ -7337,6 +7578,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P42" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="163.8461538461538" customHeight="1">
       <c r="A43" s="35" t="n">
@@ -7431,6 +7677,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P43" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="169.0384615384615" customHeight="1">
       <c r="A44" s="62" t="n">
@@ -7525,6 +7776,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P44" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="160.3846153846154" customHeight="1">
       <c r="A45" s="35" t="n">
@@ -7619,6 +7875,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P45" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="162.9807692307692" customHeight="1">
       <c r="A46" s="62" t="n">
@@ -7713,6 +7974,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P46" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="169.9038461538462" customHeight="1">
       <c r="A47" s="35" t="n">
@@ -7807,6 +8073,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P47" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="161.8269230769231" customHeight="1">
       <c r="A48" s="62" t="n">
@@ -7901,6 +8172,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P48" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="159.5192307692308" customHeight="1">
       <c r="A49" s="35" t="n">
@@ -7995,6 +8271,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P49" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="155.1923076923077" customHeight="1">
       <c r="A50" s="62" t="n">
@@ -8089,6 +8370,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P50" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="167.0192307692308" customHeight="1">
       <c r="A51" s="35" t="n">
@@ -8183,6 +8469,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P51" s="149" t="inlineStr">
+        <is>
+          <t>Lane D — Planning &amp; PM</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="175.6730769230769" customHeight="1">
       <c r="A52" s="68" t="n">
@@ -8277,6 +8568,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P52" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="162.6923076923077" customHeight="1">
       <c r="A53" s="35" t="n">
@@ -8371,6 +8667,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P53" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="158.6538461538462" customHeight="1">
       <c r="A54" s="68" t="n">
@@ -8465,6 +8766,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P54" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="143.9423076923077" customHeight="1">
       <c r="A55" s="35" t="n">
@@ -8559,6 +8865,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P55" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="151.7307692307692" customHeight="1">
       <c r="A56" s="68" t="n">
@@ -8653,6 +8964,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P56" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="159.5192307692308" customHeight="1">
       <c r="A57" s="35" t="n">
@@ -8752,6 +9068,11 @@
           <t>Superseded — Slack/Telegram connectors + Automations digest already ship.</t>
         </is>
       </c>
+      <c r="P57" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="158.0769230769231" customHeight="1">
       <c r="A58" s="68" t="n">
@@ -8846,6 +9167,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P58" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="152.8846153846154" customHeight="1">
       <c r="A59" s="35" t="n">
@@ -8940,6 +9266,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P59" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="148.5576923076923" customHeight="1">
       <c r="A60" s="68" t="n">
@@ -9034,6 +9365,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P60" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="175.3846153846154" customHeight="1">
       <c r="A61" s="35" t="n">
@@ -9128,6 +9464,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P61" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="236.8269230769231" customHeight="1">
       <c r="A62" s="74" t="n">
@@ -9221,6 +9562,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P62" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="229.3269230769231" customHeight="1">
       <c r="A63" s="35" t="n">
@@ -9316,6 +9662,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P63" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="207.6923076923077" customHeight="1">
       <c r="A64" s="74" t="n">
@@ -9411,6 +9762,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P64" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="215.1923076923077" customHeight="1">
       <c r="A65" s="35" t="n">
@@ -9506,6 +9862,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P65" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="196.1538461538462" customHeight="1">
       <c r="A66" s="74" t="n">
@@ -9601,6 +9962,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P66" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="202.2115384615385" customHeight="1">
       <c r="A67" s="35" t="n">
@@ -9696,6 +10062,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P67" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="201.0576923076923" customHeight="1">
       <c r="A68" s="74" t="n">
@@ -9791,6 +10162,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P68" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="188.9423076923077" customHeight="1">
       <c r="A69" s="35" t="n">
@@ -9886,6 +10262,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P69" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="195.2884615384615" customHeight="1">
       <c r="A70" s="74" t="n">
@@ -9981,6 +10362,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P70" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="198.4615384615385" customHeight="1">
       <c r="A71" s="35" t="n">
@@ -10074,6 +10460,11 @@
       <c r="N71" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P71" s="149" t="inlineStr">
+        <is>
+          <t>Lane E — Integrations &amp; Server</t>
         </is>
       </c>
     </row>
@@ -10170,6 +10561,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P72" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="183.75" customHeight="1">
       <c r="A73" s="35" t="n">
@@ -10264,6 +10660,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P73" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="166.7307692307692" customHeight="1">
       <c r="A74" s="80" t="n">
@@ -10358,6 +10759,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P74" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="155.7692307692308" customHeight="1">
       <c r="A75" s="35" t="n">
@@ -10452,6 +10858,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P75" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="161.25" customHeight="1">
       <c r="A76" s="80" t="n">
@@ -10546,6 +10957,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P76" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="160.9615384615385" customHeight="1">
       <c r="A77" s="35" t="n">
@@ -10640,6 +11056,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P77" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="156.3461538461538" customHeight="1">
       <c r="A78" s="80" t="n">
@@ -10735,6 +11156,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P78" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="160.9615384615385" customHeight="1">
       <c r="A79" s="35" t="n">
@@ -10829,6 +11255,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P79" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="157.2115384615385" customHeight="1">
       <c r="A80" s="80" t="n">
@@ -10923,6 +11354,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P80" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="174.8076923076923" customHeight="1">
       <c r="A81" s="35" t="n">
@@ -11017,6 +11453,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P81" s="149" t="inlineStr">
+        <is>
+          <t>Lane F — Habit &amp; Delight</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="222.1153846153846" customHeight="1">
       <c r="A82" s="87" t="n">
@@ -11111,6 +11552,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P82" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="195" customHeight="1">
       <c r="A83" s="35" t="n">
@@ -11205,6 +11651,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P83" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="186.6346153846154" customHeight="1">
       <c r="A84" s="87" t="n">
@@ -11299,6 +11750,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P84" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="188.0769230769231" customHeight="1">
       <c r="A85" s="35" t="n">
@@ -11393,6 +11849,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P85" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="203.3653846153846" customHeight="1">
       <c r="A86" s="87" t="n">
@@ -11487,6 +11948,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P86" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="186.6346153846154" customHeight="1">
       <c r="A87" s="35" t="n">
@@ -11581,6 +12047,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P87" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="193.5576923076923" customHeight="1">
       <c r="A88" s="87" t="n">
@@ -11675,6 +12146,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P88" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="182.8846153846154" customHeight="1">
       <c r="A89" s="35" t="n">
@@ -11769,6 +12245,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P89" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="189.5192307692308" customHeight="1">
       <c r="A90" s="87" t="n">
@@ -11863,6 +12344,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P90" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="192.6923076923077" customHeight="1">
       <c r="A91" s="35" t="n">
@@ -11957,6 +12443,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P91" s="149" t="inlineStr">
+        <is>
+          <t>Lane G — Quality &amp; Trust</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="197.8846153846154" customHeight="1">
       <c r="A92" s="94" t="n">
@@ -12051,6 +12542,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P92" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="194.7115384615385" customHeight="1">
       <c r="A93" s="35" t="n">
@@ -12145,6 +12641,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P93" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="188.6538461538462" customHeight="1">
       <c r="A94" s="94" t="n">
@@ -12238,6 +12739,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P94" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="206.8269230769231" customHeight="1">
       <c r="A95" s="35" t="n">
@@ -12331,6 +12837,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P95" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="181.4423076923077" customHeight="1">
       <c r="A96" s="94" t="n">
@@ -12424,6 +12935,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P96" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="176.5384615384615" customHeight="1">
       <c r="A97" s="35" t="n">
@@ -12517,6 +13033,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P97" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="177.1153846153846" customHeight="1">
       <c r="A98" s="94" t="n">
@@ -12610,6 +13131,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P98" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="184.3269230769231" customHeight="1">
       <c r="A99" s="35" t="n">
@@ -12703,6 +13229,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="P99" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="188.3653846153846" customHeight="1">
       <c r="A100" s="94" t="n">
@@ -12794,6 +13325,11 @@
       <c r="N100" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P100" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
         </is>
       </c>
     </row>
@@ -12888,6 +13424,11 @@
       <c r="N101" s="146" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+      <c r="P101" s="149" t="inlineStr">
+        <is>
+          <t>Lane H — Scale &amp; Ecosystem</t>
         </is>
       </c>
     </row>
@@ -13000,7 +13541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13008,12 +13549,13 @@
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="115" t="inlineStr">
-        <is>
-          <t>Interactive Mind Mapping — planned feature (docs verified 2026-07-25; status 0/47 steps, nothing built yet)</t>
+      <c r="A1" s="150" t="inlineStr">
+        <is>
+          <t>Interactive Mind Mapping — SHIPPED (verified 2026-07-27). All 3 phases built: canvas CRUD, AI generate/expand/regroup/chat-edit, export JSON/Markdown/Mermaid/PNG/SVG + import with validation.</t>
         </is>
       </c>
     </row>
@@ -13133,6 +13675,11 @@
           <t>Roadmap placement</t>
         </is>
       </c>
+      <c r="F10" s="151" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="67.5" customHeight="1">
       <c r="A11" s="108" t="inlineStr">
@@ -13160,6 +13707,11 @@
           <t>Extends 100-Day Roadmap Phase 2 'Living Documents' (Days 11–20) — a visual editing surface alongside the text docs.</t>
         </is>
       </c>
+      <c r="F11" s="152" t="inlineStr">
+        <is>
+          <t>Done — React Flow canvas, node inspector, toolbar, shortcuts, persistence</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="62.7" customHeight="1">
       <c r="A12" s="108" t="inlineStr">
@@ -13187,6 +13739,11 @@
           <t>Pairs with Phase 3 'AI Copilot' (Days 21–30) — reuses the local LLM + next-best-action theme.</t>
         </is>
       </c>
+      <c r="F12" s="152" t="inlineStr">
+        <is>
+          <t>Done — generate_map / expand_node / regroup_map / chat_edit via local Ollama</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="66" customHeight="1">
       <c r="A13" s="108" t="inlineStr">
@@ -13212,6 +13769,11 @@
       <c r="E13" s="119" t="inlineStr">
         <is>
           <t>Feeds Phase 7 'Collaboration &amp; Sharing' (Days 61–70) export/publish and project-level exports.</t>
+        </is>
+      </c>
+      <c r="F13" s="152" t="inlineStr">
+        <is>
+          <t>Done — JSON/Markdown/Mermaid server-side; PNG/SVG client-side; import validated</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -4605,7 +4605,12 @@
       </c>
       <c r="N12" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Split-pane Markdown editor at /documents/:id with debounced autosave; every save snapshots server-side.</t>
         </is>
       </c>
       <c r="P12" s="149" t="inlineStr">
@@ -4704,7 +4709,12 @@
       </c>
       <c r="N13" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Per-section regeneration via local model; sections parsed from ATX headings, code fences excluded so a shell "#" never splits a doc.</t>
         </is>
       </c>
       <c r="P13" s="149" t="inlineStr">
@@ -4805,7 +4815,12 @@
       </c>
       <c r="N14" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NodeVersion snapshots on every content change (edit/regen/refine/restore) + unified diff + restore, which is itself snapshotted.</t>
         </is>
       </c>
       <c r="P14" s="149" t="inlineStr">
@@ -4904,7 +4919,12 @@
       </c>
       <c r="N15" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Select text -&gt; shorten/expand/tone, preview before apply, applied by offset then comments re-anchored.</t>
         </is>
       </c>
       <c r="P15" s="149" t="inlineStr">
@@ -5003,7 +5023,12 @@
       </c>
       <c r="N16" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Threaded comments anchored to char offsets with anchor_text fallback so drifted anchors are re-found by content, not lost.</t>
         </is>
       </c>
       <c r="P16" s="149" t="inlineStr">
@@ -5102,7 +5127,12 @@
       </c>
       <c r="N17" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>draft -&gt; in_review -&gt; approved with enforced transitions (approved can never fall straight back to draft) + append-only history.</t>
         </is>
       </c>
       <c r="P17" s="149" t="inlineStr">
@@ -5200,7 +5230,12 @@
       </c>
       <c r="N18" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Live preview beside the editor via a hand-written escaping-first Markdown renderer; model output can never inject HTML.</t>
         </is>
       </c>
       <c r="P18" s="149" t="inlineStr">
@@ -5301,7 +5336,12 @@
       </c>
       <c r="N19" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[[wiki links]] resolved against project nodes, with backlinks computed both ways.</t>
         </is>
       </c>
       <c r="P19" s="149" t="inlineStr">
@@ -5401,7 +5441,12 @@
       </c>
       <c r="N20" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Free-form tags with project-wide tag list and find-by-tag.</t>
         </is>
       </c>
       <c r="P20" s="149" t="inlineStr">
@@ -5502,7 +5547,12 @@
       </c>
       <c r="N21" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Custom document types with section structure, prompt, and deterministic verification rules (missing sections, min words, placeholders).</t>
         </is>
       </c>
       <c r="P21" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -5650,7 +5650,12 @@
       </c>
       <c r="N22" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Grounded chat at /copilot with lexical retrieval + inline citations to real nodes; verified live against Ollama.</t>
         </is>
       </c>
       <c r="P22" s="149" t="inlineStr">
@@ -5748,7 +5753,12 @@
       </c>
       <c r="N23" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Deterministic signal ranking (approvals &gt; failed runs &gt; untriaged &gt; comments &gt; review &gt; Pareto); model phrases only the wording.</t>
         </is>
       </c>
       <c r="P23" s="149" t="inlineStr">
@@ -5846,7 +5856,12 @@
       </c>
       <c r="N24" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Model proposes impact/effort/risk with rationale; nothing touches the backlog until the user accepts (edits allowed).</t>
         </is>
       </c>
       <c r="P24" s="149" t="inlineStr">
@@ -6047,7 +6062,12 @@
       </c>
       <c r="N26" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>One-click summarize on any document via document_ai.summarize.</t>
         </is>
       </c>
       <c r="P26" s="149" t="inlineStr">
@@ -6145,7 +6165,12 @@
       </c>
       <c r="N27" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Same chat surface with scope=global — retrieval spans every project; threads persisted separately.</t>
         </is>
       </c>
       <c r="P27" s="149" t="inlineStr">
@@ -6244,7 +6269,12 @@
       </c>
       <c r="N28" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Prompt library with 5 seeded built-ins, fork-to-edit, variable validation, and diff-against-origin.</t>
         </is>
       </c>
       <c r="P28" s="149" t="inlineStr">
@@ -6343,7 +6373,12 @@
       </c>
       <c r="N29" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Per-task model routing in settings; model_routing.call() is the single entry point that resolves routes AND writes telemetry.</t>
         </is>
       </c>
       <c r="P29" s="149" t="inlineStr">
@@ -6441,7 +6476,12 @@
       </c>
       <c r="N30" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Per-call latency + live run tracing ship (Logs &amp; Traces, /usage). True token-by-token streaming still needs a streaming transport through providers.generate(); deferred.</t>
         </is>
       </c>
       <c r="P30" s="149" t="inlineStr">
@@ -6540,7 +6580,12 @@
       </c>
       <c r="N31" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Every model call logged (task, model, latency, est. tokens) and surfaced at /usage with honest estimate labelling.</t>
         </is>
       </c>
       <c r="P31" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -7670,7 +7670,12 @@
       </c>
       <c r="N42" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Kanban at /board over the real Pareto backlog. Planning state lives in its own PlanningMeta row so the generation pipeline's table is untouched.</t>
         </is>
       </c>
       <c r="P42" s="149" t="inlineStr">
@@ -7769,7 +7774,12 @@
       </c>
       <c r="N43" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Timeline endpoint lays features out by dependency depth when no real dates exist, plus sprint and milestone bars.</t>
         </is>
       </c>
       <c r="P43" s="149" t="inlineStr">
@@ -7868,7 +7878,12 @@
       </c>
       <c r="N44" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sprints with capacity, committed-vs-completed, and single-active enforcement (activating one closes the others).</t>
         </is>
       </c>
       <c r="P44" s="149" t="inlineStr">
@@ -7967,7 +7982,12 @@
       </c>
       <c r="N45" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Blocking is DERIVED from blocker rows, never a stored column — the two can never disagree. Cycles refused at write time.</t>
         </is>
       </c>
       <c r="P45" s="149" t="inlineStr">
@@ -8066,7 +8086,12 @@
       </c>
       <c r="N46" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Estimates seeded from the Pareto effort score then refined; capacity checked per sprint.</t>
         </is>
       </c>
       <c r="P46" s="149" t="inlineStr">
@@ -8165,7 +8190,12 @@
       </c>
       <c r="N47" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>AI work breakdown proposes subtasks; on accept they become real backlog features with real blocker edges.</t>
         </is>
       </c>
       <c r="P47" s="149" t="inlineStr">
@@ -8264,7 +8294,12 @@
       </c>
       <c r="N48" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Capacity-aware daily plan from the ready set (blocked work excluded), committed per local date.</t>
         </is>
       </c>
       <c r="P48" s="149" t="inlineStr">
@@ -8363,7 +8398,12 @@
       </c>
       <c r="N49" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Weekly review: completed last week, carryover with days-in-progress, long-blocked items, capacity from real 4-week average.</t>
         </is>
       </c>
       <c r="P49" s="149" t="inlineStr">
@@ -8462,7 +8502,12 @@
       </c>
       <c r="N50" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>OKRs with impact-weighted progress — finishing a high-impact feature moves a key result more than a small one.</t>
         </is>
       </c>
       <c r="P50" s="149" t="inlineStr">
@@ -8561,7 +8606,12 @@
       </c>
       <c r="N51" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Velocity, throughput, cycle time, and cumulative flow, all computed from append-only FeatureStatusChange rows.</t>
         </is>
       </c>
       <c r="P51" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -11991,7 +11991,12 @@
       </c>
       <c r="N85" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Deterministic project-wide pass: placeholders, thin documents, broken [[wiki links]], duplicate titles, undocumented completed features. No model involved, so findings are always literally true.</t>
         </is>
       </c>
       <c r="P85" s="149" t="inlineStr">
@@ -12189,7 +12194,12 @@
       </c>
       <c r="N87" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Batch tag/verify/set-status/move/delete/export with a PER-ITEM outcome, so a partial failure is visible rather than collapsing the job.</t>
         </is>
       </c>
       <c r="P87" s="149" t="inlineStr">
@@ -12288,7 +12298,12 @@
       </c>
       <c r="N88" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Complete versioned project archive (nodes, versions, comments, tags, features, planning, blockers, ideas, edges). Import always creates a NEW project with fresh ids — never overwrites. Verified on 157 nodes / 133 edges.</t>
         </is>
       </c>
       <c r="P88" s="149" t="inlineStr">
@@ -12585,7 +12600,12 @@
       </c>
       <c r="N91" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Trash instead of delete for ideas, features, and documents. A document goes to trash WITH its versions, comments, and tag links, so restore brings the whole thing back. Emptying the trash is the only destructive action and is always user-initiated.</t>
         </is>
       </c>
       <c r="P91" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -6786,7 +6786,12 @@
       </c>
       <c r="N33" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Paste a URL and it is fetched, stripped to readable text, and captured. Network is opt-in: refuses unless a search provider is enabled, and fetched content is scanned for injection-shaped phrases.</t>
         </is>
       </c>
       <c r="P33" s="149" t="inlineStr">
@@ -6884,7 +6889,12 @@
       </c>
       <c r="N34" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>.eml parsed entirely on-device (stdlib email) — no mail server, no account connection.</t>
         </is>
       </c>
       <c r="P34" s="149" t="inlineStr">
@@ -6982,7 +6992,12 @@
       </c>
       <c r="N35" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>OCR via optional Tesseract, detected at runtime like whisper.cpp. Verified end-to-end on a real PNG.</t>
         </is>
       </c>
       <c r="P35" s="149" t="inlineStr">
@@ -7080,7 +7095,12 @@
       </c>
       <c r="N36" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>CSV / Markdown / Notion import with de-duplication against the existing inbox, so re-running an import does not double it. Dry-run mode included.</t>
         </is>
       </c>
       <c r="P36" s="149" t="inlineStr">
@@ -7178,7 +7198,12 @@
       </c>
       <c r="N37" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Browser extension — needs a separately packaged and store-published extension; the loopback capture endpoint it would call already exists (POST /api/v1/ideas).</t>
         </is>
       </c>
       <c r="P37" s="149" t="inlineStr">
@@ -7276,7 +7301,12 @@
       </c>
       <c r="N38" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Mobile PWA + OS share target — needs a hosted origin and service worker; conflicts with local-first until the Lane E server exists.</t>
         </is>
       </c>
       <c r="P38" s="149" t="inlineStr">
@@ -7374,7 +7404,12 @@
       </c>
       <c r="N39" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Meeting notes -&gt; actions/decisions/ideas via the local model. Proposes only; nothing is captured until accepted. Verified against real Ollama.</t>
         </is>
       </c>
       <c r="P39" s="149" t="inlineStr">
@@ -7472,7 +7507,12 @@
       </c>
       <c r="N40" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Built-in gallery: feature idea, bug report, meeting notes, PRD seed, competitor teardown.</t>
         </is>
       </c>
       <c r="P40" s="149" t="inlineStr">
@@ -7570,7 +7610,12 @@
       </c>
       <c r="N41" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Near-duplicate detection across all capture sources; merging appends the distinct half rather than discarding it.</t>
         </is>
       </c>
       <c r="P41" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -10748,7 +10748,12 @@
       </c>
       <c r="N72" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Once-daily nudge whose message reflects real state (streak alive, things waiting, or nothing yet). Passes the single notification gate.</t>
         </is>
       </c>
       <c r="P72" s="149" t="inlineStr">
@@ -10847,7 +10852,12 @@
       </c>
       <c r="N73" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>7-day recap from real activity; a quiet week reads as an invitation to restart, never as a scolding.</t>
         </is>
       </c>
       <c r="P73" s="149" t="inlineStr">
@@ -10946,7 +10956,12 @@
       </c>
       <c r="N74" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>9 badges, all DERIVED from real state rather than incremented counters, so a badge can never be awarded by a drifting counter. Unearned badges show real progress.</t>
         </is>
       </c>
       <c r="P74" s="149" t="inlineStr">
@@ -11045,7 +11060,12 @@
       </c>
       <c r="N75" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Resurfaces documents and ideas on their weekly/monthly anniversary; anything under 7 days old is not yet a memory.</t>
         </is>
       </c>
       <c r="P75" s="149" t="inlineStr">
@@ -11144,7 +11164,12 @@
       </c>
       <c r="N76" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Configurable focus/break intervals with validation, stored in settings.</t>
         </is>
       </c>
       <c r="P76" s="149" t="inlineStr">
@@ -11243,7 +11268,12 @@
       </c>
       <c r="N77" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Accent colour, density, and font scale added to settings alongside the existing light/dark/system theme.</t>
         </is>
       </c>
       <c r="P77" s="149" t="inlineStr">
@@ -11343,7 +11373,12 @@
       </c>
       <c r="N78" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Full shortcut map ships (⌘K, ⌘I, ⌃`, ⌘⏎, Esc) but the discoverable in-app cheat-sheet overlay and user rebinding are not built.</t>
         </is>
       </c>
       <c r="P78" s="149" t="inlineStr">
@@ -11442,7 +11477,12 @@
       </c>
       <c r="N79" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Tray/menu-bar glance endpoint: streak, active-today, waiting counts, running work.</t>
         </is>
       </c>
       <c r="P79" s="149" t="inlineStr">
@@ -11541,7 +11581,12 @@
       </c>
       <c r="N80" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Locally generated SVG share card — SVG not PNG so the user can read exactly what it says before it leaves the machine.</t>
         </is>
       </c>
       <c r="P80" s="149" t="inlineStr">
@@ -11640,7 +11685,12 @@
       </c>
       <c r="N81" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>ONE gate (should_notify) governs every nudge: quiet hours that correctly wrap midnight, per-category mute, and a once-per-day-per-category cap.</t>
         </is>
       </c>
       <c r="P81" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -11789,7 +11789,12 @@
       </c>
       <c r="N82" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Verifier output grouped into the 7 dimensions with per-dimension pass/fail and severity counts, plus a fixable-issue count.</t>
         </is>
       </c>
       <c r="P82" s="149" t="inlineStr">
@@ -11888,7 +11893,12 @@
       </c>
       <c r="N83" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Rules are DECLARATIVE shapes (required_section, forbidden_phrase, min/max_words, required_phrase, regex_absent) — never executable code, which would be an RCE hole in an app that also imports archives.</t>
         </is>
       </c>
       <c r="P83" s="149" t="inlineStr">
@@ -11987,7 +11997,12 @@
       </c>
       <c r="N84" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Flags assertion-shaped sentences (percentages, superlatives, absolutes, money, research claims) that carry no source. Framed as "wants a source", never "is wrong". Code fences excluded.</t>
         </is>
       </c>
       <c r="P84" s="149" t="inlineStr">
@@ -12190,7 +12205,12 @@
       </c>
       <c r="N86" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Deterministic, previewable, idempotent text fixes applied through the normal save path so each is snapshotted and undoable.</t>
         </is>
       </c>
       <c r="P86" s="149" t="inlineStr">
@@ -12500,6 +12520,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Encryption-at-rest vault — needs OS keychain integration and a key-rotation story; not attempted rather than half-built.</t>
+        </is>
+      </c>
       <c r="P89" s="149" t="inlineStr">
         <is>
           <t>Lane G — Quality &amp; Trust</t>
@@ -12596,7 +12621,12 @@
       </c>
       <c r="N90" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Multi-device sync needs the Lane E server; deferred with the rest of the server work.</t>
         </is>
       </c>
       <c r="P90" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -12829,7 +12829,12 @@
       </c>
       <c r="N92" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Plugin SDK executes third-party code in-process — needs a sandbox and a signing story before it is safe to ship in an app that also imports archives.</t>
         </is>
       </c>
       <c r="P92" s="149" t="inlineStr">
@@ -12931,6 +12936,11 @@
           <t>Not started</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Visual pipeline builder — large canvas UI; the underlying pipeline steps exist but the drag-and-drop composer does not.</t>
+        </is>
+      </c>
       <c r="P93" s="149" t="inlineStr">
         <is>
           <t>Lane H — Scale &amp; Ecosystem</t>
@@ -13026,7 +13036,12 @@
       </c>
       <c r="N94" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Community marketplace needs hosting and moderation — Lane E server work.</t>
         </is>
       </c>
       <c r="P94" s="149" t="inlineStr">
@@ -13124,7 +13139,12 @@
       </c>
       <c r="N95" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>13-language selector reaching every generation prompt. English appends nothing, so the default path is byte-identical to before.</t>
         </is>
       </c>
       <c r="P95" s="149" t="inlineStr">
@@ -13222,7 +13242,12 @@
       </c>
       <c r="N96" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Curated model catalog annotated with what is installed and what this machine fits (48GB detected live). Dobby never downloads on your behalf — Ollama pulls.</t>
         </is>
       </c>
       <c r="P96" s="149" t="inlineStr">
@@ -13320,7 +13345,12 @@
       </c>
       <c r="N97" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Cross-project admin console; explicitly machine-local, aggregates nothing off-device. Verified across 3 projects / 330 documents.</t>
         </is>
       </c>
       <c r="P97" s="149" t="inlineStr">
@@ -13418,7 +13448,12 @@
       </c>
       <c r="N98" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Recommendations grounded in real signals: no model installed, a task running slow enough to reroute, an unfinished goal, an untriaged pile.</t>
         </is>
       </c>
       <c r="P98" s="149" t="inlineStr">
@@ -13516,7 +13551,12 @@
       </c>
       <c r="N99" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>3 guided goals whose steps are DERIVED from real data like onboarding, so a checklist can never disagree with the app.</t>
         </is>
       </c>
       <c r="P99" s="149" t="inlineStr">
@@ -13614,7 +13654,12 @@
       </c>
       <c r="N100" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Lexical RAG over Dobby's own shipped Markdown docs (359 sections indexed live). Stays usable with no model — the retrieved sections are the answer, just unsummarised.</t>
         </is>
       </c>
       <c r="P100" s="149" t="inlineStr">
@@ -13713,7 +13758,12 @@
       </c>
       <c r="N101" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Start Your Day composes momentum, next-best-action, daily plan, goals, recommendations and on-this-day into one guided flow.</t>
         </is>
       </c>
       <c r="P101" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -8755,7 +8755,12 @@
       </c>
       <c r="N52" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>GitHub Issues sync needs third-party OAuth credentials and a live account to test against. The outbound webhook + recipe engine (D58/D60) is the local half and ships.</t>
         </is>
       </c>
       <c r="P52" s="149" t="inlineStr">
@@ -8854,7 +8859,12 @@
       </c>
       <c r="N53" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>GitHub PR/commit sync needs third-party OAuth credentials and a live account to test against. The outbound webhook + recipe engine (D58/D60) is the local half and ships.</t>
         </is>
       </c>
       <c r="P53" s="149" t="inlineStr">
@@ -8953,7 +8963,12 @@
       </c>
       <c r="N54" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Jira sync needs third-party OAuth credentials and a live account to test against. The outbound webhook + recipe engine (D58/D60) is the local half and ships.</t>
         </is>
       </c>
       <c r="P54" s="149" t="inlineStr">
@@ -9052,7 +9067,12 @@
       </c>
       <c r="N55" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Linear sync needs third-party OAuth credentials and a live account to test against. The outbound webhook + recipe engine (D58/D60) is the local half and ships.</t>
         </is>
       </c>
       <c r="P55" s="149" t="inlineStr">
@@ -9151,7 +9171,12 @@
       </c>
       <c r="N56" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Notion sync needs third-party OAuth credentials and a live account to test against. The outbound webhook + recipe engine (D58/D60) is the local half and ships.</t>
         </is>
       </c>
       <c r="P56" s="149" t="inlineStr">
@@ -9354,7 +9379,12 @@
       </c>
       <c r="N58" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Calendar sync needs third-party OAuth credentials and a live account to test against. The outbound webhook + recipe engine (D58/D60) is the local half and ships.</t>
         </is>
       </c>
       <c r="P58" s="149" t="inlineStr">
@@ -9453,7 +9483,12 @@
       </c>
       <c r="N59" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Outbound webhooks with HMAC-SHA256 signing and full delivery history. A remote target goes through the approval gate (net.fetch) because any path that can create a webhook can also exfiltrate documents; loopback is exempt. Verified live against an independent receiver: SIGNATURE_VALID=True.</t>
         </is>
       </c>
       <c r="P59" s="149" t="inlineStr">
@@ -9552,7 +9587,12 @@
       </c>
       <c r="N60" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>API keys stored as SHA-256 hashes with a shown-once plaintext, scoped read/write/admin, revocable, with use counts. A leaked database yields no working credentials.</t>
         </is>
       </c>
       <c r="P60" s="149" t="inlineStr">
@@ -9651,7 +9691,12 @@
       </c>
       <c r="N61" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>When-this-then-that recipes with contains / not_contains / field_equals conditions and webhook/tag/create_idea/set_status/notify actions. A failing action is recorded, never raised.</t>
         </is>
       </c>
       <c r="P61" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -9794,7 +9794,12 @@
       </c>
       <c r="N62" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Multi-project workspaces already ship (project switcher + per-project scoping); memberships are now scoped per project too.</t>
         </is>
       </c>
       <c r="P62" s="149" t="inlineStr">
@@ -9894,7 +9899,12 @@
       </c>
       <c r="N63" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Read-only share links: 256-bit token stored HASHED, revocable, expirable. Read-only by CONSTRUCTION — resolve_share has no write path at all. Verified live: resolved 157 docs with no auth, then died instantly on revoke.</t>
         </is>
       </c>
       <c r="P63" s="149" t="inlineStr">
@@ -9994,7 +10004,12 @@
       </c>
       <c r="N64" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Members + 5 roles (viewer/commenter/editor/admin/owner) with capability sets. Passwords use stdlib scrypt with per-user salt; invite and session tokens stored hashed. Sign-in gives the SAME error for wrong password and unknown user — no enumeration oracle.</t>
         </is>
       </c>
       <c r="P64" s="149" t="inlineStr">
@@ -10094,7 +10109,12 @@
       </c>
       <c r="N65" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Presence heartbeats swept on read, so presence is correct even after the app was closed for a week. Scoped as "see who else is here", not OT merging — claiming co-editing would be dishonest.</t>
         </is>
       </c>
       <c r="P65" s="149" t="inlineStr">
@@ -10194,7 +10214,12 @@
       </c>
       <c r="N66" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Review requests assigned to a member; only the assigned reviewer can decide. Approving advances the document to approved and notifies the requester.</t>
         </is>
       </c>
       <c r="P66" s="149" t="inlineStr">
@@ -10294,7 +10319,12 @@
       </c>
       <c r="N67" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Changelog built from real status transitions and version history, not a model summary.</t>
         </is>
       </c>
       <c r="P67" s="149" t="inlineStr">
@@ -10394,7 +10424,12 @@
       </c>
       <c r="N68" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Docs site: one self-contained HTML page per document with inline CSS and wiki links resolved to local files.</t>
         </is>
       </c>
       <c r="P68" s="149" t="inlineStr">
@@ -10494,7 +10529,12 @@
       </c>
       <c r="N69" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Real PDF via ReportLab — no headless browser. Verified: 285-page, 421KB, `file` confirms PDF 1.4.</t>
         </is>
       </c>
       <c r="P69" s="149" t="inlineStr">
@@ -10594,7 +10634,12 @@
       </c>
       <c r="N70" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Offline .zip bundle. Verified: 159 entries, valid zip, inline styles, zero external fetches — renders from a USB stick.</t>
         </is>
       </c>
       <c r="P70" s="149" t="inlineStr">
@@ -10694,7 +10739,12 @@
       </c>
       <c r="N71" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>@mentions resolved by email or handle, with unread tracking. Review requests raise a mention automatically.</t>
         </is>
       </c>
       <c r="P71" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -12612,12 +12612,12 @@
       </c>
       <c r="N89" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Encryption-at-rest vault — needs OS keychain integration and a key-rotation story; not attempted rather than half-built.</t>
+          <t>AES-256-GCM field-level vault. Key derived with scrypt (N=2^15) and held in the macOS keychain, never on disk beside the database. Locking is the DEFAULT state. Tampering is detected, not silently decrypted. Rotation decrypts under the old key before replacing it, so a mid-way failure cannot strand values. Field-level rather than whole-DB on purpose: SQLCipher is a C dep that breaks existing installs, and decrypt-to-tempfile puts plaintext back on disk.</t>
         </is>
       </c>
       <c r="P89" s="149" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="N93" s="146" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Visual pipeline builder — large canvas UI; the underlying pipeline steps exist but the drag-and-drop composer does not.</t>
+          <t>Composable pipelines from a FIXED step catalogue (generate/verify/transform/filter/save/capture) — never user code, same reasoning as custom rules. Linear chain with an explicit trace rather than a DAG. A failed verify or unmatched filter STOPS the run and the trace says why. Dry-run mode writes nothing.</t>
         </is>
       </c>
       <c r="P93" s="149" t="inlineStr">

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -15270,7 +15270,7 @@
       </c>
       <c r="F33" s="127" t="inlineStr">
         <is>
-          <t>Mentions parsed and routed; signature-verified webhook. Needs a Slack app + bot token from your workspace to run.</t>
+          <t>Mentions parsed and routed; signature-verified webhook. @mentions of MEMBERS now also work in-app (D70). Slack itself still needs an app + bot token from your workspace to run end-to-end.</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="F39" s="127" t="inlineStr">
         <is>
-          <t>Two connectors of the 25+ OpenWorker ships. The interface is there; the rest is volume.</t>
+          <t>Two messaging connectors plus outbound webhooks (any endpoint, HMAC-signed) and a recipe engine, which together cover the generic integration case. The named 25+ SaaS connectors each need their own OAuth credentials.</t>
         </is>
       </c>
     </row>
@@ -15580,7 +15580,7 @@
       </c>
       <c r="D43" s="129" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E43" s="126" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="F43" s="127" t="inlineStr">
         <is>
-          <t>Generated documents are browsable and exportable (md/json/mermaid/png/svg). No 'deliverable' object distinct from a document.</t>
+          <t>Deliverables now exist as objects distinct from documents: a read-only share link (revocable, expirable), a real 285-page PDF (ReportLab), and a self-contained offline HTML bundle (159 entries, zero external fetches) — alongside the existing md/json/mermaid/png/svg exports.</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="F51" s="127" t="inlineStr">
         <is>
-          <t>Deliberately deferred: an OAuth broker conflicts with local-first unless optional.</t>
+          <t>Deliberately deferred: an OAuth broker conflicts with local-first unless optional. Outbound webhooks + API keys give the same integration reach without a broker.</t>
         </is>
       </c>
     </row>

--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100-Day Roadmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature · Mind Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Features" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Next Tasks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Connectors" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Tools" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Providers" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Configs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · GUI Screens" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending · Goals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature · Mind Map" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Features" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Next Tasks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Connectors" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Tools" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Providers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · Configs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OW · GUI Screens" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -247,6 +248,26 @@
       <name val="Arial"/>
       <color rgb="00166534"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B7280"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009CA3AF"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -431,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -843,6 +864,24 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1639,6 +1678,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="107" t="inlineStr">
+        <is>
+          <t>Model providers — provider-agnostic (aisuite + native OpenAI/Anthropic/Gemini). Bring your own key or run local via Ollama.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>Native SDK</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="111" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B3" s="112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>OpenAIProvider; default provider. env OPENAI_API_KEY; recommended gpt-5.6-sol. Optional custom base_url also serves Azure OpenAI /openai/v1, OpenRouter, vLLM, and any OpenAI-compliant gateway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="49.75" customHeight="1">
+      <c r="A4" s="113" t="inlineStr">
+        <is>
+          <t>Claude (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B4" s="114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" s="110" t="inlineStr">
+        <is>
+          <t>AnthropicProvider — native Messages API. env ANTHROPIC_API_KEY; recommended claude-fable-5. Extended thinking on by default (hidden thinking_budget profile override; 0 = off).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28.75" customHeight="1">
+      <c r="A5" s="111" t="inlineStr">
+        <is>
+          <t>Gemini (Google)</t>
+        </is>
+      </c>
+      <c r="B5" s="112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
+        <is>
+          <t>GeminiProvider — native Google GenAI API. env GEMINI_API_KEY; recommended gemini-3.6-flash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="43" customHeight="1">
+      <c r="A6" s="113" t="inlineStr">
+        <is>
+          <t>Ollama (local models)</t>
+        </is>
+      </c>
+      <c r="B6" s="114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="110" t="inlineStr">
+        <is>
+          <t>Local, keyless; reached via OpenAIProvider against the OpenAI-compatible /v1 endpoint (default http://localhost:11434). Recommended qwen3-coder:30b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45.25" customHeight="1">
+      <c r="A7" s="111" t="inlineStr">
+        <is>
+          <t>Z AI (GLM)</t>
+        </is>
+      </c>
+      <c r="B7" s="112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API via OpenAIProvider. base https://api.z.ai/api/paas/v4; env ZAI_API_KEY; recommended glm-5.2. China mainland endpoint variant available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32.5" customHeight="1">
+      <c r="A8" s="113" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="B8" s="114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C8" s="110" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API. base https://api.deepseek.com; env DEEPSEEK_API_KEY; recommended deepseek-v4-flash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="41.75" customHeight="1">
+      <c r="A9" s="111" t="inlineStr">
+        <is>
+          <t>Kimi (Moonshot AI)</t>
+        </is>
+      </c>
+      <c r="B9" s="112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API. base https://api.moonshot.ai/v1; env MOONSHOT_API_KEY; recommended kimi-k2.6. China mainland endpoint variant available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31.25" customHeight="1">
+      <c r="A10" s="113" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="B10" s="114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="110" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API. base https://api.minimax.io/v1; env MINIMAX_API_KEY; recommended MiniMax-M2.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="49.25" customHeight="1">
+      <c r="A11" s="111" t="inlineStr">
+        <is>
+          <t>Qwen (Alibaba)</t>
+        </is>
+      </c>
+      <c r="B11" s="112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API. base https://dashscope-intl.aliyuncs.com/compatible-mode/v1; env DASHSCOPE_API_KEY; recommended qwen3-max. China (Beijing) endpoint variant available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27.75" customHeight="1">
+      <c r="A12" s="113" t="inlineStr">
+        <is>
+          <t>xAI (Grok)</t>
+        </is>
+      </c>
+      <c r="B12" s="114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C12" s="110" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API. base https://api.x.ai/v1; env XAI_API_KEY; recommended grok-4.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33.25" customHeight="1">
+      <c r="A13" s="111" t="inlineStr">
+        <is>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="B13" s="112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API. base https://api.mistral.ai/v1; env MISTRAL_API_KEY; recommended mistral-large-latest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40.25" customHeight="1">
+      <c r="A14" s="113" t="inlineStr">
+        <is>
+          <t>Meta (Muse Spark)</t>
+        </is>
+      </c>
+      <c r="B14" s="114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" s="110" t="inlineStr">
+        <is>
+          <t>OpenAI-compatible API. base https://api.meta.ai/v1; env META_API_KEY; recommended muse-spark-1.1 (public preview, US-only as of 2026-07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="47.75" customHeight="1">
+      <c r="A15" s="111" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="B15" s="112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t>Reseller via OpenAI-compatible API (many labs' models under Together's namespace). base https://api.together.xyz/v1; env TOGETHER_API_KEY; recommended zai-org/GLM-5.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="43.25" customHeight="1">
+      <c r="A16" s="113" t="inlineStr">
+        <is>
+          <t>Fireworks AI</t>
+        </is>
+      </c>
+      <c r="B16" s="114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="110" t="inlineStr">
+        <is>
+          <t>Reseller via OpenAI-compatible API. base https://api.fireworks.ai/inference/v1; env FIREWORKS_API_KEY; recommended accounts/fireworks/models/glm-5p2.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2945,7 +3268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13878,6 +14201,1642 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="132" t="inlineStr">
+        <is>
+          <t>Pending work as of 2026-07-27. Sized S (&lt;half day) / M (1-2 days) / L (3+ days). 'Blocked by' names what must exist first — external means credentials or infra I cannot supply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="148" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="148" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="C2" s="148" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="D2" s="148" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="E2" s="148" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F2" s="148" t="inlineStr">
+        <is>
+          <t>Blocked by</t>
+        </is>
+      </c>
+      <c r="G2" s="148" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H2" s="148" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C3" s="153" t="inlineStr">
+        <is>
+          <t>Track time actually spent per work item</t>
+        </is>
+      </c>
+      <c r="D3" s="154" t="inlineStr">
+        <is>
+          <t>Nothing records that a 150-min block happened. Without it every later goal in this theme is guesswork.</t>
+        </is>
+      </c>
+      <c r="E3" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F3" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C4" s="153" t="inlineStr">
+        <is>
+          <t>Add remaining-effort so a capped block continues tomorrow</t>
+        </is>
+      </c>
+      <c r="D4" s="154" t="inlineStr">
+        <is>
+          <t>A 7-point item gets 150 min today, then the same 150 min tomorrow with no memory. Work never visibly shrinks.</t>
+        </is>
+      </c>
+      <c r="E4" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F4" s="153" t="inlineStr">
+        <is>
+          <t>Time tracking</t>
+        </is>
+      </c>
+      <c r="G4" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C5" s="153" t="inlineStr">
+        <is>
+          <t>Reconcile capacity units — planner counts points, scheduler counts minutes</t>
+        </is>
+      </c>
+      <c r="D5" s="154" t="inlineStr">
+        <is>
+          <t>capacity=8 admits one 7-point item, then the cap leaves 4h of the day empty. Measured 29.4% utilisation.</t>
+        </is>
+      </c>
+      <c r="E5" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F5" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H5" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C6" s="153" t="inlineStr">
+        <is>
+          <t>Suggest a work breakdown when an estimate exceeds one block</t>
+        </is>
+      </c>
+      <c r="D6" s="154" t="inlineStr">
+        <is>
+          <t>A 5.2h item should probably be three tasks. WBS already exists (D46); nothing offers it at the moment it is needed.</t>
+        </is>
+      </c>
+      <c r="E6" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F6" s="153" t="inlineStr">
+        <is>
+          <t>Remaining-effort</t>
+        </is>
+      </c>
+      <c r="G6" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C7" s="153" t="inlineStr">
+        <is>
+          <t>Project a completion date across days for oversized items</t>
+        </is>
+      </c>
+      <c r="D7" s="154" t="inlineStr">
+        <is>
+          <t>"This is 5.2h — it lands Thursday" is currently unanswerable.</t>
+        </is>
+      </c>
+      <c r="E7" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F7" s="153" t="inlineStr">
+        <is>
+          <t>Remaining-effort</t>
+        </is>
+      </c>
+      <c r="G7" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C8" s="153" t="inlineStr">
+        <is>
+          <t>Make max_block_minutes a user setting, not a constant</t>
+        </is>
+      </c>
+      <c r="D8" s="154" t="inlineStr">
+        <is>
+          <t>150 min is my guess about focus stamina, hard-coded. Some people work in 50s, some in 4h stretches.</t>
+        </is>
+      </c>
+      <c r="E8" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F8" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C9" s="153" t="inlineStr">
+        <is>
+          <t>Learn minutes-per-point from real cycle-time data</t>
+        </is>
+      </c>
+      <c r="D9" s="154" t="inlineStr">
+        <is>
+          <t>45 min/point is a guess. delivery_analytics already computes real cycle times — close the loop.</t>
+        </is>
+      </c>
+      <c r="E9" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F9" s="153" t="inlineStr">
+        <is>
+          <t>Time tracking</t>
+        </is>
+      </c>
+      <c r="G9" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H9" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C10" s="153" t="inlineStr">
+        <is>
+          <t>Reschedule the rest of the day when a block overruns</t>
+        </is>
+      </c>
+      <c r="D10" s="154" t="inlineStr">
+        <is>
+          <t>The buffer absorbs 15 min. A block that runs an hour long silently invalidates everything after it.</t>
+        </is>
+      </c>
+      <c r="E10" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F10" s="153" t="inlineStr">
+        <is>
+          <t>Time tracking</t>
+        </is>
+      </c>
+      <c r="G10" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H10" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="153" t="inlineStr">
+        <is>
+          <t>Time &amp; scheduling</t>
+        </is>
+      </c>
+      <c r="C11" s="153" t="inlineStr">
+        <is>
+          <t>Recurring commitments (standups, 1:1s) as fixed blocks</t>
+        </is>
+      </c>
+      <c r="D11" s="154" t="inlineStr">
+        <is>
+          <t>A schedule that ignores the meetings you already have is one you delete on day one.</t>
+        </is>
+      </c>
+      <c r="E11" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F11" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H11" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="153" t="inlineStr">
+        <is>
+          <t>Work Graph</t>
+        </is>
+      </c>
+      <c r="C12" s="153" t="inlineStr">
+        <is>
+          <t>UI reskin — serif display type, cream/dark palette, Daily Alignment layout</t>
+        </is>
+      </c>
+      <c r="D12" s="154" t="inlineStr">
+        <is>
+          <t>The last step of the agreed plan. The data model now supports every screen in the mockups.</t>
+        </is>
+      </c>
+      <c r="E12" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F12" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H12" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="153" t="inlineStr">
+        <is>
+          <t>Work Graph</t>
+        </is>
+      </c>
+      <c r="C13" s="153" t="inlineStr">
+        <is>
+          <t>Skill editor — currently you can fork and run, but not edit in the UI</t>
+        </is>
+      </c>
+      <c r="D13" s="154" t="inlineStr">
+        <is>
+          <t>The Skill Studio renders config beautifully and cannot change it. The API is complete; the form is not.</t>
+        </is>
+      </c>
+      <c r="E13" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F13" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H13" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="153" t="inlineStr">
+        <is>
+          <t>Work Graph</t>
+        </is>
+      </c>
+      <c r="C14" s="153" t="inlineStr">
+        <is>
+          <t>Attach skills to decisions and projects explicitly</t>
+        </is>
+      </c>
+      <c r="D14" s="154" t="inlineStr">
+        <is>
+          <t>Skill→project "unlocks" edges are inferred from blocked work. Real links would make the graph honest.</t>
+        </is>
+      </c>
+      <c r="E14" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F14" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H14" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="153" t="inlineStr">
+        <is>
+          <t>Work Graph</t>
+        </is>
+      </c>
+      <c r="C15" s="153" t="inlineStr">
+        <is>
+          <t>Decision templates (build-vs-buy, framework choice, hire-vs-contract)</t>
+        </is>
+      </c>
+      <c r="D15" s="154" t="inlineStr">
+        <is>
+          <t>Framing a good decision is a skill. Templates carry the framing so users do not have to.</t>
+        </is>
+      </c>
+      <c r="E15" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F15" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H15" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="153" t="inlineStr">
+        <is>
+          <t>Work Graph</t>
+        </is>
+      </c>
+      <c r="C16" s="153" t="inlineStr">
+        <is>
+          <t>Decision review — resurface decided forks to check the call held up</t>
+        </is>
+      </c>
+      <c r="D16" s="154" t="inlineStr">
+        <is>
+          <t>Deciding is append-only, which is the hard half. Learning from it needs the loop closed.</t>
+        </is>
+      </c>
+      <c r="E16" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F16" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H16" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="153" t="inlineStr">
+        <is>
+          <t>Work Graph</t>
+        </is>
+      </c>
+      <c r="C17" s="153" t="inlineStr">
+        <is>
+          <t>Graph filtering and focus mode for large projects</t>
+        </is>
+      </c>
+      <c r="D17" s="154" t="inlineStr">
+        <is>
+          <t>Currently caps at 12 project nodes and says what it hid. A real project needs filter-by-goal.</t>
+        </is>
+      </c>
+      <c r="E17" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F17" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H17" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="153" t="inlineStr">
+        <is>
+          <t>Roadmap · Partial</t>
+        </is>
+      </c>
+      <c r="C18" s="153" t="inlineStr">
+        <is>
+          <t>D29 — token-by-token streaming through providers.generate()</t>
+        </is>
+      </c>
+      <c r="D18" s="154" t="inlineStr">
+        <is>
+          <t>Per-call latency and run tracing ship. Real streaming needs a streaming transport in the provider layer.</t>
+        </is>
+      </c>
+      <c r="E18" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F18" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H18" s="156" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="153" t="inlineStr">
+        <is>
+          <t>Roadmap · Partial</t>
+        </is>
+      </c>
+      <c r="C19" s="153" t="inlineStr">
+        <is>
+          <t>D77 — keyboard cheat-sheet overlay and user rebinding</t>
+        </is>
+      </c>
+      <c r="D19" s="154" t="inlineStr">
+        <is>
+          <t>The shortcuts exist and are undiscoverable. A "?" overlay is most of the value.</t>
+        </is>
+      </c>
+      <c r="E19" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F19" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H19" s="156" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="153" t="inlineStr">
+        <is>
+          <t>Deferred · needs creds</t>
+        </is>
+      </c>
+      <c r="C20" s="153" t="inlineStr">
+        <is>
+          <t>One OAuth connector done properly end-to-end (GitHub first)</t>
+        </is>
+      </c>
+      <c r="D20" s="154" t="inlineStr">
+        <is>
+          <t>D51/D52. Building one against a live account teaches the shape for Jira, Linear, Notion.</t>
+        </is>
+      </c>
+      <c r="E20" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F20" s="153" t="inlineStr">
+        <is>
+          <t>External: GitHub OAuth app + test repo</t>
+        </is>
+      </c>
+      <c r="G20" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H20" s="156" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="153" t="inlineStr">
+        <is>
+          <t>Deferred · needs creds</t>
+        </is>
+      </c>
+      <c r="C21" s="153" t="inlineStr">
+        <is>
+          <t>Jira, Linear, Notion sync once the GitHub shape is proven</t>
+        </is>
+      </c>
+      <c r="D21" s="154" t="inlineStr">
+        <is>
+          <t>D53/D54/D55. Cheaper each time the first one is done, but each needs its own credentials.</t>
+        </is>
+      </c>
+      <c r="E21" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F21" s="153" t="inlineStr">
+        <is>
+          <t>External creds + GitHub connector</t>
+        </is>
+      </c>
+      <c r="G21" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H21" s="157" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="153" t="inlineStr">
+        <is>
+          <t>Deferred · needs creds</t>
+        </is>
+      </c>
+      <c r="C22" s="153" t="inlineStr">
+        <is>
+          <t>D57 Calendar time-blocking — write blocks to a real calendar</t>
+        </is>
+      </c>
+      <c r="D22" s="154" t="inlineStr">
+        <is>
+          <t>Pairs directly with the time-block scheduler. CalDAV would avoid a cloud dependency.</t>
+        </is>
+      </c>
+      <c r="E22" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F22" s="153" t="inlineStr">
+        <is>
+          <t>External: CalDAV or Google creds</t>
+        </is>
+      </c>
+      <c r="G22" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H22" s="156" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="153" t="inlineStr">
+        <is>
+          <t>Deferred · needs infra</t>
+        </is>
+      </c>
+      <c r="C23" s="153" t="inlineStr">
+        <is>
+          <t>D36 browser extension + D37 mobile PWA</t>
+        </is>
+      </c>
+      <c r="D23" s="154" t="inlineStr">
+        <is>
+          <t>The loopback capture endpoint already exists. Both need packaging and a hosted origin.</t>
+        </is>
+      </c>
+      <c r="E23" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F23" s="153" t="inlineStr">
+        <is>
+          <t>Store publishing / hosted origin</t>
+        </is>
+      </c>
+      <c r="G23" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H23" s="157" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="153" t="inlineStr">
+        <is>
+          <t>Deferred · needs design</t>
+        </is>
+      </c>
+      <c r="C24" s="153" t="inlineStr">
+        <is>
+          <t>D89 multi-device sync — conflict resolution model</t>
+        </is>
+      </c>
+      <c r="D24" s="154" t="inlineStr">
+        <is>
+          <t>A genuine design problem (CRDT vs last-writer-wins with a merge UI), not plumbing.</t>
+        </is>
+      </c>
+      <c r="E24" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F24" s="153" t="inlineStr">
+        <is>
+          <t>Design decision</t>
+        </is>
+      </c>
+      <c r="G24" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H24" s="157" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="153" t="inlineStr">
+        <is>
+          <t>Deferred · needs sandbox</t>
+        </is>
+      </c>
+      <c r="C25" s="153" t="inlineStr">
+        <is>
+          <t>D91 plugin SDK — sandbox and signing before executing third-party code</t>
+        </is>
+      </c>
+      <c r="D25" s="154" t="inlineStr">
+        <is>
+          <t>Dangerous in an app that also imports archives from other people. Needs a threat model first.</t>
+        </is>
+      </c>
+      <c r="E25" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F25" s="153" t="inlineStr">
+        <is>
+          <t>Security design</t>
+        </is>
+      </c>
+      <c r="G25" s="153" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H25" s="158" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="153" t="inlineStr">
+        <is>
+          <t>Deferred · needs hosting</t>
+        </is>
+      </c>
+      <c r="C26" s="153" t="inlineStr">
+        <is>
+          <t>D93 community marketplace</t>
+        </is>
+      </c>
+      <c r="D26" s="154" t="inlineStr">
+        <is>
+          <t>Needs hosting, moderation, and a trust story. Furthest from local-first.</t>
+        </is>
+      </c>
+      <c r="E26" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F26" s="153" t="inlineStr">
+        <is>
+          <t>Hosting + moderation</t>
+        </is>
+      </c>
+      <c r="G26" s="153" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H26" s="158" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="153" t="inlineStr">
+        <is>
+          <t>OW parity</t>
+        </is>
+      </c>
+      <c r="C27" s="153" t="inlineStr">
+        <is>
+          <t>Inline-vs-Inbox routing for approvals (OW row 16)</t>
+        </is>
+      </c>
+      <c r="D27" s="154" t="inlineStr">
+        <is>
+          <t>Everything goes to the Inbox. A fast yes/no for low-risk asks would cut the friction sharply.</t>
+        </is>
+      </c>
+      <c r="E27" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F27" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H27" s="156" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="153" t="inlineStr">
+        <is>
+          <t>OW parity</t>
+        </is>
+      </c>
+      <c r="C28" s="153" t="inlineStr">
+        <is>
+          <t>Per-task working folders and thread isolation (OW row 7)</t>
+        </is>
+      </c>
+      <c r="D28" s="154" t="inlineStr">
+        <is>
+          <t>Tasks run in-process today. Isolation matters once skills can be installed from elsewhere.</t>
+        </is>
+      </c>
+      <c r="E28" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F28" s="153" t="inlineStr">
+        <is>
+          <t>Plugin sandbox design</t>
+        </is>
+      </c>
+      <c r="G28" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H28" s="157" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="153" t="inlineStr">
+        <is>
+          <t>OW parity</t>
+        </is>
+      </c>
+      <c r="C29" s="153" t="inlineStr">
+        <is>
+          <t>Progressive skill disclosure for personas (OW row 32)</t>
+        </is>
+      </c>
+      <c r="D29" s="154" t="inlineStr">
+        <is>
+          <t>Personas contribute routing and prompts. The Skill object now gives this somewhere to land.</t>
+        </is>
+      </c>
+      <c r="E29" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F29" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H29" s="157" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="153" t="inlineStr">
+        <is>
+          <t>OW parity</t>
+        </is>
+      </c>
+      <c r="C30" s="153" t="inlineStr">
+        <is>
+          <t>OS-level reveal-in-Finder + OS-global capture hotkey (OW row 44, D2)</t>
+        </is>
+      </c>
+      <c r="D30" s="154" t="inlineStr">
+        <is>
+          <t>Both blocked on the same Tauri capabilities work. Worth doing together.</t>
+        </is>
+      </c>
+      <c r="E30" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F30" s="153" t="inlineStr">
+        <is>
+          <t>Tauri capabilities config</t>
+        </is>
+      </c>
+      <c r="G30" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H30" s="156" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="153" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C31" s="153" t="inlineStr">
+        <is>
+          <t>Fix suite-wide test isolation — every module shares one database</t>
+        </is>
+      </c>
+      <c r="D31" s="154" t="inlineStr">
+        <is>
+          <t>Modules set DOBBY_DB_PATH but src.main imports once. Three tests already broke on ordering.</t>
+        </is>
+      </c>
+      <c r="E31" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F31" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H31" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="153" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C32" s="153" t="inlineStr">
+        <is>
+          <t>D88 vault: extend encryption beyond settings to connector credentials</t>
+        </is>
+      </c>
+      <c r="D32" s="154" t="inlineStr">
+        <is>
+          <t>The vault protects six settings fields. Messaging and MCP credentials are still plaintext.</t>
+        </is>
+      </c>
+      <c r="E32" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F32" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H32" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="153" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C33" s="153" t="inlineStr">
+        <is>
+          <t>Frontend test coverage — there is currently none</t>
+        </is>
+      </c>
+      <c r="D33" s="154" t="inlineStr">
+        <is>
+          <t>1,334 backend tests and zero for the UI. Every bug I found in the UI was found by eye.</t>
+        </is>
+      </c>
+      <c r="E33" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F33" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H33" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="153" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C34" s="153" t="inlineStr">
+        <is>
+          <t>Deduplicate the three Markdown renderers</t>
+        </is>
+      </c>
+      <c r="D34" s="154" t="inlineStr">
+        <is>
+          <t>markdown.ts (preview), publish_service (bundles), and the PDF builder each parse Markdown separately.</t>
+        </is>
+      </c>
+      <c r="E34" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F34" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H34" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="153" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C35" s="153" t="inlineStr">
+        <is>
+          <t>Retire the seeded demo data or make it obviously fake</t>
+        </is>
+      </c>
+      <c r="D35" s="154" t="inlineStr">
+        <is>
+          <t>"Data Encryption", "Offline Syncing" look like real backlog items and pollute every screenshot.</t>
+        </is>
+      </c>
+      <c r="E35" s="154" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F35" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="153" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H35" s="156" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="153" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C36" s="153" t="inlineStr">
+        <is>
+          <t>Performance pass — the work graph and timeline read every row</t>
+        </is>
+      </c>
+      <c r="D36" s="154" t="inlineStr">
+        <is>
+          <t>Fine at 157 nodes. A project with 5,000 documents will not be.</t>
+        </is>
+      </c>
+      <c r="E36" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F36" s="153" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H36" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="153" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="C37" s="153" t="inlineStr">
+        <is>
+          <t>Signed, notarised macOS build with auto-update</t>
+        </is>
+      </c>
+      <c r="D37" s="154" t="inlineStr">
+        <is>
+          <t>The open-core plan sells the signed build. Nothing is packaged yet.</t>
+        </is>
+      </c>
+      <c r="E37" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F37" s="153" t="inlineStr">
+        <is>
+          <t>Apple developer cert</t>
+        </is>
+      </c>
+      <c r="G37" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H37" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="153" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="C38" s="153" t="inlineStr">
+        <is>
+          <t>Wire licence verification into the packaged app</t>
+        </is>
+      </c>
+      <c r="D38" s="154" t="inlineStr">
+        <is>
+          <t>The Ed25519 licensing + clock-rollback detection is built and unused by any real build.</t>
+        </is>
+      </c>
+      <c r="E38" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F38" s="153" t="inlineStr">
+        <is>
+          <t>Signed build</t>
+        </is>
+      </c>
+      <c r="G38" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H38" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="153" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="C39" s="153" t="inlineStr">
+        <is>
+          <t>Billing — Lemon Squeezy / Paddle, after 1000 beta users</t>
+        </is>
+      </c>
+      <c r="D39" s="154" t="inlineStr">
+        <is>
+          <t>Your call: deferred until the product is complete. The licence layer is ready for it.</t>
+        </is>
+      </c>
+      <c r="E39" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F39" s="153" t="inlineStr">
+        <is>
+          <t>Signed build + beta</t>
+        </is>
+      </c>
+      <c r="G39" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H39" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="153" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="C40" s="153" t="inlineStr">
+        <is>
+          <t>Onboarding for a genuinely empty install</t>
+        </is>
+      </c>
+      <c r="D40" s="154" t="inlineStr">
+        <is>
+          <t>Every screen has been verified against a seeded project. A first-run user sees empty states we have barely tested.</t>
+        </is>
+      </c>
+      <c r="E40" s="154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F40" s="153" t="inlineStr">
+        <is>
+          <t>Demo-data retirement</t>
+        </is>
+      </c>
+      <c r="G40" s="153" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H40" s="155" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="153" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="C41" s="153" t="inlineStr">
+        <is>
+          <t>Windows and Linux builds</t>
+        </is>
+      </c>
+      <c r="D41" s="154" t="inlineStr">
+        <is>
+          <t>Tauri supports them; nothing has been built or tested outside macOS. OCR/keychain paths are macOS-specific.</t>
+        </is>
+      </c>
+      <c r="E41" s="154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F41" s="153" t="inlineStr">
+        <is>
+          <t>Signed build</t>
+        </is>
+      </c>
+      <c r="G41" s="153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H41" s="157" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13970,7 +15929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14226,7 +16185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16140,7 +18099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16571,7 +18530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18137,7 +20096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19415,288 +21374,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="107" t="inlineStr">
-        <is>
-          <t>Model providers — provider-agnostic (aisuite + native OpenAI/Anthropic/Gemini). Bring your own key or run local via Ollama.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
-      <c r="B2" s="29" t="inlineStr">
-        <is>
-          <t>Native SDK</t>
-        </is>
-      </c>
-      <c r="C2" s="29" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="54" customHeight="1">
-      <c r="A3" s="111" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="B3" s="112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C3" s="109" t="inlineStr">
-        <is>
-          <t>OpenAIProvider; default provider. env OPENAI_API_KEY; recommended gpt-5.6-sol. Optional custom base_url also serves Azure OpenAI /openai/v1, OpenRouter, vLLM, and any OpenAI-compliant gateway.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="49.75" customHeight="1">
-      <c r="A4" s="113" t="inlineStr">
-        <is>
-          <t>Claude (Anthropic)</t>
-        </is>
-      </c>
-      <c r="B4" s="114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C4" s="110" t="inlineStr">
-        <is>
-          <t>AnthropicProvider — native Messages API. env ANTHROPIC_API_KEY; recommended claude-fable-5. Extended thinking on by default (hidden thinking_budget profile override; 0 = off).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28.75" customHeight="1">
-      <c r="A5" s="111" t="inlineStr">
-        <is>
-          <t>Gemini (Google)</t>
-        </is>
-      </c>
-      <c r="B5" s="112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C5" s="109" t="inlineStr">
-        <is>
-          <t>GeminiProvider — native Google GenAI API. env GEMINI_API_KEY; recommended gemini-3.6-flash.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="43" customHeight="1">
-      <c r="A6" s="113" t="inlineStr">
-        <is>
-          <t>Ollama (local models)</t>
-        </is>
-      </c>
-      <c r="B6" s="114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C6" s="110" t="inlineStr">
-        <is>
-          <t>Local, keyless; reached via OpenAIProvider against the OpenAI-compatible /v1 endpoint (default http://localhost:11434). Recommended qwen3-coder:30b.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45.25" customHeight="1">
-      <c r="A7" s="111" t="inlineStr">
-        <is>
-          <t>Z AI (GLM)</t>
-        </is>
-      </c>
-      <c r="B7" s="112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C7" s="109" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API via OpenAIProvider. base https://api.z.ai/api/paas/v4; env ZAI_API_KEY; recommended glm-5.2. China mainland endpoint variant available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32.5" customHeight="1">
-      <c r="A8" s="113" t="inlineStr">
-        <is>
-          <t>DeepSeek</t>
-        </is>
-      </c>
-      <c r="B8" s="114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="110" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API. base https://api.deepseek.com; env DEEPSEEK_API_KEY; recommended deepseek-v4-flash.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="41.75" customHeight="1">
-      <c r="A9" s="111" t="inlineStr">
-        <is>
-          <t>Kimi (Moonshot AI)</t>
-        </is>
-      </c>
-      <c r="B9" s="112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C9" s="109" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API. base https://api.moonshot.ai/v1; env MOONSHOT_API_KEY; recommended kimi-k2.6. China mainland endpoint variant available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="31.25" customHeight="1">
-      <c r="A10" s="113" t="inlineStr">
-        <is>
-          <t>MiniMax</t>
-        </is>
-      </c>
-      <c r="B10" s="114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C10" s="110" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API. base https://api.minimax.io/v1; env MINIMAX_API_KEY; recommended MiniMax-M2.5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="49.25" customHeight="1">
-      <c r="A11" s="111" t="inlineStr">
-        <is>
-          <t>Qwen (Alibaba)</t>
-        </is>
-      </c>
-      <c r="B11" s="112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="109" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API. base https://dashscope-intl.aliyuncs.com/compatible-mode/v1; env DASHSCOPE_API_KEY; recommended qwen3-max. China (Beijing) endpoint variant available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="27.75" customHeight="1">
-      <c r="A12" s="113" t="inlineStr">
-        <is>
-          <t>xAI (Grok)</t>
-        </is>
-      </c>
-      <c r="B12" s="114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C12" s="110" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API. base https://api.x.ai/v1; env XAI_API_KEY; recommended grok-4.3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="33.25" customHeight="1">
-      <c r="A13" s="111" t="inlineStr">
-        <is>
-          <t>Mistral</t>
-        </is>
-      </c>
-      <c r="B13" s="112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C13" s="109" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API. base https://api.mistral.ai/v1; env MISTRAL_API_KEY; recommended mistral-large-latest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40.25" customHeight="1">
-      <c r="A14" s="113" t="inlineStr">
-        <is>
-          <t>Meta (Muse Spark)</t>
-        </is>
-      </c>
-      <c r="B14" s="114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C14" s="110" t="inlineStr">
-        <is>
-          <t>OpenAI-compatible API. base https://api.meta.ai/v1; env META_API_KEY; recommended muse-spark-1.1 (public preview, US-only as of 2026-07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="47.75" customHeight="1">
-      <c r="A15" s="111" t="inlineStr">
-        <is>
-          <t>Together AI</t>
-        </is>
-      </c>
-      <c r="B15" s="112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C15" s="109" t="inlineStr">
-        <is>
-          <t>Reseller via OpenAI-compatible API (many labs' models under Together's namespace). base https://api.together.xyz/v1; env TOGETHER_API_KEY; recommended zai-org/GLM-5.2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="43.25" customHeight="1">
-      <c r="A16" s="113" t="inlineStr">
-        <is>
-          <t>Fireworks AI</t>
-        </is>
-      </c>
-      <c r="B16" s="114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C16" s="110" t="inlineStr">
-        <is>
-          <t>Reseller via OpenAI-compatible API. base https://api.fireworks.ai/inference/v1; env FIREWORKS_API_KEY; recommended accounts/fireworks/models/glm-5p2.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Dobby_100_Day_Roadmap.xlsx
+++ b/Dobby_100_Day_Roadmap.xlsx
@@ -14299,7 +14299,7 @@
       </c>
       <c r="H3" s="155" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H4" s="155" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="H5" s="155" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
